--- a/returns_stats.xlsx
+++ b/returns_stats.xlsx
@@ -470,10 +470,10 @@
         <v>0.0008475992477881</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.003116562696563463</v>
+        <v>-0.003116484774013828</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01954783896648904</v>
+        <v>-0.01954753441557144</v>
       </c>
     </row>
     <row r="3">
@@ -481,13 +481,13 @@
         <v>45084</v>
       </c>
       <c r="B3" t="n">
-        <v>0.007582709359632567</v>
+        <v>0.007582817711913936</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005189365337373131</v>
+        <v>0.005189443747897649</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007779460503777091</v>
+        <v>0.007779354779555048</v>
       </c>
     </row>
     <row r="4">
@@ -495,13 +495,13 @@
         <v>45085</v>
       </c>
       <c r="B4" t="n">
-        <v>0.000600378293168502</v>
+        <v>0.0006002706917564993</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0006220176461428917</v>
+        <v>0.0006219395919038195</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.00477124039446164</v>
+        <v>-0.004771344492737972</v>
       </c>
     </row>
     <row r="5">
@@ -509,13 +509,13 @@
         <v>45086</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.007080922370581777</v>
+        <v>-0.007080814898245191</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001181208003463885</v>
+        <v>0.001181130046230106</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01313533336687422</v>
+        <v>-0.0131353347407952</v>
       </c>
     </row>
     <row r="6">
@@ -523,13 +523,13 @@
         <v>45089</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0008863672623622421</v>
+        <v>0.0008863671664229855</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.006084702762612637</v>
+        <v>-0.006084625371135077</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02053791177070052</v>
+        <v>0.02053780795795013</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +537,13 @@
         <v>45090</v>
       </c>
       <c r="B7" t="n">
-        <v>0.01477372771755836</v>
+        <v>0.01477350983408288</v>
       </c>
       <c r="C7" t="n">
         <v>0.001686623755126959</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009984872255409005</v>
+        <v>0.009985185899102911</v>
       </c>
     </row>
     <row r="8">
@@ -551,13 +551,13 @@
         <v>45091</v>
       </c>
       <c r="B8" t="n">
-        <v>0.01229736532832271</v>
+        <v>0.01229747320734442</v>
       </c>
       <c r="C8" t="n">
         <v>-0.001091342829543707</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0034102476275365</v>
+        <v>-0.003410452936448705</v>
       </c>
     </row>
     <row r="9">
@@ -571,7 +571,7 @@
         <v>-0.01229904583644592</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.01045839183304631</v>
+        <v>-0.01045839291216077</v>
       </c>
     </row>
     <row r="10">
@@ -579,13 +579,13 @@
         <v>45093</v>
       </c>
       <c r="B10" t="n">
-        <v>0.009735376097337323</v>
+        <v>0.0097354813423709</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01308429839800795</v>
+        <v>0.01308421912757507</v>
       </c>
       <c r="D10" t="n">
-        <v>0.003769022898592045</v>
+        <v>0.00376923183601563</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         <v>45096</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.009932419150110228</v>
+        <v>-0.009932626575454018</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0008735453853541131</v>
+        <v>0.0008736237003428293</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001819366057822069</v>
+        <v>0.001819261988165621</v>
       </c>
     </row>
     <row r="12">
@@ -607,13 +607,13 @@
         <v>45097</v>
       </c>
       <c r="B12" t="n">
-        <v>0.002076884084328157</v>
+        <v>0.002076989578942534</v>
       </c>
       <c r="C12" t="n">
-        <v>0.002088221596812989</v>
+        <v>0.002088299775151237</v>
       </c>
       <c r="D12" t="n">
-        <v>0.007264351597230378</v>
+        <v>0.007264455289246907</v>
       </c>
     </row>
     <row r="13">
@@ -624,10 +624,10 @@
         <v>0.002815758202411311</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01748052617971418</v>
+        <v>0.01748044680054472</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.003107370485137873</v>
+        <v>-0.003107370165252199</v>
       </c>
     </row>
     <row r="14">
@@ -641,7 +641,7 @@
         <v>0.00489125821775005</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.01369914504777869</v>
+        <v>-0.01369924689820146</v>
       </c>
     </row>
     <row r="15">
@@ -663,13 +663,13 @@
         <v>45103</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.007635138816335596</v>
+        <v>-0.0076350319893429</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.004837299975780307</v>
+        <v>-0.004837223669248436</v>
       </c>
       <c r="D16" t="n">
-        <v>0.004229401713716996</v>
+        <v>0.004229295644556208</v>
       </c>
     </row>
     <row r="17">
@@ -677,13 +677,13 @@
         <v>45104</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0003608391361475949</v>
+        <v>0.0003606237995130712</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01409308411630583</v>
+        <v>0.01409308303568424</v>
       </c>
       <c r="D17" t="n">
-        <v>0.006927142168333678</v>
+        <v>0.006927354144899533</v>
       </c>
     </row>
     <row r="18">
@@ -691,13 +691,13 @@
         <v>45105</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01323872972760665</v>
+        <v>0.01323883876231613</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01058134767820995</v>
+        <v>0.01058127126630093</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01110122876004027</v>
+        <v>0.01110112269976615</v>
       </c>
     </row>
     <row r="19">
@@ -705,13 +705,13 @@
         <v>45107</v>
       </c>
       <c r="B19" t="n">
-        <v>0.008203202371324547</v>
+        <v>0.008203096167254342</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01506421251613776</v>
+        <v>0.01506413769599613</v>
       </c>
       <c r="D19" t="n">
-        <v>0.03258997209283021</v>
+        <v>0.0325898683487047</v>
       </c>
     </row>
     <row r="20">
@@ -719,13 +719,13 @@
         <v>45110</v>
       </c>
       <c r="B20" t="n">
-        <v>0.02566418152179351</v>
+        <v>0.02566428956521349</v>
       </c>
       <c r="C20" t="n">
-        <v>0.01081469631135712</v>
+        <v>0.01081469710850591</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.00134800353412623</v>
+        <v>-0.001347903199732881</v>
       </c>
     </row>
     <row r="21">
@@ -736,7 +736,7 @@
         <v>-0.01030327810008047</v>
       </c>
       <c r="C21" t="n">
-        <v>0.004884185183532397</v>
+        <v>0.004884185539692609</v>
       </c>
       <c r="D21" t="n">
         <v>0.008585164662421985</v>
@@ -747,10 +747,10 @@
         <v>45112</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.001641694132873628</v>
+        <v>-0.001641590359540368</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.03176709452242499</v>
+        <v>-0.03176702426094058</v>
       </c>
       <c r="D22" t="n">
         <v>0.001598379117492055</v>
@@ -761,13 +761,13 @@
         <v>45113</v>
       </c>
       <c r="B23" t="n">
-        <v>0.02099055076483536</v>
+        <v>0.02099054858299421</v>
       </c>
       <c r="C23" t="n">
         <v>0.001015914444040034</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.002523607783148973</v>
+        <v>-0.002523707373037865</v>
       </c>
     </row>
     <row r="24">
@@ -775,13 +775,13 @@
         <v>45114</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.001951640049567827</v>
+        <v>-0.001951741657859496</v>
       </c>
       <c r="C24" t="n">
         <v>-0.008716392235104897</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.01019425230434989</v>
+        <v>-0.01019425332216306</v>
       </c>
     </row>
     <row r="25">
@@ -789,13 +789,13 @@
         <v>45117</v>
       </c>
       <c r="B25" t="n">
-        <v>0.03852126693989333</v>
+        <v>0.03852136894596514</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.00237896414718175</v>
+        <v>-0.002379039677046335</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.000789308894245333</v>
+        <v>-0.0007894098440194286</v>
       </c>
     </row>
     <row r="26">
@@ -803,13 +803,13 @@
         <v>45118</v>
       </c>
       <c r="B26" t="n">
-        <v>0.01084071024631728</v>
+        <v>0.01084070918151658</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.004859823358026594</v>
+        <v>-0.004859748015982102</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01463318214750764</v>
+        <v>0.0146335889013316</v>
       </c>
     </row>
     <row r="27">
@@ -817,13 +817,13 @@
         <v>45119</v>
       </c>
       <c r="B27" t="n">
-        <v>0.001103257261636514</v>
+        <v>0.001103257154434045</v>
       </c>
       <c r="C27" t="n">
         <v>-0.009372715944458432</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.01134489306692577</v>
+        <v>-0.01134508979721949</v>
       </c>
     </row>
     <row r="28">
@@ -831,13 +831,13 @@
         <v>45120</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.008942123703907456</v>
+        <v>-0.008942414021801515</v>
       </c>
       <c r="C28" t="n">
-        <v>0.004990971063242755</v>
+        <v>0.004990894263712464</v>
       </c>
       <c r="D28" t="n">
-        <v>0.02385054001070763</v>
+        <v>0.02385043937509312</v>
       </c>
     </row>
     <row r="29">
@@ -845,13 +845,13 @@
         <v>45121</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.0008386407418978781</v>
+        <v>-0.0008382491551890414</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00207177190716723</v>
+        <v>0.002071848483623517</v>
       </c>
       <c r="D29" t="n">
-        <v>0.04457550389779108</v>
+        <v>0.04457550827917656</v>
       </c>
     </row>
     <row r="30">
@@ -859,13 +859,13 @@
         <v>45124</v>
       </c>
       <c r="B30" t="n">
-        <v>0.02043284228289588</v>
+        <v>0.02043264223742591</v>
       </c>
       <c r="C30" t="n">
         <v>0.02091823151829897</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.002103912520749596</v>
+        <v>-0.002103818621815301</v>
       </c>
     </row>
     <row r="31">
@@ -876,7 +876,7 @@
         <v>0.008492033447503822</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0008339239423119649</v>
+        <v>-0.0008338492447176327</v>
       </c>
       <c r="D31" t="n">
         <v>0.03671952734676442</v>
@@ -887,10 +887,10 @@
         <v>45126</v>
       </c>
       <c r="B32" t="n">
-        <v>0.00758748394708042</v>
+        <v>0.007587579195435179</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0045306017846094</v>
+        <v>0.004530526685969205</v>
       </c>
       <c r="D32" t="n">
         <v>-0.0001694499942425098</v>
@@ -901,13 +901,13 @@
         <v>45127</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.001210943411886434</v>
+        <v>-0.001211226890692751</v>
       </c>
       <c r="C33" t="n">
         <v>0.002166074385547168</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.01725471595213146</v>
+        <v>-0.01725480692299164</v>
       </c>
     </row>
     <row r="34">
@@ -915,13 +915,13 @@
         <v>45128</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.0309560570369134</v>
+        <v>-0.03095587360517038</v>
       </c>
       <c r="C34" t="n">
         <v>-0.007698062989687671</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.08133856799746886</v>
+        <v>-0.08133839039061608</v>
       </c>
     </row>
     <row r="35">
@@ -929,13 +929,13 @@
         <v>45131</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.02022650260591097</v>
+        <v>-0.02022660027507539</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001581401976352037</v>
+        <v>0.001581476814361382</v>
       </c>
       <c r="D35" t="n">
-        <v>0.003754974345962836</v>
+        <v>0.003754772439408027</v>
       </c>
     </row>
     <row r="36">
@@ -943,13 +943,13 @@
         <v>45132</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.0006431705396791054</v>
+        <v>-0.0006430709183313787</v>
       </c>
       <c r="C36" t="n">
-        <v>0.01084364311559338</v>
+        <v>0.01084356758551652</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.001496370904028432</v>
+        <v>-0.001496170279918552</v>
       </c>
     </row>
     <row r="37">
@@ -963,7 +963,7 @@
         <v>-0.003477560509708044</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01067739416206348</v>
+        <v>0.01067729255099947</v>
       </c>
     </row>
     <row r="38">
@@ -971,13 +971,13 @@
         <v>45134</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.009302385387089496</v>
+        <v>-0.009302483541473006</v>
       </c>
       <c r="C38" t="n">
         <v>-0.01038029943916075</v>
       </c>
       <c r="D38" t="n">
-        <v>0.003187889937570132</v>
+        <v>0.003187989413026227</v>
       </c>
     </row>
     <row r="39">
@@ -985,13 +985,13 @@
         <v>45135</v>
       </c>
       <c r="B39" t="n">
-        <v>0.01004898417845013</v>
+        <v>0.01004918332613713</v>
       </c>
       <c r="C39" t="n">
         <v>-0.01772099639454805</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.009348544905995904</v>
+        <v>-0.009348643138337498</v>
       </c>
     </row>
     <row r="40">
@@ -999,10 +999,10 @@
         <v>45138</v>
       </c>
       <c r="B40" t="n">
-        <v>0.00846578305599599</v>
+        <v>0.008465684135275486</v>
       </c>
       <c r="C40" t="n">
-        <v>0.004685068444669982</v>
+        <v>0.004684992138138</v>
       </c>
       <c r="D40" t="n">
         <v>0.01133907211851248</v>
@@ -1016,7 +1016,7 @@
         <v>-0.01414143693526848</v>
       </c>
       <c r="C41" t="n">
-        <v>0.006692167872915711</v>
+        <v>0.006692168381190466</v>
       </c>
       <c r="D41" t="n">
         <v>0.007007375356339329</v>
@@ -1030,10 +1030,10 @@
         <v>-0.01068352709912501</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.01308471628002705</v>
+        <v>-0.01308456637559929</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.006116417142951525</v>
+        <v>-0.00611622057471839</v>
       </c>
     </row>
     <row r="43">
@@ -1041,13 +1041,13 @@
         <v>45141</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.004203017356581795</v>
+        <v>-0.004203117084126129</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.007223389808637126</v>
+        <v>-0.007223465702508425</v>
       </c>
       <c r="D43" t="n">
-        <v>0.005490809655360085</v>
+        <v>0.005490709680456174</v>
       </c>
     </row>
     <row r="44">
@@ -1055,13 +1055,13 @@
         <v>45142</v>
       </c>
       <c r="B44" t="n">
-        <v>0.01359104872974193</v>
+        <v>0.01359115023934487</v>
       </c>
       <c r="C44" t="n">
         <v>0.01445979887308679</v>
       </c>
       <c r="D44" t="n">
-        <v>0.01029821662870223</v>
+        <v>0.01029821561588373</v>
       </c>
     </row>
     <row r="45">
@@ -1075,7 +1075,7 @@
         <v>-0.0005749783102241279</v>
       </c>
       <c r="D45" t="n">
-        <v>0.01062877241840132</v>
+        <v>0.01062867403728496</v>
       </c>
     </row>
     <row r="46">
@@ -1083,7 +1083,7 @@
         <v>45146</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.006022661760666237</v>
+        <v>-0.006022760006429206</v>
       </c>
       <c r="C46" t="n">
         <v>-0.0008175085356503242</v>
@@ -1097,7 +1097,7 @@
         <v>45147</v>
       </c>
       <c r="B47" t="n">
-        <v>0.006597145826327866</v>
+        <v>0.006597344160514718</v>
       </c>
       <c r="C47" t="n">
         <v>0.0003635583906471673</v>
@@ -1111,7 +1111,7 @@
         <v>45148</v>
       </c>
       <c r="B48" t="n">
-        <v>0.004455126124816022</v>
+        <v>0.004455027494108421</v>
       </c>
       <c r="C48" t="n">
         <v>-0.008876095730565803</v>
@@ -1125,13 +1125,13 @@
         <v>45149</v>
       </c>
       <c r="B49" t="n">
-        <v>0.004218539362639051</v>
+        <v>0.004218441604908252</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.01042261686316892</v>
+        <v>-0.01042269352655167</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.01241810595220227</v>
+        <v>-0.01241800935909898</v>
       </c>
     </row>
     <row r="50">
@@ -1139,13 +1139,13 @@
         <v>45152</v>
       </c>
       <c r="B50" t="n">
-        <v>0.01181705799052479</v>
+        <v>0.01181705914088083</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0048801975568179</v>
+        <v>-0.004880042993215983</v>
       </c>
       <c r="D50" t="n">
-        <v>0.01581824201436888</v>
+        <v>0.01581804485186344</v>
       </c>
     </row>
     <row r="51">
@@ -1153,13 +1153,13 @@
         <v>45154</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.0008148037399577923</v>
+        <v>-0.0008147076081933546</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.002917690728519662</v>
+        <v>-0.002917768352127648</v>
       </c>
       <c r="D51" t="n">
-        <v>0.01790374290153562</v>
+        <v>0.01790384091003627</v>
       </c>
     </row>
     <row r="52">
@@ -1167,13 +1167,13 @@
         <v>45155</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.01442624750311616</v>
+        <v>-0.01442634379172003</v>
       </c>
       <c r="C52" t="n">
         <v>-0.005541001710545279</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.004899535264461075</v>
+        <v>-0.004899440673360012</v>
       </c>
     </row>
     <row r="53">
@@ -1181,13 +1181,13 @@
         <v>45156</v>
       </c>
       <c r="B53" t="n">
-        <v>0.007407366157132333</v>
+        <v>0.007407464578846668</v>
       </c>
       <c r="C53" t="n">
         <v>-0.004100687425927285</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.01611698150441132</v>
+        <v>-0.01611707502920856</v>
       </c>
     </row>
     <row r="54">
@@ -1209,13 +1209,13 @@
         <v>45160</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.0002381622852911658</v>
+        <v>-0.000238064235770663</v>
       </c>
       <c r="C55" t="n">
         <v>-0.004278134694454927</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.001174028955752915</v>
+        <v>-0.001174124428547585</v>
       </c>
     </row>
     <row r="56">
@@ -1223,13 +1223,13 @@
         <v>45161</v>
       </c>
       <c r="B56" t="n">
-        <v>0.001111557996524182</v>
+        <v>0.001111361741774175</v>
       </c>
       <c r="C56" t="n">
         <v>0.002464218945049002</v>
       </c>
       <c r="D56" t="n">
-        <v>0.002991810945076834</v>
+        <v>0.002992002401095872</v>
       </c>
     </row>
     <row r="57">
@@ -1237,13 +1237,13 @@
         <v>45162</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.01681081577255428</v>
+        <v>-0.01681071945541424</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.004601020051259508</v>
+        <v>-0.004601099094363681</v>
       </c>
       <c r="D57" t="n">
-        <v>0.01111558914728605</v>
+        <v>0.01111549278808588</v>
       </c>
     </row>
     <row r="58">
@@ -1254,7 +1254,7 @@
         <v>-0.004617271164842673</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.01127084035436499</v>
+        <v>-0.01127076184089482</v>
       </c>
       <c r="D58" t="n">
         <v>-0.002458569313416814</v>
@@ -1271,7 +1271,7 @@
         <v>0.01040664335375086</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.003133673679181936</v>
+        <v>-0.003133484710136636</v>
       </c>
     </row>
     <row r="60">
@@ -1282,10 +1282,10 @@
         <v>-0.009575413560518165</v>
       </c>
       <c r="C60" t="n">
-        <v>0.00795437094559337</v>
+        <v>0.007954450432072546</v>
       </c>
       <c r="D60" t="n">
-        <v>0.001412718810287039</v>
+        <v>0.001412718542487701</v>
       </c>
     </row>
     <row r="61">
@@ -1293,13 +1293,13 @@
         <v>45168</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.0009503221131553774</v>
+        <v>-0.0009504241995356155</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.007294239776771683</v>
+        <v>-0.007294318060751426</v>
       </c>
       <c r="D61" t="n">
-        <v>0.01234453739597141</v>
+        <v>0.01234434576358767</v>
       </c>
     </row>
     <row r="62">
@@ -1307,13 +1307,13 @@
         <v>45169</v>
       </c>
       <c r="B62" t="n">
-        <v>-0.004569747740646446</v>
+        <v>-0.004569748207599256</v>
       </c>
       <c r="C62" t="n">
         <v>-0.004592427701495927</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0002091453844643709</v>
+        <v>0.0002089583970843467</v>
       </c>
     </row>
     <row r="63">
@@ -1321,13 +1321,13 @@
         <v>45170</v>
       </c>
       <c r="B63" t="n">
-        <v>0.002347253981791031</v>
+        <v>0.002347356875337159</v>
       </c>
       <c r="C63" t="n">
-        <v>0.002068230209121502</v>
+        <v>0.002068150403973679</v>
       </c>
       <c r="D63" t="n">
-        <v>0.005851668130160137</v>
+        <v>0.005851856172435221</v>
       </c>
     </row>
     <row r="64">
@@ -1338,10 +1338,10 @@
         <v>-0.0008083394661170251</v>
       </c>
       <c r="C64" t="n">
-        <v>0.006255118888831124</v>
+        <v>0.006255278667870234</v>
       </c>
       <c r="D64" t="n">
-        <v>0.01471765717401796</v>
+        <v>0.01471756424367521</v>
       </c>
     </row>
     <row r="65">
@@ -1349,13 +1349,13 @@
         <v>45174</v>
       </c>
       <c r="B65" t="n">
-        <v>0.005351368908475873</v>
+        <v>0.005351266413428757</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.006089998732091151</v>
+        <v>-0.00608999825009604</v>
       </c>
       <c r="D65" t="n">
-        <v>0.009419256366881568</v>
+        <v>0.009419257229520417</v>
       </c>
     </row>
     <row r="66">
@@ -1363,13 +1363,13 @@
         <v>45175</v>
       </c>
       <c r="B66" t="n">
-        <v>0.002104135274723307</v>
+        <v>0.002104339388215415</v>
       </c>
       <c r="C66" t="n">
-        <v>0.01308015563904874</v>
+        <v>0.01308007496716046</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.0009806775938713264</v>
+        <v>-0.0009805869549636137</v>
       </c>
     </row>
     <row r="67">
@@ -1377,13 +1377,13 @@
         <v>45176</v>
       </c>
       <c r="B67" t="n">
-        <v>0.001358778173969455</v>
+        <v>0.001358778035733588</v>
       </c>
       <c r="C67" t="n">
-        <v>0.009620907930740774</v>
+        <v>0.009620829328551794</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.007614364405863827</v>
+        <v>-0.007614455222800243</v>
       </c>
     </row>
     <row r="68">
@@ -1391,13 +1391,13 @@
         <v>45177</v>
       </c>
       <c r="B68" t="n">
-        <v>0.006661231207662377</v>
+        <v>0.00666102733619045</v>
       </c>
       <c r="C68" t="n">
-        <v>0.007790922507133757</v>
+        <v>0.00779092311368168</v>
       </c>
       <c r="D68" t="n">
-        <v>0.002318958566140505</v>
+        <v>0.002318958778357194</v>
       </c>
     </row>
     <row r="69">
@@ -1405,13 +1405,13 @@
         <v>45180</v>
       </c>
       <c r="B69" t="n">
-        <v>0.01078344102039286</v>
+        <v>0.01078364395889153</v>
       </c>
       <c r="C69" t="n">
-        <v>0.005174292864667196</v>
+        <v>0.005174370515705906</v>
       </c>
       <c r="D69" t="n">
-        <v>0.004661059930743727</v>
+        <v>0.004661060356307978</v>
       </c>
     </row>
     <row r="70">
@@ -1419,13 +1419,13 @@
         <v>45181</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.01444676114851984</v>
+        <v>-0.01444675970603448</v>
       </c>
       <c r="C70" t="n">
         <v>0.003125407324337193</v>
       </c>
       <c r="D70" t="n">
-        <v>0.01669545998576849</v>
+        <v>0.01669555238147424</v>
       </c>
     </row>
     <row r="71">
@@ -1433,13 +1433,13 @@
         <v>45182</v>
       </c>
       <c r="B71" t="n">
-        <v>0.005002280026572103</v>
+        <v>0.005002279519781272</v>
       </c>
       <c r="C71" t="n">
-        <v>0.004276374686638329</v>
+        <v>0.004276298072440454</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.001831968079866853</v>
+        <v>-0.001832057465964931</v>
       </c>
     </row>
     <row r="72">
@@ -1447,13 +1447,13 @@
         <v>45183</v>
       </c>
       <c r="B72" t="n">
-        <v>0.0009180560156307749</v>
+        <v>0.000917955115361746</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.0006083202092609374</v>
+        <v>-0.0006083202556684819</v>
       </c>
       <c r="D72" t="n">
-        <v>0.005739627383612333</v>
+        <v>0.005739538347437678</v>
       </c>
     </row>
     <row r="73">
@@ -1464,10 +1464,10 @@
         <v>0.001854671692895771</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0114735179943839</v>
+        <v>0.01147367153901535</v>
       </c>
       <c r="D73" t="n">
-        <v>0.003085828082771913</v>
+        <v>0.003085917671406202</v>
       </c>
     </row>
     <row r="74">
@@ -1478,10 +1478,10 @@
         <v>-0.008706801257334029</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.01967803624903397</v>
+        <v>-0.01967803476396202</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.01309872339685192</v>
+        <v>-0.01309872455956262</v>
       </c>
     </row>
     <row r="75">
@@ -1492,10 +1492,10 @@
         <v>-0.0222865601180271</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.04011542889563857</v>
+        <v>-0.04011550279080167</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.001039115274248048</v>
+        <v>-0.001038935481036285</v>
       </c>
     </row>
     <row r="76">
@@ -1509,7 +1509,7 @@
         <v>-0.006618881500535356</v>
       </c>
       <c r="D76" t="n">
-        <v>0.007716791492306418</v>
+        <v>0.007716790797510642</v>
       </c>
     </row>
     <row r="77">
@@ -1523,7 +1523,7 @@
         <v>-0.01525730987258878</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.003728914234168434</v>
+        <v>-0.003729003248403528</v>
       </c>
     </row>
     <row r="78">
@@ -1537,7 +1537,7 @@
         <v>0.0008824966094715947</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.01470441183473681</v>
+        <v>-0.01470450151656455</v>
       </c>
     </row>
     <row r="79">
@@ -1545,13 +1545,13 @@
         <v>45195</v>
       </c>
       <c r="B79" t="n">
-        <v>0.0008759265877027467</v>
+        <v>0.0008758210162205238</v>
       </c>
       <c r="C79" t="n">
         <v>0.00434363495740242</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.009157818059487011</v>
+        <v>-0.009157727872798893</v>
       </c>
     </row>
     <row r="80">
@@ -1559,13 +1559,13 @@
         <v>45196</v>
       </c>
       <c r="B80" t="n">
-        <v>0.011270018876538</v>
+        <v>0.01127002006528954</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.007023812485191905</v>
+        <v>-0.007023730925809102</v>
       </c>
       <c r="D80" t="n">
-        <v>0.00434743627477463</v>
+        <v>0.004347252551820002</v>
       </c>
     </row>
     <row r="81">
@@ -1573,13 +1573,13 @@
         <v>45197</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.01469032577973706</v>
+        <v>-0.01469022300839318</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.002063017263570277</v>
+        <v>-0.002063099230407595</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.0187799967109602</v>
+        <v>-0.01877972575475972</v>
       </c>
     </row>
     <row r="82">
@@ -1593,7 +1593,7 @@
         <v>0.001706369890653869</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.002778628359272561</v>
+        <v>-0.00277890774346945</v>
       </c>
     </row>
     <row r="83">
@@ -1604,10 +1604,10 @@
         <v>-0.01144998192962143</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.01195702625553374</v>
+        <v>-0.01195694408964754</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.001010361982347274</v>
+        <v>-0.001009988274601636</v>
       </c>
     </row>
     <row r="84">
@@ -1618,10 +1618,10 @@
         <v>-0.001725537896922202</v>
       </c>
       <c r="C84" t="n">
-        <v>0.01425690758020504</v>
+        <v>0.01425682323436916</v>
       </c>
       <c r="D84" t="n">
-        <v>0.007217700723763043</v>
+        <v>0.007217418667078812</v>
       </c>
     </row>
     <row r="85">
@@ -1629,13 +1629,13 @@
         <v>45204</v>
       </c>
       <c r="B85" t="n">
-        <v>-2.146103066547056e-05</v>
+        <v>-2.156780196227448e-05</v>
       </c>
       <c r="C85" t="n">
         <v>0.004053403552863211</v>
       </c>
       <c r="D85" t="n">
-        <v>0.01322396122430503</v>
+        <v>0.01322386955461075</v>
       </c>
     </row>
     <row r="86">
@@ -1643,13 +1643,13 @@
         <v>45205</v>
       </c>
       <c r="B86" t="n">
-        <v>0.001685314317953823</v>
+        <v>0.001685421271500509</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.001106823582904037</v>
+        <v>-0.001106905243195011</v>
       </c>
       <c r="D86" t="n">
-        <v>0.01042054038829265</v>
+        <v>0.01042063398485826</v>
       </c>
     </row>
     <row r="87">
@@ -1660,10 +1660,10 @@
         <v>-0.008520373726895181</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.01160337794200605</v>
+        <v>-0.0116032971398099</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.002197998834714943</v>
+        <v>-0.002197817553830195</v>
       </c>
     </row>
     <row r="88">
@@ -1674,10 +1674,10 @@
         <v>0.004416402021918397</v>
       </c>
       <c r="C88" t="n">
-        <v>0.005671872244706666</v>
+        <v>0.00567178953421088</v>
       </c>
       <c r="D88" t="n">
-        <v>0.01335209002045779</v>
+        <v>0.01335190692614763</v>
       </c>
     </row>
     <row r="89">
@@ -1688,10 +1688,10 @@
         <v>0.01587683523392247</v>
       </c>
       <c r="C89" t="n">
-        <v>0.009673047952621472</v>
+        <v>0.009673213236221834</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.0005016566785536192</v>
+        <v>-0.0005016567235731628</v>
       </c>
     </row>
     <row r="90">
@@ -1699,13 +1699,13 @@
         <v>45211</v>
       </c>
       <c r="B90" t="n">
-        <v>0.001854940199383259</v>
+        <v>0.001854834834986718</v>
       </c>
       <c r="C90" t="n">
-        <v>0.006657569107549888</v>
+        <v>0.006657487109167581</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.01933882942555543</v>
+        <v>-0.01933892094878131</v>
       </c>
     </row>
     <row r="91">
@@ -1713,13 +1713,13 @@
         <v>45212</v>
       </c>
       <c r="B91" t="n">
-        <v>-4.248840271681154e-05</v>
+        <v>-4.238323786065479e-05</v>
       </c>
       <c r="C91" t="n">
         <v>-0.009097621555094415</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.02343916734716744</v>
+        <v>-0.02343908008175355</v>
       </c>
     </row>
     <row r="92">
@@ -1727,13 +1727,13 @@
         <v>45215</v>
       </c>
       <c r="B92" t="n">
-        <v>-0.002234627352987295</v>
+        <v>-0.002234732526769645</v>
       </c>
       <c r="C92" t="n">
         <v>-0.004004539005609598</v>
       </c>
       <c r="D92" t="n">
-        <v>0.002096174252289806</v>
+        <v>0.002096361958830784</v>
       </c>
     </row>
     <row r="93">
@@ -1741,13 +1741,13 @@
         <v>45216</v>
       </c>
       <c r="B93" t="n">
-        <v>0.004777994241699002</v>
+        <v>0.00477810015468827</v>
       </c>
       <c r="C93" t="n">
         <v>0.007583619166151134</v>
       </c>
       <c r="D93" t="n">
-        <v>0.005787271800529403</v>
+        <v>0.005787271259078741</v>
       </c>
     </row>
     <row r="94">
@@ -1755,13 +1755,13 @@
         <v>45217</v>
       </c>
       <c r="B94" t="n">
-        <v>-0.01326824975760987</v>
+        <v>-0.01326835466569254</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.01391770458083452</v>
+        <v>-0.01391762320930767</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.001316984910113783</v>
+        <v>-0.001317170828684655</v>
       </c>
     </row>
     <row r="95">
@@ -1769,13 +1769,13 @@
         <v>45218</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.007680785193711182</v>
+        <v>-0.007680679691565051</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.003158371094492685</v>
+        <v>-0.003158535873882373</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.004789796719589123</v>
+        <v>-0.004789890308950495</v>
       </c>
     </row>
     <row r="96">
@@ -1786,10 +1786,10 @@
         <v>-0.00305696637336994</v>
       </c>
       <c r="C96" t="n">
-        <v>0.005181706155911625</v>
+        <v>0.005181789366338396</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.00446422095231036</v>
+        <v>-0.004464221787936817</v>
       </c>
     </row>
     <row r="97">
@@ -1800,10 +1800,10 @@
         <v>-0.01561488436635139</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.01099954515481161</v>
+        <v>-0.01099946280007902</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.01303201870596982</v>
+        <v>-0.01303183313387291</v>
       </c>
     </row>
     <row r="98">
@@ -1811,10 +1811,10 @@
         <v>45224</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.002319749674904226</v>
+        <v>-0.00231964049993838</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.006340978413743703</v>
+        <v>-0.006341144427056578</v>
       </c>
       <c r="D98" t="n">
         <v>-0.01481329077450777</v>
@@ -1825,13 +1825,13 @@
         <v>45225</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.01392853707574038</v>
+        <v>-0.01392853555155726</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.02211838029726432</v>
+        <v>-0.02211829834876411</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.007737002815652927</v>
+        <v>-0.0077369061309146</v>
       </c>
     </row>
     <row r="100">
@@ -1839,13 +1839,13 @@
         <v>45226</v>
       </c>
       <c r="B100" t="n">
-        <v>0.01765105325367888</v>
+        <v>0.01765094032034797</v>
       </c>
       <c r="C100" t="n">
         <v>0.003929232676989969</v>
       </c>
       <c r="D100" t="n">
-        <v>0.01537386565611132</v>
+        <v>0.01537386415810316</v>
       </c>
     </row>
     <row r="101">
@@ -1853,13 +1853,13 @@
         <v>45229</v>
       </c>
       <c r="B101" t="n">
-        <v>0.02061082653990143</v>
+        <v>0.02061071749021726</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0108566133679675</v>
+        <v>0.01085669873011019</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.002390637590684142</v>
+        <v>-0.00239073332455586</v>
       </c>
     </row>
     <row r="102">
@@ -1867,13 +1867,13 @@
         <v>45230</v>
       </c>
       <c r="B102" t="n">
-        <v>-0.01063784092890629</v>
+        <v>-0.01063784206553275</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.005790755564653138</v>
+        <v>-0.0057909239663404</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.006281515917242686</v>
+        <v>-0.006281612110500268</v>
       </c>
     </row>
     <row r="103">
@@ -1881,13 +1881,13 @@
         <v>45231</v>
       </c>
       <c r="B103" t="n">
-        <v>0.004152242408533846</v>
+        <v>0.004152350853289688</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.001354663443129955</v>
+        <v>-0.001354578620981539</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.01041369204287368</v>
+        <v>-0.01041349944828085</v>
       </c>
     </row>
     <row r="104">
@@ -1901,7 +1901,7 @@
         <v>0.001526010518432708</v>
       </c>
       <c r="D104" t="n">
-        <v>0.01181557802806643</v>
+        <v>0.01181557687226698</v>
       </c>
     </row>
     <row r="105">
@@ -1912,10 +1912,10 @@
         <v>-0.0002155415924455228</v>
       </c>
       <c r="C105" t="n">
-        <v>0.004740052500989966</v>
+        <v>0.004740137423816737</v>
       </c>
       <c r="D105" t="n">
-        <v>0.01379406822485962</v>
+        <v>0.0137939702136094</v>
       </c>
     </row>
     <row r="106">
@@ -1926,10 +1926,10 @@
         <v>0.008320058796743801</v>
       </c>
       <c r="C106" t="n">
-        <v>0.007245157364675903</v>
+        <v>0.007245156752299531</v>
       </c>
       <c r="D106" t="n">
-        <v>0.01025887989410967</v>
+        <v>0.01025897525635755</v>
       </c>
     </row>
     <row r="107">
@@ -1940,10 +1940,10 @@
         <v>-0.006498467313714062</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.004851164712528333</v>
+        <v>-0.004851248219655213</v>
       </c>
       <c r="D107" t="n">
-        <v>0.0007125793427693594</v>
+        <v>0.000712484881642883</v>
       </c>
     </row>
     <row r="108">
@@ -1957,7 +1957,7 @@
         <v>0.002891361003905857</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.009471056667022304</v>
+        <v>-0.009470962340365152</v>
       </c>
     </row>
     <row r="109">
@@ -1968,10 +1968,10 @@
         <v>-0.01085230974926588</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.003955635936203294</v>
+        <v>-0.003955551856027806</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.01164616871646174</v>
+        <v>-0.01164626283597714</v>
       </c>
     </row>
     <row r="110">
@@ -1979,13 +1979,13 @@
         <v>45240</v>
       </c>
       <c r="B110" t="n">
-        <v>0.001882637219176475</v>
+        <v>0.001882530281532624</v>
       </c>
       <c r="C110" t="n">
-        <v>0.003937663911053324</v>
+        <v>0.00393766357865899</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.004327880237635529</v>
+        <v>-0.004327976588324289</v>
       </c>
     </row>
     <row r="111">
@@ -1993,13 +1993,13 @@
         <v>45243</v>
       </c>
       <c r="B111" t="n">
-        <v>-0.0001294716138556806</v>
+        <v>-0.0001294716276750707</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.001810306910503989</v>
+        <v>-0.001810222675298734</v>
       </c>
       <c r="D111" t="n">
-        <v>0.003433478471448481</v>
+        <v>0.003433575573209335</v>
       </c>
     </row>
     <row r="112">
@@ -2007,13 +2007,13 @@
         <v>45245</v>
       </c>
       <c r="B112" t="n">
-        <v>0.01808076231826261</v>
+        <v>0.01808087099892353</v>
       </c>
       <c r="C112" t="n">
-        <v>0.01047830510784631</v>
+        <v>0.01047805063613372</v>
       </c>
       <c r="D112" t="n">
-        <v>0.02690119579729267</v>
+        <v>0.02690109935891627</v>
       </c>
     </row>
     <row r="113">
@@ -2024,10 +2024,10 @@
         <v>0.00180350025846665</v>
       </c>
       <c r="C113" t="n">
-        <v>0.002625569424953955</v>
+        <v>0.002625653005829509</v>
       </c>
       <c r="D113" t="n">
-        <v>0.02438848476976951</v>
+        <v>0.02438848706014185</v>
       </c>
     </row>
     <row r="114">
@@ -2041,7 +2041,7 @@
         <v>-0.002154668892700551</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.005086836601314371</v>
+        <v>-0.00508674539146059</v>
       </c>
     </row>
     <row r="115">
@@ -2055,7 +2055,7 @@
         <v>6.640861462203773e-05</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.0006609554635068626</v>
+        <v>-0.0006608633185934965</v>
       </c>
     </row>
     <row r="116">
@@ -2066,10 +2066,10 @@
         <v>0.01257788610447208</v>
       </c>
       <c r="C116" t="n">
-        <v>0.008470660339409575</v>
+        <v>0.008470743657106983</v>
       </c>
       <c r="D116" t="n">
-        <v>0.001670677928812925</v>
+        <v>0.001670585568917859</v>
       </c>
     </row>
     <row r="117">
@@ -2080,10 +2080,10 @@
         <v>0.00390938015463238</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.003557360223577222</v>
+        <v>-0.003557359929675652</v>
       </c>
       <c r="D117" t="n">
-        <v>0.01306476590192562</v>
+        <v>0.01306458179778969</v>
       </c>
     </row>
     <row r="118">
@@ -2094,10 +2094,10 @@
         <v>0.003056745698208463</v>
       </c>
       <c r="C118" t="n">
-        <v>0.005784993293596496</v>
+        <v>0.005784909901133117</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.005865150070261338</v>
+        <v>-0.00586496940622383</v>
       </c>
     </row>
     <row r="119">
@@ -2111,7 +2111,7 @@
         <v>0.00709905245670206</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.008176735204939778</v>
+        <v>-0.008176552402900827</v>
       </c>
     </row>
     <row r="120">
@@ -2125,7 +2125,7 @@
         <v>-0.002251744715390358</v>
       </c>
       <c r="D120" t="n">
-        <v>0.003687379721042605</v>
+        <v>0.003687010423321979</v>
       </c>
     </row>
     <row r="121">
@@ -2139,7 +2139,7 @@
         <v>0.0199521873389974</v>
       </c>
       <c r="D121" t="n">
-        <v>0.01171397485160242</v>
+        <v>0.01171416063466157</v>
       </c>
     </row>
     <row r="122">
@@ -2150,10 +2150,10 @@
         <v>-0.009684649125605738</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.0002244933054986742</v>
+        <v>-0.0002244128707779014</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.003048753095921897</v>
+        <v>-0.003048662343016706</v>
       </c>
     </row>
     <row r="123">
@@ -2161,13 +2161,13 @@
         <v>45261</v>
       </c>
       <c r="B123" t="n">
-        <v>0.007087507058043396</v>
+        <v>0.007087403129556913</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.002181155367918186</v>
+        <v>-0.002181155192438222</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.001958428767365072</v>
+        <v>-0.001958519619514654</v>
       </c>
     </row>
     <row r="124">
@@ -2175,13 +2175,13 @@
         <v>45264</v>
       </c>
       <c r="B124" t="n">
-        <v>0.01081732394088575</v>
+        <v>0.01081732505720212</v>
       </c>
       <c r="C124" t="n">
-        <v>0.03471780780388523</v>
+        <v>0.03471772437599685</v>
       </c>
       <c r="D124" t="n">
-        <v>0.008297105854408571</v>
+        <v>0.0082970146453476</v>
       </c>
     </row>
     <row r="125">
@@ -2189,13 +2189,13 @@
         <v>45265</v>
       </c>
       <c r="B125" t="n">
-        <v>0.007251440757797489</v>
+        <v>0.007251543590833576</v>
       </c>
       <c r="C125" t="n">
-        <v>0.008885284329332332</v>
+        <v>0.008885206406013646</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.007102169548026782</v>
+        <v>-0.007102079731953315</v>
       </c>
     </row>
     <row r="126">
@@ -2203,10 +2203,10 @@
         <v>45266</v>
       </c>
       <c r="B126" t="n">
-        <v>0.009578608332192262</v>
+        <v>0.009578506974475154</v>
       </c>
       <c r="C126" t="n">
-        <v>0.002525110728959445</v>
+        <v>0.002525188161042857</v>
       </c>
       <c r="D126" t="n">
         <v>0.01399645672239713</v>
@@ -2217,13 +2217,13 @@
         <v>45267</v>
       </c>
       <c r="B127" t="n">
-        <v>-0.001645692255949682</v>
+        <v>-0.001645592025098175</v>
       </c>
       <c r="C127" t="n">
         <v>0.001627908123423394</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.005697621732149272</v>
+        <v>-0.005697711580159637</v>
       </c>
     </row>
     <row r="128">
@@ -2231,13 +2231,13 @@
         <v>45268</v>
       </c>
       <c r="B128" t="n">
-        <v>-0.0005291549068306978</v>
+        <v>-0.0005290543452748375</v>
       </c>
       <c r="C128" t="n">
-        <v>0.01395325797797664</v>
+        <v>0.01395318106068633</v>
       </c>
       <c r="D128" t="n">
-        <v>0.01722487873981393</v>
+        <v>0.01722506102204746</v>
       </c>
     </row>
     <row r="129">
@@ -2245,13 +2245,13 @@
         <v>45271</v>
       </c>
       <c r="B129" t="n">
-        <v>0.001465957587241107</v>
+        <v>0.001465856824957479</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.001330715293986318</v>
+        <v>-0.001330715394932791</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.00177709877986465</v>
+        <v>-0.001777365120168906</v>
       </c>
     </row>
     <row r="130">
@@ -2259,13 +2259,13 @@
         <v>45272</v>
       </c>
       <c r="B130" t="n">
-        <v>-0.01435339207468034</v>
+        <v>-0.01435329160716481</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.009933427229889991</v>
+        <v>-0.009933352024532605</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.008364163480867437</v>
+        <v>-0.008363897996859548</v>
       </c>
     </row>
     <row r="131">
@@ -2273,13 +2273,13 @@
         <v>45273</v>
       </c>
       <c r="B131" t="n">
-        <v>0.004084051943815892</v>
+        <v>0.004083949596971781</v>
       </c>
       <c r="C131" t="n">
         <v>-0.002263529350387095</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.01832592995963966</v>
+        <v>-0.01832610779800525</v>
       </c>
     </row>
     <row r="132">
@@ -2293,7 +2293,7 @@
         <v>0.01180331494312736</v>
       </c>
       <c r="D132" t="n">
-        <v>0.03619739078207984</v>
+        <v>0.0361973940911291</v>
       </c>
     </row>
     <row r="133">
@@ -2304,10 +2304,10 @@
         <v>0.01276309820661847</v>
       </c>
       <c r="C133" t="n">
-        <v>0.003878458107514859</v>
+        <v>0.003878382108492451</v>
       </c>
       <c r="D133" t="n">
-        <v>0.05125043339711888</v>
+        <v>0.05125043791860318</v>
       </c>
     </row>
     <row r="134">
@@ -2318,10 +2318,10 @@
         <v>0.01017784143782818</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.0005131312155554069</v>
+        <v>-0.0005131312544022215</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.008901384356736153</v>
+        <v>-0.008901469026046605</v>
       </c>
     </row>
     <row r="135">
@@ -2332,10 +2332,10 @@
         <v>0.01471649200355785</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.001691218035255737</v>
+        <v>-0.001691066674806674</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.003867492201339195</v>
+        <v>-0.003867323504253006</v>
       </c>
     </row>
     <row r="136">
@@ -2346,7 +2346,7 @@
         <v>-0.01209885670290722</v>
       </c>
       <c r="C136" t="n">
-        <v>0.002480578325129379</v>
+        <v>0.002480426391761048</v>
       </c>
       <c r="D136" t="n">
         <v>-0.01405375327502123</v>
@@ -2357,13 +2357,13 @@
         <v>45281</v>
       </c>
       <c r="B137" t="n">
-        <v>0.01400800518896128</v>
+        <v>0.01400790741685509</v>
       </c>
       <c r="C137" t="n">
-        <v>0.01792383607116954</v>
+        <v>0.0179239887974314</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.0002603736258071088</v>
+        <v>-0.000260287409374671</v>
       </c>
     </row>
     <row r="138">
@@ -2371,13 +2371,13 @@
         <v>45282</v>
       </c>
       <c r="B138" t="n">
-        <v>0.000975495649561342</v>
+        <v>0.0009754957436201028</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.009396998715268889</v>
+        <v>-0.00939699801658167</v>
       </c>
       <c r="D138" t="n">
-        <v>0.01751296192027096</v>
+        <v>0.017513046648852</v>
       </c>
     </row>
     <row r="139">
@@ -2385,13 +2385,13 @@
         <v>45286</v>
       </c>
       <c r="B139" t="n">
-        <v>0.005068077029222406</v>
+        <v>0.005068173844893886</v>
       </c>
       <c r="C139" t="n">
-        <v>0.0069425919840711</v>
+        <v>0.006942516405500365</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.01212490588003567</v>
+        <v>-0.01212498857932187</v>
       </c>
     </row>
     <row r="140">
@@ -2402,10 +2402,10 @@
         <v>0.003413499193204217</v>
       </c>
       <c r="C140" t="n">
-        <v>0.01239271926252528</v>
+        <v>0.01239264472254309</v>
       </c>
       <c r="D140" t="n">
-        <v>0.01499402052881704</v>
+        <v>0.01499393344757771</v>
       </c>
     </row>
     <row r="141">
@@ -2413,13 +2413,13 @@
         <v>45288</v>
       </c>
       <c r="B141" t="n">
-        <v>0.007228914051542468</v>
+        <v>0.007228818535851333</v>
       </c>
       <c r="C141" t="n">
-        <v>0.001144760940591683</v>
+        <v>0.001144834652419879</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.002839529997052503</v>
+        <v>-0.00283961452448378</v>
       </c>
     </row>
     <row r="142">
@@ -2427,13 +2427,13 @@
         <v>45289</v>
       </c>
       <c r="B142" t="n">
-        <v>-0.007906275927161754</v>
+        <v>-0.007906181846734306</v>
       </c>
       <c r="C142" t="n">
-        <v>0.002345665057268631</v>
+        <v>0.002345738600615821</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.0126388438440449</v>
+        <v>-0.01263876014727616</v>
       </c>
     </row>
     <row r="143">
@@ -2444,7 +2444,7 @@
         <v>0.002050317565037041</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.006523290453711583</v>
+        <v>-0.006523363346327082</v>
       </c>
       <c r="D143" t="n">
         <v>0.005476662648449926</v>
@@ -2458,10 +2458,10 @@
         <v>0.008281024461512132</v>
       </c>
       <c r="C144" t="n">
-        <v>0.0005888300280418868</v>
+        <v>0.0005889038810493741</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.01092594012523329</v>
+        <v>-0.01092602551082356</v>
       </c>
     </row>
     <row r="145">
@@ -2469,13 +2469,13 @@
         <v>45294</v>
       </c>
       <c r="B145" t="n">
-        <v>-0.01087411457422738</v>
+        <v>-0.01087401996734927</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.01541992132935721</v>
+        <v>-0.01541984638167915</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.02893638239796925</v>
+        <v>-0.02893621223837084</v>
       </c>
     </row>
     <row r="146">
@@ -2483,13 +2483,13 @@
         <v>45295</v>
       </c>
       <c r="B146" t="n">
-        <v>0.005167804929185005</v>
+        <v>0.00516761314101033</v>
       </c>
       <c r="C146" t="n">
-        <v>0.010729888178449</v>
+        <v>0.01072981160420916</v>
       </c>
       <c r="D146" t="n">
-        <v>0.0152348372172828</v>
+        <v>0.01523483586288621</v>
       </c>
     </row>
     <row r="147">
@@ -2497,13 +2497,13 @@
         <v>45296</v>
       </c>
       <c r="B147" t="n">
-        <v>0.004255436169599225</v>
+        <v>0.004255531729745909</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.005115779235145945</v>
+        <v>-0.005115778855710351</v>
       </c>
       <c r="D147" t="n">
-        <v>0.01312229866062431</v>
+        <v>0.01312229751154104</v>
       </c>
     </row>
     <row r="148">
@@ -2514,10 +2514,10 @@
         <v>-0.00780367992130282</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.01114605485094444</v>
+        <v>-0.01114612857105157</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.00636198910736463</v>
+        <v>-0.006361988557478826</v>
       </c>
     </row>
     <row r="149">
@@ -2525,13 +2525,13 @@
         <v>45300</v>
       </c>
       <c r="B149" t="n">
-        <v>-0.00264756518354381</v>
+        <v>-0.002647660680773045</v>
       </c>
       <c r="C149" t="n">
         <v>-0.00778506460588857</v>
       </c>
       <c r="D149" t="n">
-        <v>0.004268511103730832</v>
+        <v>0.004268423746006</v>
       </c>
     </row>
     <row r="150">
@@ -2539,7 +2539,7 @@
         <v>45301</v>
       </c>
       <c r="B150" t="n">
-        <v>0.0269716416961514</v>
+        <v>0.02697154852796158</v>
       </c>
       <c r="C150" t="n">
         <v>0.003302065352293937</v>
@@ -2553,7 +2553,7 @@
         <v>45302</v>
       </c>
       <c r="B151" t="n">
-        <v>0.02630075884786409</v>
+        <v>0.0263010434602946</v>
       </c>
       <c r="C151" t="n">
         <v>-0.004196962325640263</v>
@@ -2567,10 +2567,10 @@
         <v>45303</v>
       </c>
       <c r="B152" t="n">
-        <v>0.007960167005252261</v>
+        <v>0.007959984588772118</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.004730207726976854</v>
+        <v>-0.004730283779000755</v>
       </c>
       <c r="D152" t="n">
         <v>0.07934008248304081</v>
@@ -2581,13 +2581,13 @@
         <v>45306</v>
       </c>
       <c r="B153" t="n">
-        <v>0.01707119668180246</v>
+        <v>0.01707128834965177</v>
       </c>
       <c r="C153" t="n">
-        <v>0.01925420906436504</v>
+        <v>0.01925443977609009</v>
       </c>
       <c r="D153" t="n">
-        <v>0.02439938090056559</v>
+        <v>0.02439929876574354</v>
       </c>
     </row>
     <row r="154">
@@ -2598,10 +2598,10 @@
         <v>-0.01398721867382313</v>
       </c>
       <c r="C154" t="n">
-        <v>0.003796030354148439</v>
+        <v>0.003795954814995506</v>
       </c>
       <c r="D154" t="n">
-        <v>-0.01243873459379841</v>
+        <v>-0.01243857523407321</v>
       </c>
     </row>
     <row r="155">
@@ -2609,13 +2609,13 @@
         <v>45308</v>
       </c>
       <c r="B155" t="n">
-        <v>-0.009493609453543828</v>
+        <v>-0.009493519580024645</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.08435815003093883</v>
+        <v>-0.08435821841699642</v>
       </c>
       <c r="D155" t="n">
-        <v>0.005301602309842446</v>
+        <v>0.005301601879413864</v>
       </c>
     </row>
     <row r="156">
@@ -2623,13 +2623,13 @@
         <v>45309</v>
       </c>
       <c r="B156" t="n">
-        <v>0.004682194133715178</v>
+        <v>0.004682012239050959</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.03339832075673621</v>
+        <v>-0.03339840232408209</v>
       </c>
       <c r="D156" t="n">
-        <v>0.00146329475443685</v>
+        <v>0.001463294636260715</v>
       </c>
     </row>
     <row r="157">
@@ -2637,13 +2637,13 @@
         <v>45310</v>
       </c>
       <c r="B157" t="n">
-        <v>-0.0003654929169152332</v>
+        <v>-0.0003654929499237181</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.01042964887706699</v>
+        <v>-0.01042956537148687</v>
       </c>
       <c r="D157" t="n">
-        <v>0.01010592357535423</v>
+        <v>0.01010584211816168</v>
       </c>
     </row>
     <row r="158">
@@ -2651,13 +2651,13 @@
         <v>45314</v>
       </c>
       <c r="B158" t="n">
-        <v>-0.02842888726207504</v>
+        <v>-0.02842879948539434</v>
       </c>
       <c r="C158" t="n">
         <v>-0.02944275467145385</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.01027609644374705</v>
+        <v>-0.01027593677289884</v>
       </c>
     </row>
     <row r="159">
@@ -2665,13 +2665,13 @@
         <v>45315</v>
       </c>
       <c r="B159" t="n">
-        <v>0.01151608596651599</v>
+        <v>0.01151617895516277</v>
       </c>
       <c r="C159" t="n">
         <v>0.02000212977424387</v>
       </c>
       <c r="D159" t="n">
-        <v>0.02024795895024067</v>
+        <v>0.02024779435501367</v>
       </c>
     </row>
     <row r="160">
@@ -2679,13 +2679,13 @@
         <v>45316</v>
       </c>
       <c r="B160" t="n">
-        <v>0.006845933178860397</v>
+        <v>0.006845748689584319</v>
       </c>
       <c r="C160" t="n">
         <v>-0.01442406338039448</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.003760337449192797</v>
+        <v>-0.003760258385728021</v>
       </c>
     </row>
     <row r="161">
@@ -2693,13 +2693,13 @@
         <v>45320</v>
       </c>
       <c r="B161" t="n">
-        <v>0.0701919247384617</v>
+        <v>0.07019211375715795</v>
       </c>
       <c r="C161" t="n">
         <v>0.01376396198778651</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.007489064328051631</v>
+        <v>-0.007489063733705281</v>
       </c>
     </row>
     <row r="162">
@@ -2707,13 +2707,13 @@
         <v>45321</v>
       </c>
       <c r="B162" t="n">
-        <v>-0.02791688614306631</v>
+        <v>-0.02791696907767616</v>
       </c>
       <c r="C162" t="n">
         <v>-0.007115075607969978</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.003108792960897611</v>
+        <v>-0.003108872673033169</v>
       </c>
     </row>
     <row r="163">
@@ -2721,7 +2721,7 @@
         <v>45322</v>
       </c>
       <c r="B163" t="n">
-        <v>0.01349796934524927</v>
+        <v>0.01349788157869569</v>
       </c>
       <c r="C163" t="n">
         <v>0.01263588484319866</v>
@@ -2735,13 +2735,13 @@
         <v>45323</v>
       </c>
       <c r="B164" t="n">
-        <v>1.749272752848974e-05</v>
+        <v>1.757932671186957e-05</v>
       </c>
       <c r="C164" t="n">
         <v>0.002598144701739802</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.002318041332036724</v>
+        <v>-0.002317961578335304</v>
       </c>
     </row>
     <row r="165">
@@ -2749,13 +2749,13 @@
         <v>45324</v>
       </c>
       <c r="B165" t="n">
-        <v>0.02176420943174051</v>
+        <v>0.02176429602788676</v>
       </c>
       <c r="C165" t="n">
         <v>-0.01377562033952118</v>
       </c>
       <c r="D165" t="n">
-        <v>0.02190640453708204</v>
+        <v>0.02190624290791221</v>
       </c>
     </row>
     <row r="166">
@@ -2763,13 +2763,13 @@
         <v>45327</v>
       </c>
       <c r="B166" t="n">
-        <v>-0.0128112205687374</v>
+        <v>-0.01281130423455379</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.0008989370498647675</v>
+        <v>-0.0008990237696264725</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.003631847330367699</v>
+        <v>-0.003631847614470329</v>
       </c>
     </row>
     <row r="167">
@@ -2780,10 +2780,10 @@
         <v>-0.007800377506025469</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.0005191375667681353</v>
+        <v>-0.0005190508140331396</v>
       </c>
       <c r="D167" t="n">
-        <v>0.0250413966265135</v>
+        <v>0.02504155561354859</v>
       </c>
     </row>
     <row r="168">
@@ -2791,13 +2791,13 @@
         <v>45329</v>
       </c>
       <c r="B168" t="n">
-        <v>0.01005047344215071</v>
+        <v>0.01005038691575533</v>
       </c>
       <c r="C168" t="n">
         <v>-0.009798567961059712</v>
       </c>
       <c r="D168" t="n">
-        <v>-0.0206422972241721</v>
+        <v>-0.02064244882815747</v>
       </c>
     </row>
     <row r="169">
@@ -2805,13 +2805,13 @@
         <v>45330</v>
       </c>
       <c r="B169" t="n">
-        <v>0.005529874015297365</v>
+        <v>0.00552996015444096</v>
       </c>
       <c r="C169" t="n">
         <v>-0.01881177690061908</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.0009743014501825131</v>
+        <v>-0.0009741451125850897</v>
       </c>
     </row>
     <row r="170">
@@ -2825,7 +2825,7 @@
         <v>0.0003919474945885959</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.01344466347203521</v>
+        <v>-0.01344481898585737</v>
       </c>
     </row>
     <row r="171">
@@ -2836,10 +2836,10 @@
         <v>-0.005750482688546277</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.009689327515424284</v>
+        <v>-0.009689238166751046</v>
       </c>
       <c r="D171" t="n">
-        <v>0.006439490271492154</v>
+        <v>0.006439728832474234</v>
       </c>
     </row>
     <row r="172">
@@ -2847,13 +2847,13 @@
         <v>45335</v>
       </c>
       <c r="B172" t="n">
-        <v>0.00877883789938716</v>
+        <v>0.008778752835601367</v>
       </c>
       <c r="C172" t="n">
-        <v>0.003201468395288787</v>
+        <v>0.003201287660715035</v>
       </c>
       <c r="D172" t="n">
-        <v>0.002648706812951707</v>
+        <v>0.002648548710731724</v>
       </c>
     </row>
     <row r="173">
@@ -2861,10 +2861,10 @@
         <v>45336</v>
       </c>
       <c r="B173" t="n">
-        <v>0.01110852800051143</v>
+        <v>0.0111085289372217</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.007458125388743797</v>
+        <v>-0.007457946189577291</v>
       </c>
       <c r="D173" t="n">
         <v>-0.01089309131775906</v>
@@ -2875,13 +2875,13 @@
         <v>45337</v>
       </c>
       <c r="B174" t="n">
-        <v>-0.007273728644503485</v>
+        <v>-0.007273645854000144</v>
       </c>
       <c r="C174" t="n">
-        <v>0.02167553745757145</v>
+        <v>0.02167544488280915</v>
       </c>
       <c r="D174" t="n">
-        <v>0.006091609139130982</v>
+        <v>0.006091688639145776</v>
       </c>
     </row>
     <row r="175">
@@ -2889,13 +2889,13 @@
         <v>45338</v>
       </c>
       <c r="B175" t="n">
-        <v>-0.006817009904393712</v>
+        <v>-0.006816925896236836</v>
       </c>
       <c r="C175" t="n">
         <v>0.004137046230407337</v>
       </c>
       <c r="D175" t="n">
-        <v>0.01509240679630053</v>
+        <v>0.01509232658506088</v>
       </c>
     </row>
     <row r="176">
@@ -2903,13 +2903,13 @@
         <v>45341</v>
       </c>
       <c r="B176" t="n">
-        <v>0.009191658012939641</v>
+        <v>0.009191572650700364</v>
       </c>
       <c r="C176" t="n">
         <v>-0.001971986956816996</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.001116591661557531</v>
+        <v>-0.001116513817743914</v>
       </c>
     </row>
     <row r="177">
@@ -2923,7 +2923,7 @@
         <v>0.02625074382137105</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.008530542495214233</v>
+        <v>-0.008530853553719631</v>
       </c>
     </row>
     <row r="178">
@@ -2934,10 +2934,10 @@
         <v>-0.002260342131848447</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.01041729994602625</v>
+        <v>-0.01041738617981136</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.01762360002166252</v>
+        <v>-0.01762336837329614</v>
       </c>
     </row>
     <row r="179">
@@ -2948,7 +2948,7 @@
         <v>0.009572788452789194</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.01361918090414604</v>
+        <v>-0.0136190949493703</v>
       </c>
       <c r="D179" t="n">
         <v>0.015583906628579</v>
@@ -2962,7 +2962,7 @@
         <v>0.008014184592298523</v>
       </c>
       <c r="C180" t="n">
-        <v>0.0007397105755377886</v>
+        <v>0.000739622230789605</v>
       </c>
       <c r="D180" t="n">
         <v>-0.002676438993664654</v>
@@ -2973,13 +2973,13 @@
         <v>45348</v>
       </c>
       <c r="B181" t="n">
-        <v>-0.004218038408665636</v>
+        <v>-0.004217955695542952</v>
       </c>
       <c r="C181" t="n">
-        <v>0.001196627901690173</v>
+        <v>0.001196804566237164</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.009959149263848666</v>
+        <v>-0.009959070268748427</v>
       </c>
     </row>
     <row r="182">
@@ -2987,13 +2987,13 @@
         <v>45349</v>
       </c>
       <c r="B182" t="n">
-        <v>-0.001126091703419485</v>
+        <v>-0.001126091609882418</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.001511565775110579</v>
+        <v>-0.001511653815757574</v>
       </c>
       <c r="D182" t="n">
-        <v>0.002078203518089072</v>
+        <v>0.002078123562538225</v>
       </c>
     </row>
     <row r="183">
@@ -3001,13 +3001,13 @@
         <v>45350</v>
       </c>
       <c r="B183" t="n">
-        <v>-0.02021009316342781</v>
+        <v>-0.02021009148281461</v>
       </c>
       <c r="C183" t="n">
         <v>-0.007569711862609241</v>
       </c>
       <c r="D183" t="n">
-        <v>0.004598380792844248</v>
+        <v>0.004598460417106986</v>
       </c>
     </row>
     <row r="184">
@@ -3015,13 +3015,13 @@
         <v>45351</v>
       </c>
       <c r="B184" t="n">
-        <v>0.003555305238528872</v>
+        <v>0.003555304936781578</v>
       </c>
       <c r="C184" t="n">
         <v>-0.004257116943339634</v>
       </c>
       <c r="D184" t="n">
-        <v>0.0015857507372945</v>
+        <v>0.001585592092028909</v>
       </c>
     </row>
     <row r="185">
@@ -3029,13 +3029,13 @@
         <v>45352</v>
       </c>
       <c r="B185" t="n">
-        <v>0.02144366989894175</v>
+        <v>0.02144358351368969</v>
       </c>
       <c r="C185" t="n">
         <v>0.01948838096266181</v>
       </c>
       <c r="D185" t="n">
-        <v>-0.01147028063558142</v>
+        <v>-0.01147028154327423</v>
       </c>
     </row>
     <row r="186">
@@ -3046,10 +3046,10 @@
         <v>0.01023709706985643</v>
       </c>
       <c r="C186" t="n">
-        <v>0.001362919320768485</v>
+        <v>0.001362831667586883</v>
       </c>
       <c r="D186" t="n">
-        <v>-0.01057598038136542</v>
+        <v>-0.01057582112291944</v>
       </c>
     </row>
     <row r="187">
@@ -3060,10 +3060,10 @@
         <v>-0.004776469739736444</v>
       </c>
       <c r="C187" t="n">
-        <v>0.005688476724916347</v>
+        <v>0.005688652290626095</v>
       </c>
       <c r="D187" t="n">
-        <v>-0.01875145027979674</v>
+        <v>-0.01875152967086136</v>
       </c>
     </row>
     <row r="188">
@@ -3071,10 +3071,10 @@
         <v>45357</v>
       </c>
       <c r="B188" t="n">
-        <v>0.001866476711245735</v>
+        <v>0.001866394360629853</v>
       </c>
       <c r="C188" t="n">
-        <v>0.001214538885176308</v>
+        <v>0.001214538779464203</v>
       </c>
       <c r="D188" t="n">
         <v>0.006878342390394643</v>
@@ -3085,10 +3085,10 @@
         <v>45358</v>
       </c>
       <c r="B189" t="n">
-        <v>-0.01601793214046021</v>
+        <v>-0.01601785125988586</v>
       </c>
       <c r="C189" t="n">
-        <v>0.002426218072920872</v>
+        <v>0.002426130928831371</v>
       </c>
       <c r="D189" t="n">
         <v>-0.0006801054298536391</v>
@@ -3099,7 +3099,7 @@
         <v>45362</v>
       </c>
       <c r="B190" t="n">
-        <v>-0.008333895107949685</v>
+        <v>-0.008333811572690752</v>
       </c>
       <c r="C190" t="n">
         <v>-0.01265458658952046</v>
@@ -3113,13 +3113,13 @@
         <v>45363</v>
       </c>
       <c r="B191" t="n">
-        <v>0.006017406118389745</v>
+        <v>0.006017405611499882</v>
       </c>
       <c r="C191" t="n">
-        <v>0.02223700375500326</v>
+        <v>0.02223691592072674</v>
       </c>
       <c r="D191" t="n">
-        <v>0.007715886803536298</v>
+        <v>0.007715804045242081</v>
       </c>
     </row>
     <row r="192">
@@ -3127,13 +3127,13 @@
         <v>45364</v>
       </c>
       <c r="B192" t="n">
-        <v>-0.02931356509964023</v>
+        <v>-0.02931364637853384</v>
       </c>
       <c r="C192" t="n">
-        <v>0.0005823041906569681</v>
+        <v>0.00058239016429118</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.0009610224187920346</v>
+        <v>-0.0009609403730790333</v>
       </c>
     </row>
     <row r="193">
@@ -3141,13 +3141,13 @@
         <v>45365</v>
       </c>
       <c r="B193" t="n">
-        <v>-0.0004887609143089389</v>
+        <v>-0.0004888471763835334</v>
       </c>
       <c r="C193" t="n">
         <v>-0.003389516414908256</v>
       </c>
       <c r="D193" t="n">
-        <v>0.02600224103534488</v>
+        <v>0.02600232323897433</v>
       </c>
     </row>
     <row r="194">
@@ -3155,13 +3155,13 @@
         <v>45366</v>
       </c>
       <c r="B194" t="n">
-        <v>-0.009256217833324754</v>
+        <v>-0.00925613232791167</v>
       </c>
       <c r="C194" t="n">
         <v>-0.001923734267552768</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.01167361096199826</v>
+        <v>-0.01167369014702002</v>
       </c>
     </row>
     <row r="195">
@@ -3169,13 +3169,13 @@
         <v>45369</v>
       </c>
       <c r="B195" t="n">
-        <v>0.01498345378257193</v>
+        <v>0.01498354089314291</v>
       </c>
       <c r="C195" t="n">
         <v>-0.004543379837069539</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.01918596586915178</v>
+        <v>-0.01918604693581394</v>
       </c>
     </row>
     <row r="196">
@@ -3183,13 +3183,13 @@
         <v>45370</v>
       </c>
       <c r="B196" t="n">
-        <v>-0.009882018608837861</v>
+        <v>-0.009882103585331814</v>
       </c>
       <c r="C196" t="n">
-        <v>0.002282014812759137</v>
+        <v>0.002281928087003227</v>
       </c>
       <c r="D196" t="n">
-        <v>-0.02570755024978388</v>
+        <v>-0.02570738706970421</v>
       </c>
     </row>
     <row r="197">
@@ -3200,10 +3200,10 @@
         <v>0.01298016404591817</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.01262638214893541</v>
+        <v>-0.01262621018486598</v>
       </c>
       <c r="D197" t="n">
-        <v>-0.004162854117459869</v>
+        <v>-0.004162853764311247</v>
       </c>
     </row>
     <row r="198">
@@ -3214,10 +3214,10 @@
         <v>0.005004333289521323</v>
       </c>
       <c r="C198" t="n">
-        <v>0.01027220159931774</v>
+        <v>0.01027211306431552</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.0001607495854543117</v>
+        <v>-0.0001608347596627757</v>
       </c>
     </row>
     <row r="199">
@@ -3231,7 +3231,7 @@
         <v>-0.002005949407396956</v>
       </c>
       <c r="D199" t="n">
-        <v>-0.02949108740082962</v>
+        <v>-0.02949125780404105</v>
       </c>
     </row>
     <row r="200">
@@ -3239,13 +3239,13 @@
         <v>45377</v>
       </c>
       <c r="B200" t="n">
-        <v>-0.009243953128739935</v>
+        <v>-0.00924386822134371</v>
       </c>
       <c r="C200" t="n">
         <v>-0.01209404678732406</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.01073670838624552</v>
+        <v>-0.0107365346900854</v>
       </c>
     </row>
     <row r="201">
@@ -3253,13 +3253,13 @@
         <v>45378</v>
       </c>
       <c r="B201" t="n">
-        <v>0.03556884737295585</v>
+        <v>0.03556867292553645</v>
       </c>
       <c r="C201" t="n">
         <v>0.010733824983576</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.005895583025008921</v>
+        <v>-0.005895671768469057</v>
       </c>
     </row>
     <row r="202">
@@ -3267,13 +3267,13 @@
         <v>45379</v>
       </c>
       <c r="B202" t="n">
-        <v>-0.004689041202339594</v>
+        <v>-0.0046890415903863</v>
       </c>
       <c r="C202" t="n">
-        <v>0.004997589210736564</v>
+        <v>0.004997502162920497</v>
       </c>
       <c r="D202" t="n">
-        <v>0.009569807254096174</v>
+        <v>0.009569808108390587</v>
       </c>
     </row>
     <row r="203">
@@ -3281,13 +3281,13 @@
         <v>45383</v>
       </c>
       <c r="B203" t="n">
-        <v>-0.0007234527913171362</v>
+        <v>-0.0007234528514693528</v>
       </c>
       <c r="C203" t="n">
-        <v>0.01560879353083333</v>
+        <v>0.01560888149774575</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.001735754500118203</v>
+        <v>-0.001735577806462385</v>
       </c>
     </row>
     <row r="204">
@@ -3295,13 +3295,13 @@
         <v>45384</v>
       </c>
       <c r="B204" t="n">
-        <v>0.001464760747007965</v>
+        <v>0.001464844075024008</v>
       </c>
       <c r="C204" t="n">
-        <v>0.006562330498500746</v>
+        <v>0.0065624157822739</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.008425562242256657</v>
+        <v>-0.00842556149594309</v>
       </c>
     </row>
     <row r="205">
@@ -3312,10 +3312,10 @@
         <v>-0.01032307464911986</v>
       </c>
       <c r="C205" t="n">
-        <v>0.001452657473535179</v>
+        <v>0.001452572622700155</v>
       </c>
       <c r="D205" t="n">
-        <v>-0.001483502720812102</v>
+        <v>-0.001483681248203861</v>
       </c>
     </row>
     <row r="206">
@@ -3329,7 +3329,7 @@
         <v>0.03056062902697976</v>
       </c>
       <c r="D206" t="n">
-        <v>0.004086029104894529</v>
+        <v>0.004086029470441677</v>
       </c>
     </row>
     <row r="207">
@@ -3343,7 +3343,7 @@
         <v>0.01436892674643553</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.005112033499656721</v>
+        <v>-0.005112033955131934</v>
       </c>
     </row>
     <row r="208">
@@ -3354,10 +3354,10 @@
         <v>0.01772136582839878</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.001903787779338306</v>
+        <v>-0.001903868712373247</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.001622673111028594</v>
+        <v>-0.001622494143456166</v>
       </c>
     </row>
     <row r="209">
@@ -3368,10 +3368,10 @@
         <v>-0.01502370665519792</v>
       </c>
       <c r="C209" t="n">
-        <v>0.00126082810839856</v>
+        <v>0.001260990385465233</v>
       </c>
       <c r="D209" t="n">
-        <v>0.01229087773761517</v>
+        <v>0.01229087663509909</v>
       </c>
     </row>
     <row r="210">
@@ -3382,10 +3382,10 @@
         <v>0.01088032252948357</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.00787833092537038</v>
+        <v>-0.007878411272634445</v>
       </c>
       <c r="D210" t="n">
-        <v>0.007994209680902475</v>
+        <v>0.007994120359654744</v>
       </c>
     </row>
     <row r="211">
@@ -3410,7 +3410,7 @@
         <v>-0.001584751223950853</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.01596505187091724</v>
+        <v>-0.01596496930744018</v>
       </c>
       <c r="D212" t="n">
         <v>-0.01118023737785934</v>
@@ -3424,7 +3424,7 @@
         <v>0.0006315330845154676</v>
       </c>
       <c r="C213" t="n">
-        <v>0.009734509116311907</v>
+        <v>0.009734424396571795</v>
       </c>
       <c r="D213" t="n">
         <v>-0.03657678243446849</v>
@@ -3438,7 +3438,7 @@
         <v>-0.0009722404490967174</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.009640662004145262</v>
+        <v>-0.009640578910032893</v>
       </c>
       <c r="D214" t="n">
         <v>0.003393680943233113</v>
@@ -3449,10 +3449,10 @@
         <v>45401</v>
       </c>
       <c r="B215" t="n">
-        <v>0.003961000316043073</v>
+        <v>0.003960915947892163</v>
       </c>
       <c r="C215" t="n">
-        <v>0.02448666890519857</v>
+        <v>0.02448658294770811</v>
       </c>
       <c r="D215" t="n">
         <v>-0.005636849154855295</v>
@@ -3463,13 +3463,13 @@
         <v>45404</v>
       </c>
       <c r="B216" t="n">
-        <v>0.006614921658523842</v>
+        <v>0.006615006249704791</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.01247316727722692</v>
+        <v>-0.01247308537963343</v>
       </c>
       <c r="D216" t="n">
-        <v>0.015234668465816</v>
+        <v>0.01523476232794607</v>
       </c>
     </row>
     <row r="217">
@@ -3480,10 +3480,10 @@
         <v>-0.01386962401486869</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.003041946434375165</v>
+        <v>-0.003041946182100408</v>
       </c>
       <c r="D217" t="n">
-        <v>0.006735431827328497</v>
+        <v>0.0067352462973711</v>
       </c>
     </row>
     <row r="218">
@@ -3491,13 +3491,13 @@
         <v>45406</v>
       </c>
       <c r="B218" t="n">
-        <v>-0.006270052120062264</v>
+        <v>-0.00626996746284525</v>
       </c>
       <c r="C218" t="n">
-        <v>0.002719652446152354</v>
+        <v>0.00271948584980608</v>
       </c>
       <c r="D218" t="n">
-        <v>-0.008076987184873707</v>
+        <v>-0.008076804256446191</v>
       </c>
     </row>
     <row r="219">
@@ -3505,13 +3505,13 @@
         <v>45407</v>
       </c>
       <c r="B219" t="n">
-        <v>0.006757890722983495</v>
+        <v>0.006757719764541203</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.0006284177734631191</v>
+        <v>-0.0006283348661474397</v>
       </c>
       <c r="D219" t="n">
-        <v>0.005381842313964436</v>
+        <v>0.005381656649972477</v>
       </c>
     </row>
     <row r="220">
@@ -3519,13 +3519,13 @@
         <v>45408</v>
       </c>
       <c r="B220" t="n">
-        <v>-0.005085633263730904</v>
+        <v>-0.005085633694074887</v>
       </c>
       <c r="C220" t="n">
         <v>-0.0006288129306849521</v>
       </c>
       <c r="D220" t="n">
-        <v>-0.00570047841179655</v>
+        <v>-0.005700386849457506</v>
       </c>
     </row>
     <row r="221">
@@ -3533,7 +3533,7 @@
         <v>45411</v>
       </c>
       <c r="B221" t="n">
-        <v>0.008588217363141082</v>
+        <v>0.008588388197732222</v>
       </c>
       <c r="C221" t="n">
         <v>0.01304808324790918</v>
@@ -3547,7 +3547,7 @@
         <v>45412</v>
       </c>
       <c r="B222" t="n">
-        <v>0.001348149172575308</v>
+        <v>0.001348064731056198</v>
       </c>
       <c r="C222" t="n">
         <v>-0.006145858426906181</v>
@@ -3564,7 +3564,7 @@
         <v>-0.0003067085032111283</v>
       </c>
       <c r="C223" t="n">
-        <v>0.007992863332201061</v>
+        <v>0.007992945833216192</v>
       </c>
       <c r="D223" t="n">
         <v>-0.004294239916644127</v>
@@ -3578,10 +3578,10 @@
         <v>-0.02219500329589563</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.0082558073391229</v>
+        <v>-0.008255888510229181</v>
       </c>
       <c r="D224" t="n">
-        <v>0.001308100210140717</v>
+        <v>0.001308006560354791</v>
       </c>
     </row>
     <row r="225">
@@ -3595,7 +3595,7 @@
         <v>0.002007167405733812</v>
       </c>
       <c r="D225" t="n">
-        <v>0.006778214353488243</v>
+        <v>0.006778214987437359</v>
       </c>
     </row>
     <row r="226">
@@ -3609,7 +3609,7 @@
         <v>-0.01083639716253415</v>
       </c>
       <c r="D226" t="n">
-        <v>0.01055448630231792</v>
+        <v>0.01055467307834701</v>
       </c>
     </row>
     <row r="227">
@@ -3617,13 +3617,13 @@
         <v>45420</v>
       </c>
       <c r="B227" t="n">
-        <v>0.01218370953242398</v>
+        <v>0.01218353322904409</v>
       </c>
       <c r="C227" t="n">
         <v>-0.015602721371197</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.009472762613006447</v>
+        <v>-0.009472761742199021</v>
       </c>
     </row>
     <row r="228">
@@ -3631,13 +3631,13 @@
         <v>45421</v>
       </c>
       <c r="B228" t="n">
-        <v>-0.01721842192697542</v>
+        <v>-0.01721825074486427</v>
       </c>
       <c r="C228" t="n">
         <v>-0.02370753859481822</v>
       </c>
       <c r="D228" t="n">
-        <v>0.008582573324213527</v>
+        <v>0.008582572527693788</v>
       </c>
     </row>
     <row r="229">
@@ -3648,10 +3648,10 @@
         <v>0.009540091317467692</v>
       </c>
       <c r="C229" t="n">
-        <v>0.006932757219380248</v>
+        <v>0.006932843858268756</v>
       </c>
       <c r="D229" t="n">
-        <v>-0.01017670190791542</v>
+        <v>-0.01017688500528502</v>
       </c>
     </row>
     <row r="230">
@@ -3659,13 +3659,13 @@
         <v>45425</v>
       </c>
       <c r="B230" t="n">
-        <v>-0.003357284131203619</v>
+        <v>-0.003357196352184899</v>
       </c>
       <c r="C230" t="n">
-        <v>0.01206623886396518</v>
+        <v>0.01206615178338732</v>
       </c>
       <c r="D230" t="n">
-        <v>-0.00101766556610916</v>
+        <v>-0.001017665660714373</v>
       </c>
     </row>
     <row r="231">
@@ -3673,13 +3673,13 @@
         <v>45426</v>
       </c>
       <c r="B231" t="n">
-        <v>0.01238682729967255</v>
+        <v>0.01238673813400348</v>
       </c>
       <c r="C231" t="n">
         <v>0.003916797365439262</v>
       </c>
       <c r="D231" t="n">
-        <v>0.0008781851894072989</v>
+        <v>0.0008781852711290394</v>
       </c>
     </row>
     <row r="232">
@@ -3687,13 +3687,13 @@
         <v>45427</v>
       </c>
       <c r="B232" t="n">
-        <v>-0.00267585657554914</v>
+        <v>-0.002675769578456499</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.01536665958983563</v>
+        <v>-0.01536674427468987</v>
       </c>
       <c r="D232" t="n">
-        <v>-0.003334119910423206</v>
+        <v>-0.003333934268368366</v>
       </c>
     </row>
     <row r="233">
@@ -3701,13 +3701,13 @@
         <v>45428</v>
       </c>
       <c r="B233" t="n">
-        <v>0.006407604267281597</v>
+        <v>0.006407516477841657</v>
       </c>
       <c r="C233" t="n">
-        <v>0.01511985433941421</v>
+        <v>0.01511994164631392</v>
       </c>
       <c r="D233" t="n">
-        <v>0.02352204867307583</v>
+        <v>0.02352195319173678</v>
       </c>
     </row>
     <row r="234">
@@ -3729,13 +3729,13 @@
         <v>45433</v>
       </c>
       <c r="B235" t="n">
-        <v>0.0002960990307985245</v>
+        <v>0.0002960129805134049</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.003620009146567127</v>
+        <v>-0.003619924643914252</v>
       </c>
       <c r="D235" t="n">
-        <v>-0.007027606363796735</v>
+        <v>-0.007027698078072353</v>
       </c>
     </row>
     <row r="236">
@@ -3743,13 +3743,13 @@
         <v>45434</v>
       </c>
       <c r="B236" t="n">
-        <v>0.01707721578627575</v>
+        <v>0.01707721725534017</v>
       </c>
       <c r="C236" t="n">
-        <v>0.0002741896457745252</v>
+        <v>0.0002741896225206819</v>
       </c>
       <c r="D236" t="n">
-        <v>0.01439880267517557</v>
+        <v>0.01439889636847513</v>
       </c>
     </row>
     <row r="237">
@@ -3757,10 +3757,10 @@
         <v>45435</v>
       </c>
       <c r="B237" t="n">
-        <v>0.01738947961730397</v>
+        <v>0.01738965024895833</v>
       </c>
       <c r="C237" t="n">
-        <v>0.02288928030067305</v>
+        <v>0.02288919357356312</v>
       </c>
       <c r="D237" t="n">
         <v>0.01209784919841184</v>
@@ -3771,10 +3771,10 @@
         <v>45436</v>
       </c>
       <c r="B238" t="n">
-        <v>-0.00390301001815252</v>
+        <v>-0.003903092828415056</v>
       </c>
       <c r="C238" t="n">
-        <v>0.01648134588098138</v>
+        <v>0.01648126299183716</v>
       </c>
       <c r="D238" t="n">
         <v>-0.004958003476747019</v>
@@ -3788,10 +3788,10 @@
         <v>-0.009457826453420637</v>
       </c>
       <c r="C239" t="n">
-        <v>0.006920657038791633</v>
+        <v>0.00692073914831437</v>
       </c>
       <c r="D239" t="n">
-        <v>0.004266100517410942</v>
+        <v>0.004266010105192786</v>
       </c>
     </row>
     <row r="240">
@@ -3799,13 +3799,13 @@
         <v>45440</v>
       </c>
       <c r="B240" t="n">
-        <v>-0.006854253936252164</v>
+        <v>-0.006854169678868094</v>
       </c>
       <c r="C240" t="n">
-        <v>0.00183276480722272</v>
+        <v>0.001832845791925442</v>
       </c>
       <c r="D240" t="n">
-        <v>-0.002922493776128965</v>
+        <v>-0.002922494039235723</v>
       </c>
     </row>
     <row r="241">
@@ -3813,13 +3813,13 @@
         <v>45441</v>
       </c>
       <c r="B241" t="n">
-        <v>-0.01059264462082832</v>
+        <v>-0.01059264372216007</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.01450498688750346</v>
+        <v>-0.01450506655151229</v>
       </c>
       <c r="D241" t="n">
-        <v>-0.01097454442029133</v>
+        <v>-0.01097436482713499</v>
       </c>
     </row>
     <row r="242">
@@ -3827,13 +3827,13 @@
         <v>45442</v>
       </c>
       <c r="B242" t="n">
-        <v>-0.01105306884443924</v>
+        <v>-0.01105315364384329</v>
       </c>
       <c r="C242" t="n">
         <v>0.004342556429610012</v>
       </c>
       <c r="D242" t="n">
-        <v>-0.01619627465963336</v>
+        <v>-0.01619636447493988</v>
       </c>
     </row>
     <row r="243">
@@ -3847,7 +3847,7 @@
         <v>0.01102420609618626</v>
       </c>
       <c r="D243" t="n">
-        <v>0.00532366538105844</v>
+        <v>0.005323572584158054</v>
       </c>
     </row>
     <row r="244">
@@ -3858,10 +3858,10 @@
         <v>0.05587598499664725</v>
       </c>
       <c r="C244" t="n">
-        <v>0.0265416896455315</v>
+        <v>0.02654177042665928</v>
       </c>
       <c r="D244" t="n">
-        <v>-0.000710752325798536</v>
+        <v>-0.0007107523914048341</v>
       </c>
     </row>
     <row r="245">
@@ -3872,10 +3872,10 @@
         <v>-0.07485139657931561</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.05664026166199176</v>
+        <v>-0.05664041458980795</v>
       </c>
       <c r="D245" t="n">
-        <v>-0.008713278195762397</v>
+        <v>-0.008713371371776413</v>
       </c>
     </row>
     <row r="246">
@@ -3886,10 +3886,10 @@
         <v>0.01680057958887304</v>
       </c>
       <c r="C246" t="n">
-        <v>0.04628657586696616</v>
+        <v>0.04628666314534535</v>
       </c>
       <c r="D246" t="n">
-        <v>0.02615425415237782</v>
+        <v>0.02615435220974405</v>
       </c>
     </row>
     <row r="247">
@@ -3903,7 +3903,7 @@
         <v>0.005090807040371015</v>
       </c>
       <c r="D247" t="n">
-        <v>0.02947339133062687</v>
+        <v>0.02947366643126181</v>
       </c>
     </row>
     <row r="248">
@@ -3914,10 +3914,10 @@
         <v>0.02678814369268001</v>
       </c>
       <c r="C248" t="n">
-        <v>0.008751645360729254</v>
+        <v>0.008751724683893292</v>
       </c>
       <c r="D248" t="n">
-        <v>0.0416709962223929</v>
+        <v>0.04167072424619001</v>
       </c>
     </row>
     <row r="249">
@@ -3928,10 +3928,10 @@
         <v>0.000986523838947706</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.007658653736140497</v>
+        <v>-0.007658810403847194</v>
       </c>
       <c r="D249" t="n">
-        <v>-0.02207232618711041</v>
+        <v>-0.02207215869700463</v>
       </c>
     </row>
     <row r="250">
@@ -3939,13 +3939,13 @@
         <v>45454</v>
       </c>
       <c r="B250" t="n">
-        <v>-0.01000748777380378</v>
+        <v>-0.01000740381132559</v>
       </c>
       <c r="C250" t="n">
-        <v>0.002241673106388786</v>
+        <v>0.002241752525893981</v>
       </c>
       <c r="D250" t="n">
-        <v>-0.00266699802096626</v>
+        <v>-0.002667170971703325</v>
       </c>
     </row>
     <row r="251">
@@ -3953,13 +3953,13 @@
         <v>45455</v>
       </c>
       <c r="B251" t="n">
-        <v>0.004565133833809965</v>
+        <v>0.004565048635417179</v>
       </c>
       <c r="C251" t="n">
         <v>0.00597515109447988</v>
       </c>
       <c r="D251" t="n">
-        <v>-0.007053451776451447</v>
+        <v>-0.007053278744034053</v>
       </c>
     </row>
     <row r="252">
@@ -3973,7 +3973,7 @@
         <v>0.004192808022098315</v>
       </c>
       <c r="D252" t="n">
-        <v>0.005891474901685623</v>
+        <v>0.005891474386540141</v>
       </c>
     </row>
     <row r="253">
@@ -3984,10 +3984,10 @@
         <v>0.008394474272240382</v>
       </c>
       <c r="C253" t="n">
-        <v>0.01021664186520543</v>
+        <v>0.01021656359835288</v>
       </c>
       <c r="D253" t="n">
-        <v>-0.003380244078900918</v>
+        <v>-0.003380330712078217</v>
       </c>
     </row>
     <row r="254">
@@ -3998,10 +3998,10 @@
         <v>0.00235186640515872</v>
       </c>
       <c r="C254" t="n">
-        <v>0.006825652727592058</v>
+        <v>0.006825808207053807</v>
       </c>
       <c r="D254" t="n">
-        <v>0.006246131165788871</v>
+        <v>0.006246218387639502</v>
       </c>
     </row>
     <row r="255">
@@ -4009,13 +4009,13 @@
         <v>45462</v>
       </c>
       <c r="B255" t="n">
-        <v>-0.01510778578328931</v>
+        <v>-0.01510770236647663</v>
       </c>
       <c r="C255" t="n">
-        <v>0.03112953945838526</v>
+        <v>0.03112946011289042</v>
       </c>
       <c r="D255" t="n">
-        <v>0.008777347351639708</v>
+        <v>0.008777086549538238</v>
       </c>
     </row>
     <row r="256">
@@ -4023,13 +4023,13 @@
         <v>45463</v>
       </c>
       <c r="B256" t="n">
-        <v>0.01031771393608749</v>
+        <v>0.01031754366945381</v>
       </c>
       <c r="C256" t="n">
         <v>0.006936652144256872</v>
       </c>
       <c r="D256" t="n">
-        <v>0.002679695374333324</v>
+        <v>0.002679781761089295</v>
       </c>
     </row>
     <row r="257">
@@ -4037,13 +4037,13 @@
         <v>45464</v>
       </c>
       <c r="B257" t="n">
-        <v>-0.01323203812922091</v>
+        <v>-0.01323187157559025</v>
       </c>
       <c r="C257" t="n">
-        <v>-0.002156462521004543</v>
+        <v>-0.002156536633886263</v>
       </c>
       <c r="D257" t="n">
-        <v>0.0114159852930944</v>
+        <v>0.01141615766459636</v>
       </c>
     </row>
     <row r="258">
@@ -4051,13 +4051,13 @@
         <v>45467</v>
       </c>
       <c r="B258" t="n">
-        <v>-0.008750509096278281</v>
+        <v>-0.008750678264007772</v>
       </c>
       <c r="C258" t="n">
-        <v>0.003992176374129297</v>
+        <v>0.00399225094369493</v>
       </c>
       <c r="D258" t="n">
-        <v>-0.003620992197276962</v>
+        <v>-0.003621076619785057</v>
       </c>
     </row>
     <row r="259">
@@ -4065,13 +4065,13 @@
         <v>45468</v>
       </c>
       <c r="B259" t="n">
-        <v>0.008793131420791411</v>
+        <v>0.008793217879960125</v>
       </c>
       <c r="C259" t="n">
         <v>0.02328988671348364</v>
       </c>
       <c r="D259" t="n">
-        <v>0.009691183866326947</v>
+        <v>0.009691268903565531</v>
       </c>
     </row>
     <row r="260">
@@ -4085,7 +4085,7 @@
         <v>-0.005755686627786472</v>
       </c>
       <c r="D260" t="n">
-        <v>-0.0008105432610621133</v>
+        <v>-0.0008107116348573529</v>
       </c>
     </row>
     <row r="261">
@@ -4093,13 +4093,13 @@
         <v>45470</v>
       </c>
       <c r="B261" t="n">
-        <v>0.01091463516632452</v>
+        <v>0.01091471676497258</v>
       </c>
       <c r="C261" t="n">
         <v>-0.003144306988719037</v>
       </c>
       <c r="D261" t="n">
-        <v>0.02119169304783064</v>
+        <v>0.02119177912342929</v>
       </c>
     </row>
     <row r="262">
@@ -4107,10 +4107,10 @@
         <v>45471</v>
       </c>
       <c r="B262" t="n">
-        <v>0.02276964031814055</v>
+        <v>0.02276955776259104</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.00728112937923775</v>
+        <v>-0.007281202321097524</v>
       </c>
       <c r="D262" t="n">
         <v>-0.004194940121218571</v>
@@ -4124,7 +4124,7 @@
         <v>-0.003353811926567474</v>
       </c>
       <c r="C263" t="n">
-        <v>0.01270921799465796</v>
+        <v>0.01270936588221061</v>
       </c>
       <c r="D263" t="n">
         <v>0.01535034187529072</v>
@@ -4135,13 +4135,13 @@
         <v>45475</v>
       </c>
       <c r="B264" t="n">
-        <v>0.0032208997154759</v>
+        <v>0.003220820529250545</v>
       </c>
       <c r="C264" t="n">
-        <v>0.01489563327119514</v>
+        <v>0.01489555963571143</v>
       </c>
       <c r="D264" t="n">
-        <v>0.01901559722249102</v>
+        <v>0.01901551558771208</v>
       </c>
     </row>
     <row r="265">
@@ -4149,13 +4149,13 @@
         <v>45476</v>
       </c>
       <c r="B265" t="n">
-        <v>-0.008146097436494082</v>
+        <v>-0.008146019147482364</v>
       </c>
       <c r="C265" t="n">
-        <v>0.02198663297016257</v>
+        <v>0.02198670446001594</v>
       </c>
       <c r="D265" t="n">
-        <v>0.003917127627734551</v>
+        <v>0.003917208052960142</v>
       </c>
     </row>
     <row r="266">
@@ -4166,7 +4166,7 @@
         <v>0.001030643971437151</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.02346415821205317</v>
+        <v>-0.0234642265225351</v>
       </c>
       <c r="D266" t="n">
         <v>0.01428662399238023</v>
@@ -4183,7 +4183,7 @@
         <v>-0.04576910720291349</v>
       </c>
       <c r="D267" t="n">
-        <v>-0.00193870522467765</v>
+        <v>-0.001938626549845002</v>
       </c>
     </row>
     <row r="268">
@@ -4197,7 +4197,7 @@
         <v>-0.007736180590102726</v>
       </c>
       <c r="D268" t="n">
-        <v>0.008619488892513294</v>
+        <v>0.008619409385409282</v>
       </c>
     </row>
     <row r="269">
@@ -4205,7 +4205,7 @@
         <v>45482</v>
       </c>
       <c r="B269" t="n">
-        <v>-0.00663697862976842</v>
+        <v>-0.006636901459187605</v>
       </c>
       <c r="C269" t="n">
         <v>0.0007032014693770794</v>
@@ -4219,10 +4219,10 @@
         <v>45483</v>
       </c>
       <c r="B270" t="n">
-        <v>-0.003804370034202087</v>
+        <v>-0.003804447424831436</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.006355059753558767</v>
+        <v>-0.006354984152985965</v>
       </c>
       <c r="D270" t="n">
         <v>-0.005370673488082067</v>
@@ -4236,10 +4236,10 @@
         <v>-0.00225658996090794</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.002582750579912974</v>
+        <v>-0.002582902551578781</v>
       </c>
       <c r="D271" t="n">
-        <v>0.002699876080044961</v>
+        <v>0.002699797290653505</v>
       </c>
     </row>
     <row r="272">
@@ -4247,13 +4247,13 @@
         <v>45485</v>
       </c>
       <c r="B272" t="n">
-        <v>0.01016992285840179</v>
+        <v>0.01016984469917048</v>
       </c>
       <c r="C272" t="n">
-        <v>0.0004931573558710767</v>
+        <v>0.0004932336746024113</v>
       </c>
       <c r="D272" t="n">
-        <v>0.03572930799929686</v>
+        <v>0.03572946796130538</v>
       </c>
     </row>
     <row r="273">
@@ -4261,13 +4261,13 @@
         <v>45488</v>
       </c>
       <c r="B273" t="n">
-        <v>0.0003131259423954091</v>
+        <v>0.0003132033389889877</v>
       </c>
       <c r="C273" t="n">
         <v>-0.0003697047645558893</v>
       </c>
       <c r="D273" t="n">
-        <v>-0.002745611611350118</v>
+        <v>-0.002745687269626429</v>
       </c>
     </row>
     <row r="274">
@@ -4275,10 +4275,10 @@
         <v>45489</v>
       </c>
       <c r="B274" t="n">
-        <v>-0.01313216732042599</v>
+        <v>-0.01313224466856666</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.001448781033240532</v>
+        <v>-0.001448704761535802</v>
       </c>
       <c r="D274" t="n">
         <v>0.01113029565052281</v>
@@ -4289,10 +4289,10 @@
         <v>45491</v>
       </c>
       <c r="B275" t="n">
-        <v>0.006613799016347954</v>
+        <v>0.00661395628954442</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.003055905705052431</v>
+        <v>-0.003056058236355796</v>
       </c>
       <c r="D275" t="n">
         <v>0.01853947927756439</v>
@@ -4303,13 +4303,13 @@
         <v>45492</v>
       </c>
       <c r="B276" t="n">
-        <v>-0.01986854795816262</v>
+        <v>-0.01986862427358238</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.004644645399305647</v>
+        <v>-0.004644492522152488</v>
       </c>
       <c r="D276" t="n">
-        <v>0.0198514340951077</v>
+        <v>0.01985150796365764</v>
       </c>
     </row>
     <row r="277">
@@ -4317,13 +4317,13 @@
         <v>45495</v>
       </c>
       <c r="B277" t="n">
-        <v>-0.03502879093942579</v>
+        <v>-0.03502887038023872</v>
       </c>
       <c r="C277" t="n">
-        <v>0.02193120570482132</v>
+        <v>0.02193112704267852</v>
       </c>
       <c r="D277" t="n">
-        <v>0.009983485076850096</v>
+        <v>0.009983556784430858</v>
       </c>
     </row>
     <row r="278">
@@ -4331,13 +4331,13 @@
         <v>45496</v>
       </c>
       <c r="B278" t="n">
-        <v>-0.008512851601945037</v>
+        <v>-0.008512852302761664</v>
       </c>
       <c r="C278" t="n">
         <v>-0.01470272547033757</v>
       </c>
       <c r="D278" t="n">
-        <v>0.01438561700775143</v>
+        <v>0.01438547151498359</v>
       </c>
     </row>
     <row r="279">
@@ -4345,7 +4345,7 @@
         <v>45497</v>
       </c>
       <c r="B279" t="n">
-        <v>0.005242268948590256</v>
+        <v>0.005242269383863185</v>
       </c>
       <c r="C279" t="n">
         <v>-0.008866751124292471</v>
@@ -4359,13 +4359,13 @@
         <v>45498</v>
       </c>
       <c r="B280" t="n">
-        <v>-0.002206367739850834</v>
+        <v>-0.002206285323713364</v>
       </c>
       <c r="C280" t="n">
-        <v>0.007823832682266385</v>
+        <v>0.007823909812235685</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.004961827682652076</v>
+        <v>-0.004961969305511293</v>
       </c>
     </row>
     <row r="281">
@@ -4376,10 +4376,10 @@
         <v>0.01113984164322313</v>
       </c>
       <c r="C281" t="n">
-        <v>0.0009588594279477114</v>
+        <v>0.000958782823369031</v>
       </c>
       <c r="D281" t="n">
-        <v>0.02961882210880029</v>
+        <v>0.02961896865351199</v>
       </c>
     </row>
     <row r="282">
@@ -4387,7 +4387,7 @@
         <v>45502</v>
       </c>
       <c r="B282" t="n">
-        <v>0.007339147452146255</v>
+        <v>0.007339065583135795</v>
       </c>
       <c r="C282" t="n">
         <v>-0.008095590711742706</v>
@@ -4401,10 +4401,10 @@
         <v>45503</v>
       </c>
       <c r="B283" t="n">
-        <v>-0.004572067977327232</v>
+        <v>-0.004571987076364858</v>
       </c>
       <c r="C283" t="n">
-        <v>0.00654186488280617</v>
+        <v>0.006541787800893095</v>
       </c>
       <c r="D283" t="n">
         <v>0.003233393591180356</v>
@@ -4415,13 +4415,13 @@
         <v>45504</v>
       </c>
       <c r="B284" t="n">
-        <v>-0.005105313731040506</v>
+        <v>-0.005105232085210853</v>
       </c>
       <c r="C284" t="n">
-        <v>0.0001237547844894493</v>
+        <v>0.0001237547939667571</v>
       </c>
       <c r="D284" t="n">
-        <v>-0.004741305387207406</v>
+        <v>-0.004741236205408783</v>
       </c>
     </row>
     <row r="285">
@@ -4429,13 +4429,13 @@
         <v>45505</v>
       </c>
       <c r="B285" t="n">
-        <v>0.006559685357006018</v>
+        <v>0.006559602753897442</v>
       </c>
       <c r="C285" t="n">
-        <v>0.0142657980502916</v>
+        <v>0.01426587571410542</v>
       </c>
       <c r="D285" t="n">
-        <v>-0.00837674608225214</v>
+        <v>-0.008376815011341465</v>
       </c>
     </row>
     <row r="286">
@@ -4446,7 +4446,7 @@
         <v>-0.0105425608535733</v>
       </c>
       <c r="C286" t="n">
-        <v>0.01241763176275645</v>
+        <v>0.01241755626829044</v>
       </c>
       <c r="D286" t="n">
         <v>-0.01694920363116204</v>
@@ -4457,13 +4457,13 @@
         <v>45509</v>
       </c>
       <c r="B287" t="n">
-        <v>-0.03468226286875775</v>
+        <v>-0.03468218047007954</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.02615795935241139</v>
+        <v>-0.02615796130297132</v>
       </c>
       <c r="D287" t="n">
-        <v>-0.03805178825906042</v>
+        <v>-0.03805171695188936</v>
       </c>
     </row>
     <row r="288">
@@ -4471,13 +4471,13 @@
         <v>45510</v>
       </c>
       <c r="B288" t="n">
-        <v>0.006028488266833332</v>
+        <v>0.006028317034009634</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.009005185954926831</v>
+        <v>-0.009005110073006306</v>
       </c>
       <c r="D288" t="n">
-        <v>-0.0004566276726896135</v>
+        <v>-0.0004567017667042039</v>
       </c>
     </row>
     <row r="289">
@@ -4485,10 +4485,10 @@
         <v>45511</v>
       </c>
       <c r="B289" t="n">
-        <v>0.006026472118986215</v>
+        <v>0.006026557477948336</v>
       </c>
       <c r="C289" t="n">
-        <v>0.01392711471993868</v>
+        <v>0.01392703745267765</v>
       </c>
       <c r="D289" t="n">
         <v>0.02315692704332073</v>
@@ -4499,10 +4499,10 @@
         <v>45512</v>
       </c>
       <c r="B290" t="n">
-        <v>-0.01071792947560068</v>
+        <v>-0.01071801381495485</v>
       </c>
       <c r="C290" t="n">
-        <v>0.0118262462070402</v>
+        <v>0.01182632331420841</v>
       </c>
       <c r="D290" t="n">
         <v>-0.02707009970505114</v>
@@ -4513,10 +4513,10 @@
         <v>45513</v>
       </c>
       <c r="B291" t="n">
-        <v>0.01737261909430532</v>
+        <v>0.01737270582847295</v>
       </c>
       <c r="C291" t="n">
-        <v>0.004565684902443357</v>
+        <v>0.004565609587207753</v>
       </c>
       <c r="D291" t="n">
         <v>0.01583340317705106</v>
@@ -4527,10 +4527,10 @@
         <v>45516</v>
       </c>
       <c r="B292" t="n">
-        <v>-0.009275608270023716</v>
+        <v>-0.009275775864647895</v>
       </c>
       <c r="C292" t="n">
-        <v>0.005999184144544145</v>
+        <v>0.005999334540197632</v>
       </c>
       <c r="D292" t="n">
         <v>0.01505014097910484</v>
@@ -4541,13 +4541,13 @@
         <v>45517</v>
       </c>
       <c r="B293" t="n">
-        <v>0.002053901312930373</v>
+        <v>0.002054070824125231</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.03427495488392041</v>
+        <v>-0.03427510138121703</v>
       </c>
       <c r="D293" t="n">
-        <v>2.774452609166644e-05</v>
+        <v>2.781677746166444e-05</v>
       </c>
     </row>
     <row r="294">
@@ -4555,13 +4555,13 @@
         <v>45518</v>
       </c>
       <c r="B294" t="n">
-        <v>-0.001212781235384153</v>
+        <v>-0.001212865643877681</v>
       </c>
       <c r="C294" t="n">
-        <v>0.002869212821661637</v>
+        <v>0.002869367384826571</v>
       </c>
       <c r="D294" t="n">
-        <v>0.01435378144509136</v>
+        <v>0.01435370815867953</v>
       </c>
     </row>
     <row r="295">
@@ -4569,13 +4569,13 @@
         <v>45520</v>
       </c>
       <c r="B295" t="n">
-        <v>0.01118435302740761</v>
+        <v>0.01118452299459638</v>
       </c>
       <c r="C295" t="n">
-        <v>0.01511384225756762</v>
+        <v>0.01511384109455638</v>
       </c>
       <c r="D295" t="n">
-        <v>0.01958037046866368</v>
+        <v>0.0195802992416747</v>
       </c>
     </row>
     <row r="296">
@@ -4583,13 +4583,13 @@
         <v>45523</v>
       </c>
       <c r="B296" t="n">
-        <v>0.0103177376446526</v>
+        <v>0.01031765320610134</v>
       </c>
       <c r="C296" t="n">
-        <v>-0.0003369504911707732</v>
+        <v>-0.0003370262700076454</v>
       </c>
       <c r="D296" t="n">
-        <v>0.003146943841579652</v>
+        <v>0.003147013920548725</v>
       </c>
     </row>
     <row r="297">
@@ -4600,10 +4600,10 @@
         <v>0.005072557760318563</v>
       </c>
       <c r="C297" t="n">
-        <v>0.0037693544536892</v>
+        <v>0.003769430283625086</v>
       </c>
       <c r="D297" t="n">
-        <v>0.003968294315219723</v>
+        <v>0.003968155035283027</v>
       </c>
     </row>
     <row r="298">
@@ -4614,10 +4614,10 @@
         <v>0.001821661683359288</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.007266237529757191</v>
+        <v>-0.007266236980828067</v>
       </c>
       <c r="D298" t="n">
-        <v>0.0002669153992636009</v>
+        <v>0.000267123530447666</v>
       </c>
     </row>
     <row r="299">
@@ -4628,10 +4628,10 @@
         <v>-0.0003670710938989963</v>
       </c>
       <c r="C299" t="n">
-        <v>0.003383018307382857</v>
+        <v>0.003382941951820984</v>
       </c>
       <c r="D299" t="n">
-        <v>0.004031718674120111</v>
+        <v>0.004031649048341412</v>
       </c>
     </row>
     <row r="300">
@@ -4645,7 +4645,7 @@
         <v>-0.00383136357651781</v>
       </c>
       <c r="D300" t="n">
-        <v>-0.009652976059740803</v>
+        <v>-0.009653045127478332</v>
       </c>
     </row>
     <row r="301">
@@ -4653,13 +4653,13 @@
         <v>45530</v>
       </c>
       <c r="B301" t="n">
-        <v>0.008416767308946804</v>
+        <v>0.008416849393318548</v>
       </c>
       <c r="C301" t="n">
         <v>0.009168955358966002</v>
       </c>
       <c r="D301" t="n">
-        <v>0.007545272857612195</v>
+        <v>0.007545343124776727</v>
       </c>
     </row>
     <row r="302">
@@ -4667,13 +4667,13 @@
         <v>45531</v>
       </c>
       <c r="B302" t="n">
-        <v>-0.008032478302011592</v>
+        <v>-0.008032559047420396</v>
       </c>
       <c r="C302" t="n">
         <v>-0.001341501236599818</v>
       </c>
       <c r="D302" t="n">
-        <v>0.01276551503640655</v>
+        <v>0.01276544581773509</v>
       </c>
     </row>
     <row r="303">
@@ -4681,13 +4681,13 @@
         <v>45532</v>
       </c>
       <c r="B303" t="n">
-        <v>-0.001432903525187212</v>
+        <v>-0.001432821466801792</v>
       </c>
       <c r="C303" t="n">
         <v>-0.0003969022287185764</v>
       </c>
       <c r="D303" t="n">
-        <v>0.02052518311313101</v>
+        <v>0.0205252528621509</v>
       </c>
     </row>
     <row r="304">
@@ -4695,13 +4695,13 @@
         <v>45533</v>
       </c>
       <c r="B304" t="n">
-        <v>0.01510044019290691</v>
+        <v>0.01510035677588206</v>
       </c>
       <c r="C304" t="n">
         <v>0.0008857139553528626</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.002965234242521819</v>
+        <v>-0.002965301214114646</v>
       </c>
     </row>
     <row r="305">
@@ -4715,7 +4715,7 @@
         <v>-0.001006947834348626</v>
       </c>
       <c r="D305" t="n">
-        <v>0.005353376016327349</v>
+        <v>0.005353376375917707</v>
       </c>
     </row>
     <row r="306">
@@ -4723,13 +4723,13 @@
         <v>45537</v>
       </c>
       <c r="B306" t="n">
-        <v>0.004388480741684075</v>
+        <v>0.004388562301346211</v>
       </c>
       <c r="C306" t="n">
         <v>-0.006078689878129206</v>
       </c>
       <c r="D306" t="n">
-        <v>0.01070118605268644</v>
+        <v>0.01070132039386329</v>
       </c>
     </row>
     <row r="307">
@@ -4737,13 +4737,13 @@
         <v>45538</v>
       </c>
       <c r="B307" t="n">
-        <v>-0.004699072739482779</v>
+        <v>-0.004699153561198988</v>
       </c>
       <c r="C307" t="n">
-        <v>0.006392363566181558</v>
+        <v>0.006392439610525269</v>
       </c>
       <c r="D307" t="n">
-        <v>-0.0118350991043209</v>
+        <v>-0.01183503221627291</v>
       </c>
     </row>
     <row r="308">
@@ -4754,10 +4754,10 @@
         <v>0.003594790918618695</v>
       </c>
       <c r="C308" t="n">
-        <v>0.002717940971943777</v>
+        <v>0.002717789643927881</v>
       </c>
       <c r="D308" t="n">
-        <v>-0.00968447228536784</v>
+        <v>-0.009684604784462869</v>
       </c>
     </row>
     <row r="309">
@@ -4768,10 +4768,10 @@
         <v>-0.01424514487199091</v>
       </c>
       <c r="C309" t="n">
-        <v>0.002223017149710627</v>
+        <v>0.002223092673748761</v>
       </c>
       <c r="D309" t="n">
-        <v>0.005565916098315471</v>
+        <v>0.005565848546690955</v>
       </c>
     </row>
     <row r="310">
@@ -4785,7 +4785,7 @@
         <v>-0.005165735032823582</v>
       </c>
       <c r="D310" t="n">
-        <v>-0.01619130817053038</v>
+        <v>-0.01619117490277877</v>
       </c>
     </row>
     <row r="311">
@@ -4793,13 +4793,13 @@
         <v>45544</v>
       </c>
       <c r="B311" t="n">
-        <v>-0.001621403126458643</v>
+        <v>-0.00162131907238261</v>
       </c>
       <c r="C311" t="n">
         <v>0.00583407968377414</v>
       </c>
       <c r="D311" t="n">
-        <v>-0.003785626990373325</v>
+        <v>-0.003785763298499112</v>
       </c>
     </row>
     <row r="312">
@@ -4807,13 +4807,13 @@
         <v>45545</v>
       </c>
       <c r="B312" t="n">
-        <v>-0.0006324396587149561</v>
+        <v>-0.000632439605469437</v>
       </c>
       <c r="C312" t="n">
-        <v>0.002338325553316922</v>
+        <v>0.002338250411906495</v>
       </c>
       <c r="D312" t="n">
-        <v>0.009315650937877784</v>
+        <v>0.009315720119196014</v>
       </c>
     </row>
     <row r="313">
@@ -4821,10 +4821,10 @@
         <v>45546</v>
       </c>
       <c r="B313" t="n">
-        <v>-0.006859303736274303</v>
+        <v>-0.006859303158420094</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.003908283455877903</v>
+        <v>-0.003908208782745892</v>
       </c>
       <c r="D313" t="n">
         <v>-0.001124320694617764</v>
@@ -4835,13 +4835,13 @@
         <v>45547</v>
       </c>
       <c r="B314" t="n">
-        <v>0.01949710400793836</v>
+        <v>0.01949701752838262</v>
       </c>
       <c r="C314" t="n">
         <v>0.01380860083210744</v>
       </c>
       <c r="D314" t="n">
-        <v>0.02109773890152677</v>
+        <v>0.02109780688813068</v>
       </c>
     </row>
     <row r="315">
@@ -4855,7 +4855,7 @@
         <v>-0.0003900315826106393</v>
       </c>
       <c r="D315" t="n">
-        <v>-0.003255587451233777</v>
+        <v>-0.003255587234470614</v>
       </c>
     </row>
     <row r="316">
@@ -4863,13 +4863,13 @@
         <v>45551</v>
       </c>
       <c r="B316" t="n">
-        <v>-0.0008658534199453838</v>
+        <v>-0.000865769811079109</v>
       </c>
       <c r="C316" t="n">
         <v>0.003001236497852</v>
       </c>
       <c r="D316" t="n">
-        <v>0.003163349923174019</v>
+        <v>0.003163349711864383</v>
       </c>
     </row>
     <row r="317">
@@ -4877,13 +4877,13 @@
         <v>45552</v>
       </c>
       <c r="B317" t="n">
-        <v>0.0006457687627332565</v>
+        <v>0.0006456850273792725</v>
       </c>
       <c r="C317" t="n">
         <v>-0.001286626408101399</v>
       </c>
       <c r="D317" t="n">
-        <v>0.001179419136075444</v>
+        <v>0.001179352468839268</v>
       </c>
     </row>
     <row r="318">
@@ -4891,10 +4891,10 @@
         <v>45553</v>
       </c>
       <c r="B318" t="n">
-        <v>-0.006011048005007624</v>
+        <v>-0.006011131632325806</v>
       </c>
       <c r="C318" t="n">
-        <v>0.01558010291147571</v>
+        <v>0.01558002877417075</v>
       </c>
       <c r="D318" t="n">
         <v>-0.03093392245462234</v>
@@ -4905,13 +4905,13 @@
         <v>45554</v>
       </c>
       <c r="B319" t="n">
-        <v>0.004253682671688575</v>
+        <v>0.00425376716261705</v>
       </c>
       <c r="C319" t="n">
-        <v>0.008083504360068439</v>
+        <v>0.008083577950127374</v>
       </c>
       <c r="D319" t="n">
-        <v>0.001083446223771878</v>
+        <v>0.001083377590411772</v>
       </c>
     </row>
     <row r="320">
@@ -4925,7 +4925,7 @@
         <v>0.01913953937510993</v>
       </c>
       <c r="D320" t="n">
-        <v>0.006097644584244</v>
+        <v>0.006097645002292928</v>
       </c>
     </row>
     <row r="321">
@@ -4936,10 +4936,10 @@
         <v>0.005013723772059109</v>
       </c>
       <c r="C321" t="n">
-        <v>0.01068235477355017</v>
+        <v>0.01068242582819168</v>
       </c>
       <c r="D321" t="n">
-        <v>-0.004880101397624514</v>
+        <v>-0.004879965443033041</v>
       </c>
     </row>
     <row r="322">
@@ -4950,10 +4950,10 @@
         <v>-0.002678542792911798</v>
       </c>
       <c r="C322" t="n">
-        <v>0.004688057156291059</v>
+        <v>0.004687986523075782</v>
       </c>
       <c r="D322" t="n">
-        <v>0.001133649038555395</v>
+        <v>0.001133580483187124</v>
       </c>
     </row>
     <row r="323">
@@ -4964,10 +4964,10 @@
         <v>0.003071716228543853</v>
       </c>
       <c r="C323" t="n">
-        <v>0.006249799257544986</v>
+        <v>0.006249729281961658</v>
       </c>
       <c r="D323" t="n">
-        <v>-0.001737980716615239</v>
+        <v>-0.001738049116816631</v>
       </c>
     </row>
     <row r="324">
@@ -4978,10 +4978,10 @@
         <v>0.00267751209611089</v>
       </c>
       <c r="C324" t="n">
-        <v>0.002444990835543726</v>
+        <v>0.002445130087513236</v>
       </c>
       <c r="D324" t="n">
-        <v>0.002611612607576141</v>
+        <v>0.002611749825104592</v>
       </c>
     </row>
     <row r="325">
@@ -4992,10 +4992,10 @@
         <v>0.01884245948180774</v>
       </c>
       <c r="C325" t="n">
-        <v>-0.01726979046798749</v>
+        <v>-0.01726992801265725</v>
       </c>
       <c r="D325" t="n">
-        <v>0.003420662405571706</v>
+        <v>0.003420662171800926</v>
       </c>
     </row>
     <row r="326">
@@ -5006,10 +5006,10 @@
         <v>-0.03249960872518631</v>
       </c>
       <c r="C326" t="n">
-        <v>-0.01175366055529969</v>
+        <v>-0.01175359079455474</v>
       </c>
       <c r="D326" t="n">
-        <v>-0.01633675345897545</v>
+        <v>-0.01633668423848633</v>
       </c>
     </row>
     <row r="327">
@@ -5023,7 +5023,7 @@
         <v>-0.003377567551350991</v>
       </c>
       <c r="D327" t="n">
-        <v>0.01532840079505737</v>
+        <v>0.0153282601944853</v>
       </c>
     </row>
     <row r="328">
@@ -5037,7 +5037,7 @@
         <v>-0.02560535132398034</v>
       </c>
       <c r="D328" t="n">
-        <v>-0.005749885929033471</v>
+        <v>-0.005749954122706513</v>
       </c>
     </row>
     <row r="329">
@@ -5051,7 +5051,7 @@
         <v>-0.01447675050668695</v>
       </c>
       <c r="D329" t="n">
-        <v>0.01307164707334807</v>
+        <v>0.01307178514600915</v>
       </c>
     </row>
     <row r="330">
@@ -5059,13 +5059,13 @@
         <v>45572</v>
       </c>
       <c r="B330" t="n">
-        <v>-0.01139536044326506</v>
+        <v>-0.01139544924404778</v>
       </c>
       <c r="C330" t="n">
         <v>-0.02404009922405448</v>
       </c>
       <c r="D330" t="n">
-        <v>0.008419619749848062</v>
+        <v>0.008419551476762654</v>
       </c>
     </row>
     <row r="331">
@@ -5073,13 +5073,13 @@
         <v>45573</v>
       </c>
       <c r="B331" t="n">
-        <v>0.01942397970975418</v>
+        <v>0.01942398145450097</v>
       </c>
       <c r="C331" t="n">
-        <v>0.02055257976550795</v>
+        <v>0.02055265623993874</v>
       </c>
       <c r="D331" t="n">
-        <v>0.00736696161860606</v>
+        <v>0.007367028756387395</v>
       </c>
     </row>
     <row r="332">
@@ -5087,13 +5087,13 @@
         <v>45574</v>
       </c>
       <c r="B332" t="n">
-        <v>-0.0162807896075462</v>
+        <v>-0.01628070292922423</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.01084149986470606</v>
+        <v>-0.01084164892096806</v>
       </c>
       <c r="D332" t="n">
-        <v>0.002155424062906031</v>
+        <v>0.002155423919254051</v>
       </c>
     </row>
     <row r="333">
@@ -5104,10 +5104,10 @@
         <v>-0.002582604978059955</v>
       </c>
       <c r="C333" t="n">
-        <v>0.01791007305343806</v>
+        <v>0.01791015016587449</v>
       </c>
       <c r="D333" t="n">
-        <v>-0.01728325011423626</v>
+        <v>-0.01728338197173951</v>
       </c>
     </row>
     <row r="334">
@@ -5118,10 +5118,10 @@
         <v>0.0007658406340240731</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.006857458749716105</v>
+        <v>-0.00685753317244131</v>
       </c>
       <c r="D334" t="n">
-        <v>0.008389768157495148</v>
+        <v>0.008389904071394616</v>
       </c>
     </row>
     <row r="335">
@@ -5132,10 +5132,10 @@
         <v>0.0003097629900348231</v>
       </c>
       <c r="C335" t="n">
-        <v>0.02247116327231335</v>
+        <v>0.02247123989283173</v>
       </c>
       <c r="D335" t="n">
-        <v>0.01229912039558956</v>
+        <v>0.0122989853501505</v>
       </c>
     </row>
     <row r="336">
@@ -5149,7 +5149,7 @@
         <v>-0.002369529134962467</v>
       </c>
       <c r="D336" t="n">
-        <v>0.0002042538499464897</v>
+        <v>0.0002043201581525267</v>
       </c>
     </row>
     <row r="337">
@@ -5157,13 +5157,13 @@
         <v>45581</v>
       </c>
       <c r="B337" t="n">
-        <v>0.007477475917652132</v>
+        <v>0.007477567526442686</v>
       </c>
       <c r="C337" t="n">
         <v>0.009322552378198568</v>
       </c>
       <c r="D337" t="n">
-        <v>-0.02000715570999945</v>
+        <v>-0.02000722199112204</v>
       </c>
     </row>
     <row r="338">
@@ -5171,13 +5171,13 @@
         <v>45582</v>
       </c>
       <c r="B338" t="n">
-        <v>0.001735559381236262</v>
+        <v>0.001735468294560061</v>
       </c>
       <c r="C338" t="n">
         <v>-0.01567837431578245</v>
       </c>
       <c r="D338" t="n">
-        <v>0.02499858137071587</v>
+        <v>0.02499865069577423</v>
       </c>
     </row>
     <row r="339">
@@ -5199,7 +5199,7 @@
         <v>45586</v>
       </c>
       <c r="B340" t="n">
-        <v>0.007283123146972992</v>
+        <v>0.007283213726322124</v>
       </c>
       <c r="C340" t="n">
         <v>0.02785618266221945</v>
@@ -5213,13 +5213,13 @@
         <v>45587</v>
       </c>
       <c r="B341" t="n">
-        <v>-0.01887954174516315</v>
+        <v>-0.01887971989625237</v>
       </c>
       <c r="C341" t="n">
         <v>-0.008185280922534233</v>
       </c>
       <c r="D341" t="n">
-        <v>-0.0006208127818041476</v>
+        <v>-0.0006207426889078826</v>
       </c>
     </row>
     <row r="342">
@@ -5227,13 +5227,13 @@
         <v>45588</v>
       </c>
       <c r="B342" t="n">
-        <v>-0.003591769067250006</v>
+        <v>-0.003591769396453004</v>
       </c>
       <c r="C342" t="n">
         <v>0.01239396946459115</v>
       </c>
       <c r="D342" t="n">
-        <v>0.01177380381603932</v>
+        <v>0.01177366271740099</v>
       </c>
     </row>
     <row r="343">
@@ -5241,13 +5241,13 @@
         <v>45589</v>
       </c>
       <c r="B343" t="n">
-        <v>0.0009525988259191376</v>
+        <v>0.000952690898761821</v>
       </c>
       <c r="C343" t="n">
         <v>0.007978955998030335</v>
       </c>
       <c r="D343" t="n">
-        <v>-0.005364626723492694</v>
+        <v>-0.005364557775090817</v>
       </c>
     </row>
     <row r="344">
@@ -5261,7 +5261,7 @@
         <v>-0.00357213164553527</v>
       </c>
       <c r="D344" t="n">
-        <v>-0.0006977082121671918</v>
+        <v>-0.0006976385180095246</v>
       </c>
     </row>
     <row r="345">
@@ -5275,7 +5275,7 @@
         <v>-0.005277097282829213</v>
       </c>
       <c r="D345" t="n">
-        <v>0.001772304485425646</v>
+        <v>0.00177216487619436</v>
       </c>
     </row>
     <row r="346">
@@ -5289,7 +5289,7 @@
         <v>0.01017764234634311</v>
       </c>
       <c r="D346" t="n">
-        <v>-0.002738062599842994</v>
+        <v>-0.00273806279046529</v>
       </c>
     </row>
     <row r="347">
@@ -5300,10 +5300,10 @@
         <v>0.002910516413599851</v>
       </c>
       <c r="C347" t="n">
-        <v>-0.009846707832153578</v>
+        <v>-0.009846778454829508</v>
       </c>
       <c r="D347" t="n">
-        <v>-0.02022524103323287</v>
+        <v>-0.02022510282400558</v>
       </c>
     </row>
     <row r="348">
@@ -5314,10 +5314,10 @@
         <v>-0.008817616322833066</v>
       </c>
       <c r="C348" t="n">
-        <v>0.0006340791811547675</v>
+        <v>0.000634221876375296</v>
       </c>
       <c r="D348" t="n">
-        <v>-0.02488749184970085</v>
+        <v>-0.02488763257973314</v>
       </c>
     </row>
     <row r="349">
@@ -5328,10 +5328,10 @@
         <v>0.004954743276563756</v>
       </c>
       <c r="C349" t="n">
-        <v>0.0009219328713974129</v>
+        <v>0.0009217902461020611</v>
       </c>
       <c r="D349" t="n">
-        <v>0.002048522845870648</v>
+        <v>0.00204859606575436</v>
       </c>
     </row>
     <row r="350">
@@ -5342,10 +5342,10 @@
         <v>-0.02726628556460031</v>
       </c>
       <c r="C350" t="n">
-        <v>-0.01335414685281566</v>
+        <v>-0.01335407658967425</v>
       </c>
       <c r="D350" t="n">
-        <v>0.001590257079407742</v>
+        <v>0.001590184158595243</v>
       </c>
     </row>
     <row r="351">
@@ -5359,7 +5359,7 @@
         <v>0.0255235901576325</v>
       </c>
       <c r="D351" t="n">
-        <v>-0.005358304877485898</v>
+        <v>-0.005358232462558399</v>
       </c>
     </row>
     <row r="352">
@@ -5367,13 +5367,13 @@
         <v>45602</v>
       </c>
       <c r="B352" t="n">
-        <v>0.01536033136555481</v>
+        <v>0.01536042569214979</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.001478999460454489</v>
+        <v>-0.001479069842079128</v>
       </c>
       <c r="D352" t="n">
-        <v>0.0396191810750568</v>
+        <v>0.03961925427230373</v>
       </c>
     </row>
     <row r="353">
@@ -5381,13 +5381,13 @@
         <v>45603</v>
       </c>
       <c r="B353" t="n">
-        <v>-0.01486394013696746</v>
+        <v>-0.01486393875611314</v>
       </c>
       <c r="C353" t="n">
-        <v>-0.004956566604921053</v>
+        <v>-0.004956496468410787</v>
       </c>
       <c r="D353" t="n">
-        <v>-0.01132304469582512</v>
+        <v>-0.0113231143063397</v>
       </c>
     </row>
     <row r="354">
@@ -5395,10 +5395,10 @@
         <v>45604</v>
       </c>
       <c r="B354" t="n">
-        <v>-0.0167731862886642</v>
+        <v>-0.01677337330954298</v>
       </c>
       <c r="C354" t="n">
-        <v>0.004523153775752853</v>
+        <v>0.004523082938771239</v>
       </c>
       <c r="D354" t="n">
         <v>0.01491914243114012</v>
@@ -5409,10 +5409,10 @@
         <v>45607</v>
       </c>
       <c r="B355" t="n">
-        <v>-0.008607733532774997</v>
+        <v>-0.008607638448302146</v>
       </c>
       <c r="C355" t="n">
-        <v>0.006754286243775276</v>
+        <v>0.006754357238096809</v>
       </c>
       <c r="D355" t="n">
         <v>0.01647583740782999</v>
@@ -5426,7 +5426,7 @@
         <v>0.001217991446004429</v>
       </c>
       <c r="C356" t="n">
-        <v>-0.0272321317875448</v>
+        <v>-0.0272320617426306</v>
       </c>
       <c r="D356" t="n">
         <v>0.004677193181553019</v>
@@ -5440,10 +5440,10 @@
         <v>-0.01742198491102764</v>
       </c>
       <c r="C357" t="n">
-        <v>-0.0214468511258068</v>
+        <v>-0.02144692158728967</v>
       </c>
       <c r="D357" t="n">
-        <v>-0.0002140959509893126</v>
+        <v>-0.0002140272424042688</v>
       </c>
     </row>
     <row r="358">
@@ -5457,7 +5457,7 @@
         <v>0.006780317535256319</v>
       </c>
       <c r="D358" t="n">
-        <v>-0.00206053065656997</v>
+        <v>-0.002060599238257299</v>
       </c>
     </row>
     <row r="359">
@@ -5471,7 +5471,7 @@
         <v>0.007295753829026363</v>
       </c>
       <c r="D359" t="n">
-        <v>-0.02847872027528453</v>
+        <v>-0.02847878914048174</v>
       </c>
     </row>
     <row r="360">
@@ -5485,7 +5485,7 @@
         <v>0.02178765189590481</v>
       </c>
       <c r="D360" t="n">
-        <v>0.007342152233054788</v>
+        <v>0.007342223637379686</v>
       </c>
     </row>
     <row r="361">
@@ -5493,7 +5493,7 @@
         <v>45617</v>
       </c>
       <c r="B361" t="n">
-        <v>-0.01502036738137025</v>
+        <v>-0.01502026821935865</v>
       </c>
       <c r="C361" t="n">
         <v>-0.0006027482707913201</v>
@@ -5507,10 +5507,10 @@
         <v>45618</v>
       </c>
       <c r="B362" t="n">
-        <v>0.03466896418556509</v>
+        <v>0.034668759346967</v>
       </c>
       <c r="C362" t="n">
-        <v>0.002527058317954634</v>
+        <v>0.002526987263313352</v>
       </c>
       <c r="D362" t="n">
         <v>0.03718547208268164</v>
@@ -5521,13 +5521,13 @@
         <v>45621</v>
       </c>
       <c r="B363" t="n">
-        <v>0.01706958626314314</v>
+        <v>0.01706968522489305</v>
       </c>
       <c r="C363" t="n">
-        <v>0.02291469824634795</v>
+        <v>0.02291477074597914</v>
       </c>
       <c r="D363" t="n">
-        <v>-0.006597554825666374</v>
+        <v>-0.006597487325284535</v>
       </c>
     </row>
     <row r="364">
@@ -5535,13 +5535,13 @@
         <v>45622</v>
       </c>
       <c r="B364" t="n">
-        <v>0.006759889878657832</v>
+        <v>0.006759985546502145</v>
       </c>
       <c r="C364" t="n">
         <v>-2.792299351117578e-05</v>
       </c>
       <c r="D364" t="n">
-        <v>0.01823049414316369</v>
+        <v>0.01823042495575344</v>
       </c>
     </row>
     <row r="365">
@@ -5549,13 +5549,13 @@
         <v>45623</v>
       </c>
       <c r="B365" t="n">
-        <v>-0.001929397396852939</v>
+        <v>-0.001929492238984531</v>
       </c>
       <c r="C365" t="n">
         <v>0.01498134685019492</v>
       </c>
       <c r="D365" t="n">
-        <v>0.0001819117523800262</v>
+        <v>0.0001818450202626387</v>
       </c>
     </row>
     <row r="366">
@@ -5569,7 +5569,7 @@
         <v>-0.0105667119049504</v>
       </c>
       <c r="D366" t="n">
-        <v>-0.03525590515194343</v>
+        <v>-0.03525590750421692</v>
       </c>
     </row>
     <row r="367">
@@ -5583,7 +5583,7 @@
         <v>0.001617337337406433</v>
       </c>
       <c r="D367" t="n">
-        <v>0.0006462835273843837</v>
+        <v>0.000646352730300892</v>
       </c>
     </row>
     <row r="368">
@@ -5591,7 +5591,7 @@
         <v>45628</v>
       </c>
       <c r="B368" t="n">
-        <v>0.01311721020932977</v>
+        <v>0.01311730549218981</v>
       </c>
       <c r="C368" t="n">
         <v>0.004816072393940996</v>
@@ -5605,7 +5605,7 @@
         <v>45629</v>
       </c>
       <c r="B369" t="n">
-        <v>0.01080860395911376</v>
+        <v>0.01080841484419715</v>
       </c>
       <c r="C369" t="n">
         <v>0.01196872734915932</v>
@@ -5619,7 +5619,7 @@
         <v>45630</v>
       </c>
       <c r="B370" t="n">
-        <v>-0.01084422299258125</v>
+        <v>-0.01084413095803116</v>
       </c>
       <c r="C370" t="n">
         <v>0.01850737844170225</v>
@@ -5647,13 +5647,13 @@
         <v>45632</v>
       </c>
       <c r="B372" t="n">
-        <v>-0.007942161610169252</v>
+        <v>-0.007942254741674204</v>
       </c>
       <c r="C372" t="n">
         <v>-0.005306231280730711</v>
       </c>
       <c r="D372" t="n">
-        <v>-0.006434630804587949</v>
+        <v>-0.006434564441505919</v>
       </c>
     </row>
     <row r="373">
@@ -5661,13 +5661,13 @@
         <v>45635</v>
       </c>
       <c r="B373" t="n">
-        <v>-0.01250433477472224</v>
+        <v>-0.01250424207149214</v>
       </c>
       <c r="C373" t="n">
-        <v>0.007624548819251897</v>
+        <v>0.007624615484305375</v>
       </c>
       <c r="D373" t="n">
-        <v>0.0006502953781071241</v>
+        <v>0.0006502285418068521</v>
       </c>
     </row>
     <row r="374">
@@ -5678,7 +5678,7 @@
         <v>-0.007952826815636138</v>
       </c>
       <c r="C374" t="n">
-        <v>-0.001016028465998797</v>
+        <v>-0.001016094559382008</v>
       </c>
       <c r="D374" t="n">
         <v>0.01294418930574825</v>
@@ -5717,13 +5717,13 @@
         <v>45639</v>
       </c>
       <c r="B377" t="n">
-        <v>0.007878642465797059</v>
+        <v>0.007878739959269243</v>
       </c>
       <c r="C377" t="n">
         <v>0.006723119648891718</v>
       </c>
       <c r="D377" t="n">
-        <v>0.006391632621449483</v>
+        <v>0.00639156800010432</v>
       </c>
     </row>
     <row r="378">
@@ -5731,13 +5731,13 @@
         <v>45642</v>
       </c>
       <c r="B378" t="n">
-        <v>-0.003574610687712587</v>
+        <v>-0.003574610341935625</v>
       </c>
       <c r="C378" t="n">
         <v>-0.003499400054690072</v>
       </c>
       <c r="D378" t="n">
-        <v>-0.009826520039718289</v>
+        <v>-0.009826456459751887</v>
       </c>
     </row>
     <row r="379">
@@ -5745,7 +5745,7 @@
         <v>45643</v>
       </c>
       <c r="B379" t="n">
-        <v>-0.01813443510820112</v>
+        <v>-0.01813462750447625</v>
       </c>
       <c r="C379" t="n">
         <v>-0.01712948256549496</v>
@@ -5759,13 +5759,13 @@
         <v>45644</v>
       </c>
       <c r="B380" t="n">
-        <v>0.006383925574390714</v>
+        <v>0.006384025076941802</v>
       </c>
       <c r="C380" t="n">
-        <v>-0.0123006319336868</v>
+        <v>-0.01230056444680261</v>
       </c>
       <c r="D380" t="n">
-        <v>0.001290132390579624</v>
+        <v>0.001290067429230657</v>
       </c>
     </row>
     <row r="381">
@@ -5776,10 +5776,10 @@
         <v>-0.01819275722362368</v>
       </c>
       <c r="C381" t="n">
-        <v>-0.009499073720226958</v>
+        <v>-0.009499141398529698</v>
       </c>
       <c r="D381" t="n">
-        <v>-0.016648642574698</v>
+        <v>-0.01664857877717041</v>
       </c>
     </row>
     <row r="382">
@@ -5787,13 +5787,13 @@
         <v>45646</v>
       </c>
       <c r="B382" t="n">
-        <v>-0.02043949982898952</v>
+        <v>-0.02043959989361133</v>
       </c>
       <c r="C382" t="n">
         <v>-0.01226649036547267</v>
       </c>
       <c r="D382" t="n">
-        <v>-0.01235731604901313</v>
+        <v>-0.01235744800113325</v>
       </c>
     </row>
     <row r="383">
@@ -5801,13 +5801,13 @@
         <v>45649</v>
       </c>
       <c r="B383" t="n">
-        <v>0.0141043073754461</v>
+        <v>0.01410441096881709</v>
       </c>
       <c r="C383" t="n">
         <v>0.01665255447047009</v>
       </c>
       <c r="D383" t="n">
-        <v>0.001118525118016578</v>
+        <v>0.001118658870568723</v>
       </c>
     </row>
     <row r="384">
@@ -5815,13 +5815,13 @@
         <v>45650</v>
       </c>
       <c r="B384" t="n">
-        <v>0.0003681747898482968</v>
+        <v>0.0003680740580316311</v>
       </c>
       <c r="C384" t="n">
         <v>-0.00161021912100856</v>
       </c>
       <c r="D384" t="n">
-        <v>-0.007924955177864956</v>
+        <v>-0.007925021904777063</v>
       </c>
     </row>
     <row r="385">
@@ -5829,13 +5829,13 @@
         <v>45652</v>
       </c>
       <c r="B385" t="n">
-        <v>-0.005070584497742225</v>
+        <v>-0.005070484313569934</v>
       </c>
       <c r="C385" t="n">
         <v>-0.004087635638419518</v>
       </c>
       <c r="D385" t="n">
-        <v>-0.0008643575431018791</v>
+        <v>-0.000864290341289764</v>
       </c>
     </row>
     <row r="386">
@@ -5849,7 +5849,7 @@
         <v>0.004188217402619765</v>
       </c>
       <c r="D386" t="n">
-        <v>0.004901971674011518</v>
+        <v>0.004901904355880227</v>
       </c>
     </row>
     <row r="387">
@@ -5857,13 +5857,13 @@
         <v>45656</v>
       </c>
       <c r="B387" t="n">
-        <v>-0.008476487007721301</v>
+        <v>-0.008476386172787898</v>
       </c>
       <c r="C387" t="n">
         <v>-0.01131656594057928</v>
       </c>
       <c r="D387" t="n">
-        <v>-0.005608515790522239</v>
+        <v>-0.005608382186727767</v>
       </c>
     </row>
     <row r="388">
@@ -5871,13 +5871,13 @@
         <v>45657</v>
       </c>
       <c r="B388" t="n">
-        <v>0.003923367267915978</v>
+        <v>0.003923265171965395</v>
       </c>
       <c r="C388" t="n">
-        <v>-0.002840438977185888</v>
+        <v>-0.002840508565087774</v>
       </c>
       <c r="D388" t="n">
-        <v>-0.01364105946300631</v>
+        <v>-0.013641193279195</v>
       </c>
     </row>
     <row r="389">
@@ -5888,10 +5888,10 @@
         <v>0.004771917014613658</v>
       </c>
       <c r="C389" t="n">
-        <v>0.005584146155594105</v>
+        <v>0.005584286117549908</v>
       </c>
       <c r="D389" t="n">
-        <v>0.001329786507454633</v>
+        <v>0.001329786598278204</v>
       </c>
     </row>
     <row r="390">
@@ -5902,10 +5902,10 @@
         <v>0.01682710072094262</v>
       </c>
       <c r="C390" t="n">
-        <v>0.006170298318180611</v>
+        <v>0.006170228491382268</v>
       </c>
       <c r="D390" t="n">
-        <v>0.04002655222544726</v>
+        <v>0.04002662316415817</v>
       </c>
     </row>
     <row r="391">
@@ -5913,13 +5913,13 @@
         <v>45660</v>
       </c>
       <c r="B391" t="n">
-        <v>0.007529353861090327</v>
+        <v>0.00752945301111696</v>
       </c>
       <c r="C391" t="n">
         <v>-0.02483628394118675</v>
       </c>
       <c r="D391" t="n">
-        <v>-0.009755541541096147</v>
+        <v>-0.009755607124568688</v>
       </c>
     </row>
     <row r="392">
@@ -5927,13 +5927,13 @@
         <v>45663</v>
       </c>
       <c r="B392" t="n">
-        <v>-0.02649555953674909</v>
+        <v>-0.02649575374746627</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.02212431192407482</v>
+        <v>-0.02212438265374617</v>
       </c>
       <c r="D392" t="n">
-        <v>-0.0004642693413878796</v>
+        <v>-0.0004642693721362834</v>
       </c>
     </row>
     <row r="393">
@@ -5941,13 +5941,13 @@
         <v>45664</v>
       </c>
       <c r="B393" t="n">
-        <v>0.01876011000739353</v>
+        <v>0.01876021299125341</v>
       </c>
       <c r="C393" t="n">
-        <v>0.001695341020026886</v>
+        <v>0.001695413472577068</v>
       </c>
       <c r="D393" t="n">
-        <v>-0.003612314987877063</v>
+        <v>-0.00361218270654029</v>
       </c>
     </row>
     <row r="394">
@@ -5961,7 +5961,7 @@
         <v>-0.01114732237242666</v>
       </c>
       <c r="D394" t="n">
-        <v>0.001191224559295767</v>
+        <v>0.001191157979521629</v>
       </c>
     </row>
     <row r="395">
@@ -5969,7 +5969,7 @@
         <v>45666</v>
       </c>
       <c r="B395" t="n">
-        <v>-0.008494666485831082</v>
+        <v>-0.008494763778998937</v>
       </c>
       <c r="C395" t="n">
         <v>-0.01564069391746248</v>
@@ -5983,13 +5983,13 @@
         <v>45667</v>
       </c>
       <c r="B396" t="n">
-        <v>-0.01024109342998425</v>
+        <v>-0.01024099630817799</v>
       </c>
       <c r="C396" t="n">
         <v>-0.006625543270068146</v>
       </c>
       <c r="D396" t="n">
-        <v>0.02589569741105313</v>
+        <v>0.02589576438158736</v>
       </c>
     </row>
     <row r="397">
@@ -6003,7 +6003,7 @@
         <v>-0.01563300789054567</v>
       </c>
       <c r="D397" t="n">
-        <v>-0.002414774758001892</v>
+        <v>-0.00241490516047993</v>
       </c>
     </row>
     <row r="398">
@@ -6017,7 +6017,7 @@
         <v>0.009657521848774886</v>
       </c>
       <c r="D398" t="n">
-        <v>-0.01128833051884148</v>
+        <v>-0.0112882658194442</v>
       </c>
     </row>
     <row r="399">
@@ -6028,7 +6028,7 @@
         <v>0.01085761847236366</v>
       </c>
       <c r="C399" t="n">
-        <v>-0.00215597673432566</v>
+        <v>-0.002155901597477028</v>
       </c>
       <c r="D399" t="n">
         <v>0.004948270309358849</v>
@@ -6042,7 +6042,7 @@
         <v>0.01138002114414349</v>
       </c>
       <c r="C400" t="n">
-        <v>0.005477639716709337</v>
+        <v>0.005477639304247495</v>
       </c>
       <c r="D400" t="n">
         <v>-0.01087376732774925</v>
@@ -6056,7 +6056,7 @@
         <v>0.02834697770128503</v>
       </c>
       <c r="C401" t="n">
-        <v>-0.00926122024099274</v>
+        <v>-0.009261294436401002</v>
       </c>
       <c r="D401" t="n">
         <v>-0.05859631970008738</v>
@@ -6070,10 +6070,10 @@
         <v>0.002380334717906996</v>
       </c>
       <c r="C402" t="n">
-        <v>0.008858957987167182</v>
+        <v>0.008859033576190889</v>
       </c>
       <c r="D402" t="n">
-        <v>-0.001184193970448999</v>
+        <v>-0.00118412324274364</v>
       </c>
     </row>
     <row r="403">
@@ -6084,10 +6084,10 @@
         <v>-0.02432111045111041</v>
       </c>
       <c r="C403" t="n">
-        <v>-0.005359553978894871</v>
+        <v>-0.005359553577328979</v>
       </c>
       <c r="D403" t="n">
-        <v>-0.006948738378760866</v>
+        <v>-0.006948808698264863</v>
       </c>
     </row>
     <row r="404">
@@ -6095,13 +6095,13 @@
         <v>45679</v>
       </c>
       <c r="B404" t="n">
-        <v>0.002669453763929797</v>
+        <v>0.00266935709712679</v>
       </c>
       <c r="C404" t="n">
-        <v>0.01439973978352405</v>
+        <v>0.01439966336981824</v>
       </c>
       <c r="D404" t="n">
-        <v>0.03096023932929159</v>
+        <v>0.03096016802223756</v>
       </c>
     </row>
     <row r="405">
@@ -6109,13 +6109,13 @@
         <v>45680</v>
       </c>
       <c r="B405" t="n">
-        <v>-0.01053167108029096</v>
+        <v>-0.01053167209564354</v>
       </c>
       <c r="C405" t="n">
         <v>-0.0006902436675249035</v>
       </c>
       <c r="D405" t="n">
-        <v>0.004847960027776876</v>
+        <v>0.004847960363089321</v>
       </c>
     </row>
     <row r="406">
@@ -6123,13 +6123,13 @@
         <v>45681</v>
       </c>
       <c r="B406" t="n">
-        <v>-0.01373004043869797</v>
+        <v>-0.01372994434088126</v>
       </c>
       <c r="C406" t="n">
         <v>-0.009069579141327888</v>
       </c>
       <c r="D406" t="n">
-        <v>0.005360634113181328</v>
+        <v>0.005360703314142734</v>
       </c>
     </row>
     <row r="407">
@@ -6143,7 +6143,7 @@
         <v>-0.01212276193736517</v>
       </c>
       <c r="D407" t="n">
-        <v>-0.02849983965506808</v>
+        <v>-0.02849977119010993</v>
       </c>
     </row>
     <row r="408">
@@ -6151,13 +6151,13 @@
         <v>45685</v>
       </c>
       <c r="B408" t="n">
-        <v>0.004107922914950768</v>
+        <v>0.004108023069107958</v>
       </c>
       <c r="C408" t="n">
-        <v>0.02491099582874678</v>
+        <v>0.02491107174010621</v>
       </c>
       <c r="D408" t="n">
-        <v>0.004253635883327833</v>
+        <v>0.004253565110124535</v>
       </c>
     </row>
     <row r="409">
@@ -6165,13 +6165,13 @@
         <v>45686</v>
       </c>
       <c r="B409" t="n">
-        <v>0.0008911166028169326</v>
+        <v>0.0008910167695281856</v>
       </c>
       <c r="C409" t="n">
-        <v>0.004130751303307534</v>
+        <v>0.004130676931069166</v>
       </c>
       <c r="D409" t="n">
-        <v>0.02814590577287834</v>
+        <v>0.02814583559793715</v>
       </c>
     </row>
     <row r="410">
@@ -6182,10 +6182,10 @@
         <v>0.01420481101409754</v>
       </c>
       <c r="C410" t="n">
-        <v>0.008465988045161854</v>
+        <v>0.008466061806765346</v>
       </c>
       <c r="D410" t="n">
-        <v>-0.01132229390623274</v>
+        <v>-0.01132229467902313</v>
       </c>
     </row>
     <row r="411">
@@ -6196,10 +6196,10 @@
         <v>0.0096164947627011</v>
       </c>
       <c r="C411" t="n">
-        <v>0.004286143527001629</v>
+        <v>0.004286070071127357</v>
       </c>
       <c r="D411" t="n">
-        <v>0.01067233825634784</v>
+        <v>0.01067240802863756</v>
       </c>
     </row>
     <row r="412">
@@ -6210,10 +6210,10 @@
         <v>-0.0003952324898430781</v>
       </c>
       <c r="C412" t="n">
-        <v>-0.004591654064610928</v>
+        <v>-0.004591581234390629</v>
       </c>
       <c r="D412" t="n">
-        <v>-0.01513453994531377</v>
+        <v>-0.01513460825183799</v>
       </c>
     </row>
     <row r="413">
@@ -6224,10 +6224,10 @@
         <v>-0.01478720860403326</v>
       </c>
       <c r="C413" t="n">
-        <v>-0.007658376597711403</v>
+        <v>-0.007658449203545969</v>
       </c>
       <c r="D413" t="n">
-        <v>0.006454703952373908</v>
+        <v>0.006454843112454034</v>
       </c>
     </row>
     <row r="414">
@@ -6241,7 +6241,7 @@
         <v>0.02556623989048901</v>
       </c>
       <c r="D414" t="n">
-        <v>0.01905220920286887</v>
+        <v>0.01905220788995465</v>
       </c>
     </row>
     <row r="415">
@@ -6255,7 +6255,7 @@
         <v>0.009820413213954771</v>
       </c>
       <c r="D415" t="n">
-        <v>-0.0009216342430028446</v>
+        <v>-0.0009217018037021019</v>
       </c>
     </row>
     <row r="416">
@@ -6269,7 +6269,7 @@
         <v>0.003481369617795549</v>
       </c>
       <c r="D416" t="n">
-        <v>0.009804772944896678</v>
+        <v>0.009804705259487845</v>
       </c>
     </row>
     <row r="417">
@@ -6280,10 +6280,10 @@
         <v>-0.01158756678390982</v>
       </c>
       <c r="C417" t="n">
-        <v>-0.006365263493061657</v>
+        <v>-0.006365192546400555</v>
       </c>
       <c r="D417" t="n">
-        <v>-0.006264255643993355</v>
+        <v>-0.006264189035658396</v>
       </c>
     </row>
     <row r="418">
@@ -6294,7 +6294,7 @@
         <v>-0.01030233399041214</v>
       </c>
       <c r="C418" t="n">
-        <v>-0.009810946181598723</v>
+        <v>-0.009811088283372293</v>
       </c>
       <c r="D418" t="n">
         <v>-0.01226591726195314</v>
@@ -6308,7 +6308,7 @@
         <v>-0.01499621389573924</v>
       </c>
       <c r="C419" t="n">
-        <v>-0.008363660408577389</v>
+        <v>-0.008363661011669299</v>
       </c>
       <c r="D419" t="n">
         <v>-0.002472994684980301</v>
@@ -6322,7 +6322,7 @@
         <v>-0.01481960966486229</v>
       </c>
       <c r="C420" t="n">
-        <v>0.003173869312238953</v>
+        <v>0.003173869543032559</v>
       </c>
       <c r="D420" t="n">
         <v>-0.006664352797898676</v>
@@ -6333,13 +6333,13 @@
         <v>45701</v>
       </c>
       <c r="B421" t="n">
-        <v>-0.0003700161801112323</v>
+        <v>-0.0003699149721845263</v>
       </c>
       <c r="C421" t="n">
-        <v>-0.005331687981506628</v>
+        <v>-0.005331615881260965</v>
       </c>
       <c r="D421" t="n">
-        <v>-0.01068088561028024</v>
+        <v>-0.01068081669333754</v>
       </c>
     </row>
     <row r="422">
@@ -6347,13 +6347,13 @@
         <v>45702</v>
       </c>
       <c r="B422" t="n">
-        <v>0.0009457331801288049</v>
+        <v>0.0009456318389988727</v>
       </c>
       <c r="C422" t="n">
         <v>-0.001678754608358535</v>
       </c>
       <c r="D422" t="n">
-        <v>0.007134120660347021</v>
+        <v>0.007134120163377222</v>
       </c>
     </row>
     <row r="423">
@@ -6361,13 +6361,13 @@
         <v>45705</v>
       </c>
       <c r="B423" t="n">
-        <v>0.006284736081139775</v>
+        <v>0.006284634931411404</v>
       </c>
       <c r="C423" t="n">
         <v>0.01327552782709396</v>
       </c>
       <c r="D423" t="n">
-        <v>-0.00759528692422351</v>
+        <v>-0.007595424733935041</v>
       </c>
     </row>
     <row r="424">
@@ -6375,13 +6375,13 @@
         <v>45706</v>
       </c>
       <c r="B424" t="n">
-        <v>0.0004082035955892405</v>
+        <v>0.0004083041546305566</v>
       </c>
       <c r="C424" t="n">
         <v>0.003319092425039027</v>
       </c>
       <c r="D424" t="n">
-        <v>0.005238000981332425</v>
+        <v>0.005238071043311754</v>
       </c>
     </row>
     <row r="425">
@@ -6389,7 +6389,7 @@
         <v>45707</v>
       </c>
       <c r="B425" t="n">
-        <v>0.001672740835293229</v>
+        <v>0.00167284131227774</v>
       </c>
       <c r="C425" t="n">
         <v>0.002408491434787496</v>
@@ -6403,7 +6403,7 @@
         <v>45708</v>
       </c>
       <c r="B426" t="n">
-        <v>0.004521637495415787</v>
+        <v>0.004521536732671194</v>
       </c>
       <c r="C426" t="n">
         <v>-0.02321676029499764</v>
@@ -6431,13 +6431,13 @@
         <v>45712</v>
       </c>
       <c r="B428" t="n">
-        <v>-0.01107343640443348</v>
+        <v>-0.01107353665644695</v>
       </c>
       <c r="C428" t="n">
-        <v>-0.00909894534719069</v>
+        <v>-0.009099018446354745</v>
       </c>
       <c r="D428" t="n">
-        <v>-0.02804411984328237</v>
+        <v>-0.02804404909804414</v>
       </c>
     </row>
     <row r="429">
@@ -6445,13 +6445,13 @@
         <v>45713</v>
       </c>
       <c r="B429" t="n">
-        <v>-0.008686382129851511</v>
+        <v>-0.008686383010429899</v>
       </c>
       <c r="C429" t="n">
-        <v>0.003130373020749477</v>
+        <v>0.003130447022080762</v>
       </c>
       <c r="D429" t="n">
-        <v>0.002040714276927869</v>
+        <v>0.002040641341926275</v>
       </c>
     </row>
     <row r="430">
@@ -6459,13 +6459,13 @@
         <v>45715</v>
       </c>
       <c r="B430" t="n">
-        <v>0.00257467234975528</v>
+        <v>0.002574774875932162</v>
       </c>
       <c r="C430" t="n">
-        <v>0.01090733369971053</v>
+        <v>0.01090740723989914</v>
       </c>
       <c r="D430" t="n">
-        <v>-0.001923387870605753</v>
+        <v>-0.001923315232368994</v>
       </c>
     </row>
     <row r="431">
@@ -6476,10 +6476,10 @@
         <v>-0.005799020532345489</v>
       </c>
       <c r="C431" t="n">
-        <v>0.01863945454512383</v>
+        <v>0.01863938044245428</v>
       </c>
       <c r="D431" t="n">
-        <v>-0.04341664619779295</v>
+        <v>-0.04341664303800707</v>
       </c>
     </row>
     <row r="432">
@@ -6490,10 +6490,10 @@
         <v>-0.02403969859990374</v>
       </c>
       <c r="C432" t="n">
-        <v>-0.01780761488497562</v>
+        <v>-0.0178076863005443</v>
       </c>
       <c r="D432" t="n">
-        <v>0.01238377232057597</v>
+        <v>0.01238369529698957</v>
       </c>
     </row>
     <row r="433">
@@ -6504,10 +6504,10 @@
         <v>-0.007982883563999676</v>
       </c>
       <c r="C433" t="n">
-        <v>0.004965972638943494</v>
+        <v>0.004966045710393496</v>
       </c>
       <c r="D433" t="n">
-        <v>-0.01188111088465682</v>
+        <v>-0.01188103573388932</v>
       </c>
     </row>
     <row r="434">
@@ -6515,13 +6515,13 @@
         <v>45721</v>
       </c>
       <c r="B434" t="n">
-        <v>0.01179098102119269</v>
+        <v>0.01179108698944109</v>
       </c>
       <c r="C434" t="n">
         <v>-0.01169591277933391</v>
       </c>
       <c r="D434" t="n">
-        <v>0.01374165711994091</v>
+        <v>0.01374158002045567</v>
       </c>
     </row>
     <row r="435">
@@ -6529,7 +6529,7 @@
         <v>45722</v>
       </c>
       <c r="B435" t="n">
-        <v>0.02892137856724375</v>
+        <v>0.02892137553821139</v>
       </c>
       <c r="C435" t="n">
         <v>0.00071003759926902</v>
@@ -6543,13 +6543,13 @@
         <v>45723</v>
       </c>
       <c r="B436" t="n">
-        <v>0.03323425487731768</v>
+        <v>0.03323414970498373</v>
       </c>
       <c r="C436" t="n">
         <v>-0.001153001575254331</v>
       </c>
       <c r="D436" t="n">
-        <v>-0.01739663247436252</v>
+        <v>-0.01739655764112469</v>
       </c>
     </row>
     <row r="437">
@@ -6557,13 +6557,13 @@
         <v>45726</v>
       </c>
       <c r="B437" t="n">
-        <v>-0.0091214390020945</v>
+        <v>-0.009121537517458145</v>
       </c>
       <c r="C437" t="n">
         <v>-0.001035977002116217</v>
       </c>
       <c r="D437" t="n">
-        <v>0.009163727343526551</v>
+        <v>0.009163650487507224</v>
       </c>
     </row>
     <row r="438">
@@ -6571,7 +6571,7 @@
         <v>45727</v>
       </c>
       <c r="B438" t="n">
-        <v>0.007186637014978459</v>
+        <v>0.007186737151737566</v>
       </c>
       <c r="C438" t="n">
         <v>-0.001185149189864565</v>
@@ -6585,13 +6585,13 @@
         <v>45728</v>
       </c>
       <c r="B439" t="n">
-        <v>0.007816969840073407</v>
+        <v>0.007816871127249048</v>
       </c>
       <c r="C439" t="n">
-        <v>0.01521807809876319</v>
+        <v>0.0152180046960142</v>
       </c>
       <c r="D439" t="n">
-        <v>-0.04257942110175095</v>
+        <v>-0.04257949837823705</v>
       </c>
     </row>
     <row r="440">
@@ -6599,13 +6599,13 @@
         <v>45729</v>
       </c>
       <c r="B440" t="n">
-        <v>-0.007279042194173413</v>
+        <v>-0.007278847012767597</v>
       </c>
       <c r="C440" t="n">
-        <v>-0.002659139307361391</v>
+        <v>-0.002658994894723987</v>
       </c>
       <c r="D440" t="n">
-        <v>-0.006914539079963089</v>
+        <v>-0.006914458924843436</v>
       </c>
     </row>
     <row r="441">
@@ -6613,10 +6613,10 @@
         <v>45733</v>
       </c>
       <c r="B441" t="n">
-        <v>-0.007252200212939597</v>
+        <v>-0.007252396828106189</v>
       </c>
       <c r="C441" t="n">
-        <v>0.002226763161670142</v>
+        <v>0.002226618009812054</v>
       </c>
       <c r="D441" t="n">
         <v>0.006456338399974282</v>
@@ -6641,13 +6641,13 @@
         <v>45735</v>
       </c>
       <c r="B443" t="n">
-        <v>0.006699817904729732</v>
+        <v>0.006699917956740187</v>
       </c>
       <c r="C443" t="n">
-        <v>0.01970295403258904</v>
+        <v>0.01970302779193922</v>
       </c>
       <c r="D443" t="n">
-        <v>-0.002201106714873502</v>
+        <v>-0.002201187468687693</v>
       </c>
     </row>
     <row r="444">
@@ -6655,13 +6655,13 @@
         <v>45736</v>
       </c>
       <c r="B444" t="n">
-        <v>0.01764012835000028</v>
+        <v>0.01764022707469448</v>
       </c>
       <c r="C444" t="n">
-        <v>0.01413331534383944</v>
+        <v>0.01413338628032945</v>
       </c>
       <c r="D444" t="n">
-        <v>0.01827864370022847</v>
+        <v>0.0182787261115156</v>
       </c>
     </row>
     <row r="445">
@@ -6669,13 +6669,13 @@
         <v>45737</v>
       </c>
       <c r="B445" t="n">
-        <v>0.005673147612239138</v>
+        <v>0.005672953035154915</v>
       </c>
       <c r="C445" t="n">
-        <v>0.0009046361184625873</v>
+        <v>0.0009045661072957234</v>
       </c>
       <c r="D445" t="n">
-        <v>-0.01423678803641193</v>
+        <v>-0.01423662907804701</v>
       </c>
     </row>
     <row r="446">
@@ -6683,13 +6683,13 @@
         <v>45740</v>
       </c>
       <c r="B446" t="n">
-        <v>0.02017472711669765</v>
+        <v>0.0201747290628751</v>
       </c>
       <c r="C446" t="n">
         <v>0.01674807182942484</v>
       </c>
       <c r="D446" t="n">
-        <v>0.0001256975751817713</v>
+        <v>0.0001254556737932955</v>
       </c>
     </row>
     <row r="447">
@@ -6697,13 +6697,13 @@
         <v>45741</v>
       </c>
       <c r="B447" t="n">
-        <v>-0.01278703914358825</v>
+        <v>-0.01278694579429218</v>
       </c>
       <c r="C447" t="n">
         <v>0.01191667407843133</v>
       </c>
       <c r="D447" t="n">
-        <v>0.02241400270743865</v>
+        <v>0.02241408513131238</v>
       </c>
     </row>
     <row r="448">
@@ -6717,7 +6717,7 @@
         <v>-0.008180234130266362</v>
       </c>
       <c r="D448" t="n">
-        <v>-0.01780841522191234</v>
+        <v>-0.0178083363723277</v>
       </c>
     </row>
     <row r="449">
@@ -6731,7 +6731,7 @@
         <v>0.01040653312911322</v>
       </c>
       <c r="D449" t="n">
-        <v>0.002563476386105101</v>
+        <v>0.00256339590108734</v>
       </c>
     </row>
     <row r="450">
@@ -6742,10 +6742,10 @@
         <v>-0.002425308203808707</v>
       </c>
       <c r="C450" t="n">
-        <v>0.001561288451006559</v>
+        <v>0.001561356229971222</v>
       </c>
       <c r="D450" t="n">
-        <v>-0.0205170311713524</v>
+        <v>-0.0205169510973896</v>
       </c>
     </row>
     <row r="451">
@@ -6756,10 +6756,10 @@
         <v>-0.01764569050199283</v>
       </c>
       <c r="C451" t="n">
-        <v>-0.03301056549507253</v>
+        <v>-0.03301063093444112</v>
       </c>
       <c r="D451" t="n">
-        <v>-0.02810935178775276</v>
+        <v>-0.02810943124102727</v>
       </c>
     </row>
     <row r="452">
@@ -6767,13 +6767,13 @@
         <v>45749</v>
       </c>
       <c r="B452" t="n">
-        <v>-0.001157523791606052</v>
+        <v>-0.00115742549644704</v>
       </c>
       <c r="C452" t="n">
         <v>0.01643240622455666</v>
       </c>
       <c r="D452" t="n">
-        <v>0.01549310133552173</v>
+        <v>0.01549301721982821</v>
       </c>
     </row>
     <row r="453">
@@ -6781,13 +6781,13 @@
         <v>45750</v>
       </c>
       <c r="B453" t="n">
-        <v>-0.001958242079422967</v>
+        <v>-0.001958241886714229</v>
       </c>
       <c r="C453" t="n">
         <v>-0.0011408792385178</v>
       </c>
       <c r="D453" t="n">
-        <v>-0.03460968065142023</v>
+        <v>-0.03460968351822213</v>
       </c>
     </row>
     <row r="454">
@@ -6795,13 +6795,13 @@
         <v>45751</v>
       </c>
       <c r="B454" t="n">
-        <v>-0.0352366639104077</v>
+        <v>-0.03523675903814394</v>
       </c>
       <c r="C454" t="n">
-        <v>0.01250810280826586</v>
+        <v>0.01250803387752764</v>
       </c>
       <c r="D454" t="n">
-        <v>-0.02996993156780392</v>
+        <v>-0.02996976253538575</v>
       </c>
     </row>
     <row r="455">
@@ -6809,13 +6809,13 @@
         <v>45754</v>
       </c>
       <c r="B455" t="n">
-        <v>-0.0323731522124393</v>
+        <v>-0.03237325441590511</v>
       </c>
       <c r="C455" t="n">
-        <v>-0.03279606366085663</v>
+        <v>-0.03279599781438536</v>
       </c>
       <c r="D455" t="n">
-        <v>-0.03781899642084319</v>
+        <v>-0.03781916998136392</v>
       </c>
     </row>
     <row r="456">
@@ -6823,13 +6823,13 @@
         <v>45755</v>
       </c>
       <c r="B456" t="n">
-        <v>0.01415461827283049</v>
+        <v>0.01415472539070151</v>
       </c>
       <c r="C456" t="n">
         <v>0.006514305125184139</v>
       </c>
       <c r="D456" t="n">
-        <v>0.02294616743404854</v>
+        <v>0.02294616954347961</v>
       </c>
     </row>
     <row r="457">
@@ -6843,7 +6843,7 @@
         <v>-0.002345801522980695</v>
       </c>
       <c r="D457" t="n">
-        <v>-0.0175672866711043</v>
+        <v>-0.01756719838238596</v>
       </c>
     </row>
     <row r="458">
@@ -6868,7 +6868,7 @@
         <v>0.01735106601006997</v>
       </c>
       <c r="C459" t="n">
-        <v>0.03218488498066319</v>
+        <v>0.0321848165039329</v>
       </c>
       <c r="D459" t="n">
         <v>0.01174221781535278</v>
@@ -6882,10 +6882,10 @@
         <v>-0.0006450607873236258</v>
       </c>
       <c r="C460" t="n">
-        <v>0.00702450716034142</v>
+        <v>0.007024507626357979</v>
       </c>
       <c r="D460" t="n">
-        <v>-0.00904635045770219</v>
+        <v>-0.009046260413802187</v>
       </c>
     </row>
     <row r="461">
@@ -6896,10 +6896,10 @@
         <v>0.02840308136111935</v>
       </c>
       <c r="C461" t="n">
-        <v>0.01528216173541019</v>
+        <v>0.01528216274218019</v>
       </c>
       <c r="D461" t="n">
-        <v>0.004529120159982192</v>
+        <v>0.004529028882543029</v>
       </c>
     </row>
     <row r="462">
@@ -6907,10 +6907,10 @@
         <v>45768</v>
       </c>
       <c r="B462" t="n">
-        <v>0.01647704334262579</v>
+        <v>0.01647694673650513</v>
       </c>
       <c r="C462" t="n">
-        <v>0.01069911301207394</v>
+        <v>0.01069917859346714</v>
       </c>
       <c r="D462" t="n">
         <v>0.02219090024922488</v>
@@ -6921,13 +6921,13 @@
         <v>45769</v>
       </c>
       <c r="B463" t="n">
-        <v>-0.003319276896597279</v>
+        <v>-0.003319087131763432</v>
       </c>
       <c r="C463" t="n">
         <v>0.01795443950951259</v>
       </c>
       <c r="D463" t="n">
-        <v>-0.01943480908718753</v>
+        <v>-0.01943489757967731</v>
       </c>
     </row>
     <row r="464">
@@ -6935,13 +6935,13 @@
         <v>45770</v>
       </c>
       <c r="B464" t="n">
-        <v>0.006815426227561927</v>
+        <v>0.006815330221019433</v>
       </c>
       <c r="C464" t="n">
-        <v>-0.01926901507209733</v>
+        <v>-0.01926895200417866</v>
       </c>
       <c r="D464" t="n">
-        <v>0.03661784245557609</v>
+        <v>0.03661793600662477</v>
       </c>
     </row>
     <row r="465">
@@ -6952,10 +6952,10 @@
         <v>0.001230771503837103</v>
       </c>
       <c r="C465" t="n">
-        <v>-0.003690388809441059</v>
+        <v>-0.003690452879171247</v>
       </c>
       <c r="D465" t="n">
-        <v>-0.002372953983392878</v>
+        <v>-0.002373041041909385</v>
       </c>
     </row>
     <row r="466">
@@ -6969,7 +6969,7 @@
         <v>-0.002921576166589168</v>
       </c>
       <c r="D466" t="n">
-        <v>0.005980660199122578</v>
+        <v>0.00598066072102843</v>
       </c>
     </row>
     <row r="467">
@@ -6977,13 +6977,13 @@
         <v>45775</v>
       </c>
       <c r="B467" t="n">
-        <v>0.05259917776237399</v>
+        <v>0.05259927244439733</v>
       </c>
       <c r="C467" t="n">
         <v>0.004709102164633272</v>
       </c>
       <c r="D467" t="n">
-        <v>0.001283505514146466</v>
+        <v>0.001283592372284703</v>
       </c>
     </row>
     <row r="468">
@@ -6991,10 +6991,10 @@
         <v>45776</v>
       </c>
       <c r="B468" t="n">
-        <v>0.0225744751242265</v>
+        <v>0.02257438314295412</v>
       </c>
       <c r="C468" t="n">
-        <v>-0.005936862294536049</v>
+        <v>-0.005936797863572374</v>
       </c>
       <c r="D468" t="n">
         <v>0.01039072652608608</v>
@@ -7008,10 +7008,10 @@
         <v>0.003786538322317012</v>
       </c>
       <c r="C469" t="n">
-        <v>0.008486976406088864</v>
+        <v>0.008486911040237244</v>
       </c>
       <c r="D469" t="n">
-        <v>0.001736243300771045</v>
+        <v>0.001736157556126772</v>
       </c>
     </row>
     <row r="470">
@@ -7022,10 +7022,10 @@
         <v>0.01053384946893909</v>
       </c>
       <c r="C470" t="n">
-        <v>-0.001610292503800737</v>
+        <v>-0.001610356774106259</v>
       </c>
       <c r="D470" t="n">
-        <v>0.004533080083216401</v>
+        <v>0.004533080471230244</v>
       </c>
     </row>
     <row r="471">
@@ -7036,10 +7036,10 @@
         <v>0.008099785134819015</v>
       </c>
       <c r="C471" t="n">
-        <v>0.007752685520943103</v>
+        <v>0.007752750393984709</v>
       </c>
       <c r="D471" t="n">
-        <v>0.001128092091988275</v>
+        <v>0.001128177397886176</v>
       </c>
     </row>
     <row r="472">
@@ -7064,10 +7064,10 @@
         <v>-0.0104863361608325</v>
       </c>
       <c r="C473" t="n">
-        <v>0.00719578819246669</v>
+        <v>0.007195724145077742</v>
       </c>
       <c r="D473" t="n">
-        <v>-0.002117135117428726</v>
+        <v>-0.002117050166978607</v>
       </c>
     </row>
     <row r="474">
@@ -7078,10 +7078,10 @@
         <v>0.0007112498232164643</v>
       </c>
       <c r="C474" t="n">
-        <v>-0.008789065604971169</v>
+        <v>-0.008789002574052129</v>
       </c>
       <c r="D474" t="n">
-        <v>0.002055395216643108</v>
+        <v>0.0020553099109899</v>
       </c>
     </row>
     <row r="475">
@@ -7089,7 +7089,7 @@
         <v>45786</v>
       </c>
       <c r="B475" t="n">
-        <v>-0.021179777793082</v>
+        <v>-0.0211798653016152</v>
       </c>
       <c r="C475" t="n">
         <v>-0.02011929373234767</v>
@@ -7103,13 +7103,13 @@
         <v>45789</v>
       </c>
       <c r="B476" t="n">
-        <v>0.04305835110795075</v>
+        <v>0.04305835495745569</v>
       </c>
       <c r="C476" t="n">
-        <v>0.03572000038758771</v>
+        <v>0.03571993491669878</v>
       </c>
       <c r="D476" t="n">
-        <v>0.07913232000660919</v>
+        <v>0.07913240517681541</v>
       </c>
     </row>
     <row r="477">
@@ -7117,13 +7117,13 @@
         <v>45790</v>
       </c>
       <c r="B477" t="n">
-        <v>-0.01447966461450589</v>
+        <v>-0.01447966585557914</v>
       </c>
       <c r="C477" t="n">
-        <v>-0.01767837896779623</v>
+        <v>-0.01767825365944375</v>
       </c>
       <c r="D477" t="n">
-        <v>-0.03583497569079441</v>
+        <v>-0.03583505178723412</v>
       </c>
     </row>
     <row r="478">
@@ -7131,13 +7131,13 @@
         <v>45791</v>
       </c>
       <c r="B478" t="n">
-        <v>0.006145354061017017</v>
+        <v>0.006145528537022882</v>
       </c>
       <c r="C478" t="n">
-        <v>-0.006241487228413334</v>
+        <v>-0.006241551177302629</v>
       </c>
       <c r="D478" t="n">
-        <v>0.01517272507967449</v>
+        <v>0.01517280693776812</v>
       </c>
     </row>
     <row r="479">
@@ -7145,13 +7145,13 @@
         <v>45792</v>
       </c>
       <c r="B479" t="n">
-        <v>0.02092113971943621</v>
+        <v>0.02092105147146905</v>
       </c>
       <c r="C479" t="n">
         <v>0.01214280173133342</v>
       </c>
       <c r="D479" t="n">
-        <v>0.01293653884005619</v>
+        <v>0.01293637652764335</v>
       </c>
     </row>
     <row r="480">
@@ -7165,7 +7165,7 @@
         <v>0.0004653747495106941</v>
       </c>
       <c r="D480" t="n">
-        <v>-0.01432114867229883</v>
+        <v>-0.01432107020749007</v>
       </c>
     </row>
     <row r="481">
@@ -7179,7 +7179,7 @@
         <v>0.002067505119682567</v>
       </c>
       <c r="D481" t="n">
-        <v>-0.01893201405765788</v>
+        <v>-0.01893209481908953</v>
       </c>
     </row>
     <row r="482">
@@ -7187,13 +7187,13 @@
         <v>45797</v>
       </c>
       <c r="B482" t="n">
-        <v>-0.01124374208253376</v>
+        <v>-0.01124382753818676</v>
       </c>
       <c r="C482" t="n">
         <v>-0.01227624548508843</v>
       </c>
       <c r="D482" t="n">
-        <v>0.0005127707409344762</v>
+        <v>0.0005128531030658134</v>
       </c>
     </row>
     <row r="483">
@@ -7201,13 +7201,13 @@
         <v>45798</v>
       </c>
       <c r="B483" t="n">
-        <v>0.003228928433082867</v>
+        <v>0.003228928712150969</v>
       </c>
       <c r="C483" t="n">
         <v>0.006214444699292221</v>
       </c>
       <c r="D483" t="n">
-        <v>0.00506230151527598</v>
+        <v>0.005062219237552013</v>
       </c>
     </row>
     <row r="484">
@@ -7215,13 +7215,13 @@
         <v>45799</v>
       </c>
       <c r="B484" t="n">
-        <v>-0.01385383332290924</v>
+        <v>-0.01385374836714848</v>
       </c>
       <c r="C484" t="n">
         <v>-0.003581070429987232</v>
       </c>
       <c r="D484" t="n">
-        <v>-0.01338866201382916</v>
+        <v>-0.01338858124655562</v>
       </c>
     </row>
     <row r="485">
@@ -7232,7 +7232,7 @@
         <v>0.01234573401648476</v>
       </c>
       <c r="C485" t="n">
-        <v>0.007135748376859485</v>
+        <v>0.007135683935831194</v>
       </c>
       <c r="D485" t="n">
         <v>0.01117936570522771</v>
@@ -7246,10 +7246,10 @@
         <v>0.005606876125006099</v>
       </c>
       <c r="C486" t="n">
-        <v>0.003413250552809721</v>
+        <v>0.00341337874011538</v>
       </c>
       <c r="D486" t="n">
-        <v>0.01003317641596735</v>
+        <v>0.01003309435909028</v>
       </c>
     </row>
     <row r="487">
@@ -7260,10 +7260,10 @@
         <v>-0.008851440092437768</v>
       </c>
       <c r="C487" t="n">
-        <v>-0.007164136123751441</v>
+        <v>-0.007164135666917426</v>
       </c>
       <c r="D487" t="n">
-        <v>-0.006580176684588546</v>
+        <v>-0.006580095977403055</v>
       </c>
     </row>
     <row r="488">
@@ -7271,10 +7271,10 @@
         <v>45805</v>
       </c>
       <c r="B488" t="n">
-        <v>-0.006469296318463824</v>
+        <v>-0.006469209739104365</v>
       </c>
       <c r="C488" t="n">
-        <v>-0.001453583872309649</v>
+        <v>-0.00145358377895044</v>
       </c>
       <c r="D488" t="n">
         <v>0.00108276574681998</v>
@@ -7285,10 +7285,10 @@
         <v>45806</v>
       </c>
       <c r="B489" t="n">
-        <v>0.003468121654575773</v>
+        <v>0.003468034209246351</v>
       </c>
       <c r="C489" t="n">
-        <v>0.002079543654304405</v>
+        <v>0.002079479200126633</v>
       </c>
       <c r="D489" t="n">
         <v>0.008779705559551543</v>
@@ -7302,7 +7302,7 @@
         <v>0.002186419414939023</v>
       </c>
       <c r="C490" t="n">
-        <v>0.009027251979717876</v>
+        <v>0.009027316166663191</v>
       </c>
       <c r="D490" t="n">
         <v>-0.0005756090600607111</v>
@@ -7316,7 +7316,7 @@
         <v>-0.005067263552035794</v>
       </c>
       <c r="C491" t="n">
-        <v>-0.006581369672977289</v>
+        <v>-0.006581369254318625</v>
       </c>
       <c r="D491" t="n">
         <v>-0.005695232309131937</v>
@@ -7327,10 +7327,10 @@
         <v>45811</v>
       </c>
       <c r="B492" t="n">
-        <v>-0.005800273178426574</v>
+        <v>-0.005800360272230853</v>
       </c>
       <c r="C492" t="n">
-        <v>-0.00388174894113158</v>
+        <v>-0.003881812726692857</v>
       </c>
       <c r="D492" t="n">
         <v>-0.006950710778507507</v>
@@ -7341,10 +7341,10 @@
         <v>45812</v>
       </c>
       <c r="B493" t="n">
-        <v>0.01280678739671193</v>
+        <v>0.01280678851861117</v>
       </c>
       <c r="C493" t="n">
-        <v>0.008625131877934011</v>
+        <v>0.008625196161596849</v>
       </c>
       <c r="D493" t="n">
         <v>0.005314308611814145</v>
@@ -7355,10 +7355,10 @@
         <v>45813</v>
       </c>
       <c r="B494" t="n">
-        <v>0.01327712017193661</v>
+        <v>0.01327720781454467</v>
       </c>
       <c r="C494" t="n">
-        <v>0.004327216467577832</v>
+        <v>0.004327216191787109</v>
       </c>
       <c r="D494" t="n">
         <v>0.001998493314153027</v>
@@ -7369,10 +7369,10 @@
         <v>45814</v>
       </c>
       <c r="B495" t="n">
-        <v>0.0007626139236709406</v>
+        <v>0.0007625285628107825</v>
       </c>
       <c r="C495" t="n">
-        <v>0.01492614601234155</v>
+        <v>0.01492608160579545</v>
       </c>
       <c r="D495" t="n">
         <v>0.006112073665204276</v>
@@ -7383,10 +7383,10 @@
         <v>45817</v>
       </c>
       <c r="B496" t="n">
-        <v>0.003671643535153146</v>
+        <v>0.003671729144148594</v>
       </c>
       <c r="C496" t="n">
-        <v>0.0001011671867168218</v>
+        <v>0.0001011046606433919</v>
       </c>
       <c r="D496" t="n">
         <v>0.005819158641383382</v>
@@ -7400,7 +7400,7 @@
         <v>-0.007109403277025583</v>
       </c>
       <c r="C497" t="n">
-        <v>-0.006872483345676805</v>
+        <v>-0.0068724212555904</v>
       </c>
       <c r="D497" t="n">
         <v>0.01468623640095834</v>
@@ -7414,7 +7414,7 @@
         <v>0.007229809741173154</v>
       </c>
       <c r="C498" t="n">
-        <v>-0.007581607855601802</v>
+        <v>-0.007581544903214166</v>
       </c>
       <c r="D498" t="n">
         <v>0.02199239147224796</v>
@@ -7425,10 +7425,10 @@
         <v>45820</v>
       </c>
       <c r="B499" t="n">
-        <v>-0.005038255784043266</v>
+        <v>-0.005038340761961302</v>
       </c>
       <c r="C499" t="n">
-        <v>-0.003588993482671055</v>
+        <v>-0.003589056688319436</v>
       </c>
       <c r="D499" t="n">
         <v>-0.01379424914869842</v>
@@ -7439,7 +7439,7 @@
         <v>45821</v>
       </c>
       <c r="B500" t="n">
-        <v>-0.009503373368724199</v>
+        <v>-0.009503288772156671</v>
       </c>
       <c r="C500" t="n">
         <v>-0.01327571261741145</v>
@@ -7453,7 +7453,7 @@
         <v>45824</v>
       </c>
       <c r="B501" t="n">
-        <v>0.006933309097606699</v>
+        <v>0.006933222869926148</v>
       </c>
       <c r="C501" t="n">
         <v>0.009282444635375642</v>
@@ -7467,7 +7467,7 @@
         <v>45825</v>
       </c>
       <c r="B502" t="n">
-        <v>-0.004590408089462872</v>
+        <v>-0.004590408482557651</v>
       </c>
       <c r="C502" t="n">
         <v>-0.00299680132370661</v>
@@ -7481,7 +7481,7 @@
         <v>45826</v>
       </c>
       <c r="B503" t="n">
-        <v>-0.0007685818469123085</v>
+        <v>-0.0007684958841638334</v>
       </c>
       <c r="C503" t="n">
         <v>0.002228453548387188</v>
@@ -7495,7 +7495,7 @@
         <v>45827</v>
       </c>
       <c r="B504" t="n">
-        <v>0.002237695986731625</v>
+        <v>0.00223760989169941</v>
       </c>
       <c r="C504" t="n">
         <v>0.0007239357230035548</v>
@@ -7509,7 +7509,7 @@
         <v>45828</v>
       </c>
       <c r="B505" t="n">
-        <v>0.02295391752454212</v>
+        <v>0.0229540053991637</v>
       </c>
       <c r="C505" t="n">
         <v>0.01519139669023017</v>
@@ -7526,7 +7526,7 @@
         <v>-0.006411090241396078</v>
       </c>
       <c r="C506" t="n">
-        <v>-0.008296384736435458</v>
+        <v>-0.008296447708053489</v>
       </c>
       <c r="D506" t="n">
         <v>-0.02396944180168414</v>
@@ -7537,10 +7537,10 @@
         <v>45832</v>
       </c>
       <c r="B507" t="n">
-        <v>-0.00411860249971141</v>
+        <v>-0.004118687016805178</v>
       </c>
       <c r="C507" t="n">
-        <v>0.006415499914848688</v>
+        <v>0.006415563820652226</v>
       </c>
       <c r="D507" t="n">
         <v>-0.001515215707403095</v>
@@ -7551,7 +7551,7 @@
         <v>45833</v>
       </c>
       <c r="B508" t="n">
-        <v>0.01137306138106009</v>
+        <v>0.0113731472128864</v>
       </c>
       <c r="C508" t="n">
         <v>0.009842419828163251</v>
@@ -7565,10 +7565,10 @@
         <v>45834</v>
       </c>
       <c r="B509" t="n">
-        <v>0.01908266081831589</v>
+        <v>0.01908257690602988</v>
       </c>
       <c r="C509" t="n">
-        <v>0.02100796522285253</v>
+        <v>0.02100802770155896</v>
       </c>
       <c r="D509" t="n">
         <v>0.0006812084707270571</v>
@@ -7579,10 +7579,10 @@
         <v>45835</v>
       </c>
       <c r="B510" t="n">
-        <v>0.0134420860335005</v>
+        <v>0.01344208714033557</v>
       </c>
       <c r="C510" t="n">
-        <v>0.007550746724865443</v>
+        <v>0.007550685069652507</v>
       </c>
       <c r="D510" t="n">
         <v>-0.004950521814194087</v>
@@ -7593,7 +7593,7 @@
         <v>45838</v>
       </c>
       <c r="B511" t="n">
-        <v>-0.009766436377643628</v>
+        <v>-0.009766355922302017</v>
       </c>
       <c r="C511" t="n">
         <v>-0.006650435554941159</v>
@@ -7621,7 +7621,7 @@
         <v>45840</v>
       </c>
       <c r="B513" t="n">
-        <v>-0.006281089763032099</v>
+        <v>-0.006281009205256427</v>
       </c>
       <c r="C513" t="n">
         <v>-0.01297149543072262</v>
@@ -7635,7 +7635,7 @@
         <v>45841</v>
       </c>
       <c r="B514" t="n">
-        <v>-0.000658344818495471</v>
+        <v>-0.0006585068990413445</v>
       </c>
       <c r="C514" t="n">
         <v>0.0005538259278525803</v>
@@ -7649,7 +7649,7 @@
         <v>45842</v>
       </c>
       <c r="B515" t="n">
-        <v>0.006259085481400639</v>
+        <v>0.006259167109516239</v>
       </c>
       <c r="C515" t="n">
         <v>0.001107223501737975</v>
@@ -7677,7 +7677,7 @@
         <v>45846</v>
       </c>
       <c r="B517" t="n">
-        <v>-0.002530062867381666</v>
+        <v>-0.002529982994201152</v>
       </c>
       <c r="C517" t="n">
         <v>0.007044422521019555</v>
@@ -7691,7 +7691,7 @@
         <v>45847</v>
       </c>
       <c r="B518" t="n">
-        <v>-0.01209672737504952</v>
+        <v>-0.01209680648216571</v>
       </c>
       <c r="C518" t="n">
         <v>0.004896491971455363</v>
@@ -7705,7 +7705,7 @@
         <v>45848</v>
       </c>
       <c r="B519" t="n">
-        <v>-0.001185043006442732</v>
+        <v>-0.00118496195014961</v>
       </c>
       <c r="C519" t="n">
         <v>-0.002486058437645711</v>
@@ -7719,7 +7719,7 @@
         <v>45849</v>
       </c>
       <c r="B520" t="n">
-        <v>-0.01450032197239437</v>
+        <v>-0.01450040194811342</v>
       </c>
       <c r="C520" t="n">
         <v>-0.01121520547190669</v>
@@ -7775,7 +7775,7 @@
         <v>45855</v>
       </c>
       <c r="B524" t="n">
-        <v>-0.006192692010126066</v>
+        <v>-0.006192774888766461</v>
       </c>
       <c r="C524" t="n">
         <v>-0.00470873275173922</v>
@@ -7789,7 +7789,7 @@
         <v>45856</v>
       </c>
       <c r="B525" t="n">
-        <v>-0.0002709506163521835</v>
+        <v>-0.0002709506389481087</v>
       </c>
       <c r="C525" t="n">
         <v>-0.01484724333406418</v>
@@ -7803,7 +7803,7 @@
         <v>45859</v>
       </c>
       <c r="B526" t="n">
-        <v>-0.03211388916092317</v>
+        <v>-0.03211380842210021</v>
       </c>
       <c r="C526" t="n">
         <v>0.02201902118733501</v>
@@ -7831,7 +7831,7 @@
         <v>45861</v>
       </c>
       <c r="B528" t="n">
-        <v>0.008352212772528844</v>
+        <v>0.008352125623248163</v>
       </c>
       <c r="C528" t="n">
         <v>0.008569600498690821</v>
@@ -7845,7 +7845,7 @@
         <v>45862</v>
       </c>
       <c r="B529" t="n">
-        <v>-0.01523231431371186</v>
+        <v>-0.01523231563020155</v>
       </c>
       <c r="C529" t="n">
         <v>-0.004989450728788647</v>
@@ -7859,7 +7859,7 @@
         <v>45863</v>
       </c>
       <c r="B530" t="n">
-        <v>-0.007983564911071106</v>
+        <v>-0.007983477847461673</v>
       </c>
       <c r="C530" t="n">
         <v>-0.002289456349655272</v>
@@ -7873,7 +7873,7 @@
         <v>45866</v>
       </c>
       <c r="B531" t="n">
-        <v>-0.00294607045514228</v>
+        <v>-0.002945981984557977</v>
       </c>
       <c r="C531" t="n">
         <v>0.001945537494542959</v>
@@ -7887,7 +7887,7 @@
         <v>45867</v>
       </c>
       <c r="B532" t="n">
-        <v>0.02125974232938521</v>
+        <v>0.02125974044296597</v>
       </c>
       <c r="C532" t="n">
         <v>0.006522268153317246</v>
@@ -7901,7 +7901,7 @@
         <v>45868</v>
       </c>
       <c r="B533" t="n">
-        <v>-0.004939664122301846</v>
+        <v>-0.004939663693119933</v>
       </c>
       <c r="C533" t="n">
         <v>0.002077598581772033</v>
@@ -7915,7 +7915,7 @@
         <v>45869</v>
       </c>
       <c r="B534" t="n">
-        <v>-0.01411247403872329</v>
+        <v>-0.01411256012262685</v>
       </c>
       <c r="C534" t="n">
         <v>-0.003751652420309948</v>
@@ -7971,7 +7971,7 @@
         <v>45875</v>
       </c>
       <c r="B538" t="n">
-        <v>0.0007903961995867625</v>
+        <v>0.0007904846701709545</v>
       </c>
       <c r="C538" t="n">
         <v>0.00389364549820348</v>
@@ -7985,7 +7985,7 @@
         <v>45876</v>
       </c>
       <c r="B539" t="n">
-        <v>-0.002441008878437123</v>
+        <v>-0.002441185464059914</v>
       </c>
       <c r="C539" t="n">
         <v>0.005087379911111745</v>
@@ -7999,7 +7999,7 @@
         <v>45877</v>
       </c>
       <c r="B540" t="n">
-        <v>-0.01554635100336188</v>
+        <v>-0.01554626376399793</v>
       </c>
       <c r="C540" t="n">
         <v>-0.0107747818667655</v>
@@ -10964,7 +10964,7 @@
         <v>0.01131676360786527</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01033768582553751</v>
+        <v>0.01033775009584303</v>
       </c>
       <c r="D2" t="n">
         <v>0.04173046067354669</v>
@@ -10978,7 +10978,7 @@
         <v>0.05609118821429271</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02910172764452623</v>
+        <v>0.02910172579328685</v>
       </c>
       <c r="D3" t="n">
         <v>0.03944302829352053</v>
@@ -10992,7 +10992,7 @@
         <v>-0.07357062629644417</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01943661040270772</v>
+        <v>0.01943654738745182</v>
       </c>
       <c r="D4" t="n">
         <v>-0.05793477443741268</v>
@@ -11193,13 +11193,13 @@
         <v>42491</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.02528756825252187</v>
+        <v>-0.02528756645232355</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04375876676492663</v>
+        <v>0.04375864953280062</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03356508442525419</v>
+        <v>0.03356501680742552</v>
       </c>
     </row>
     <row r="3">
@@ -11207,13 +11207,13 @@
         <v>42522</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01179713557295226</v>
+        <v>0.01179720774730497</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.004611297476646681</v>
+        <v>-0.004611073360027418</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.06234697400321998</v>
+        <v>-0.06234737061372064</v>
       </c>
     </row>
     <row r="4">
@@ -11221,13 +11221,13 @@
         <v>42552</v>
       </c>
       <c r="B4" t="n">
-        <v>0.04720650687542016</v>
+        <v>0.04720650006027394</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0679828419162305</v>
+        <v>0.067982608570059</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.07212737298965033</v>
+        <v>-0.07212705935675201</v>
       </c>
     </row>
     <row r="5">
@@ -11235,13 +11235,13 @@
         <v>42583</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04443786848058484</v>
+        <v>0.04443772449348371</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03610977076168398</v>
+        <v>0.03610977457685749</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.03538678437497011</v>
+        <v>-0.0353866393054626</v>
       </c>
     </row>
     <row r="6">
@@ -11252,10 +11252,10 @@
         <v>0.0223586158868474</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.01421162386364216</v>
+        <v>-0.01421131939482478</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001930926164017688</v>
+        <v>0.0001930146621764717</v>
       </c>
     </row>
     <row r="7">
@@ -11263,13 +11263,13 @@
         <v>42644</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.02652962219273525</v>
+        <v>-0.0265295576384359</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.01084173124683785</v>
+        <v>-0.01084172900384139</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.03720878611448108</v>
+        <v>-0.03720855519695743</v>
       </c>
     </row>
     <row r="8">
@@ -11277,13 +11277,13 @@
         <v>42675</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.06151943362372714</v>
+        <v>-0.06151949585772287</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.04721808622001189</v>
+        <v>-0.04721828549724461</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.01151596642464936</v>
+        <v>-0.01151612646270839</v>
       </c>
     </row>
     <row r="9">
@@ -11291,13 +11291,13 @@
         <v>42705</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0932780315434445</v>
+        <v>0.09327810220401633</v>
       </c>
       <c r="C9" t="n">
         <v>0.005501787592539387</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03592845118424171</v>
+        <v>0.0359283692898742</v>
       </c>
     </row>
     <row r="10">
@@ -11305,13 +11305,13 @@
         <v>42736</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.03436804601787069</v>
+        <v>-0.03436817306027418</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0666969909233539</v>
+        <v>0.06669688176476263</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.08113999773431013</v>
+        <v>-0.08113992509467516</v>
       </c>
     </row>
     <row r="11">
@@ -11319,13 +11319,13 @@
         <v>42767</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1845102362377589</v>
+        <v>0.1845103155196031</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0804026363915733</v>
+        <v>0.08040284928600028</v>
       </c>
       <c r="D11" t="n">
-        <v>0.09024361054970909</v>
+        <v>0.09024352451475637</v>
       </c>
     </row>
     <row r="12">
@@ -11333,13 +11333,13 @@
         <v>42795</v>
       </c>
       <c r="B12" t="n">
-        <v>0.06691972401921342</v>
+        <v>0.06691983703160731</v>
       </c>
       <c r="C12" t="n">
-        <v>0.03773108636389777</v>
+        <v>0.03773098807238862</v>
       </c>
       <c r="D12" t="n">
-        <v>0.009729168036144875</v>
+        <v>0.009729484457982496</v>
       </c>
     </row>
     <row r="13">
@@ -11347,13 +11347,13 @@
         <v>42826</v>
       </c>
       <c r="B13" t="n">
-        <v>0.05624955776734253</v>
+        <v>0.05624944588518699</v>
       </c>
       <c r="C13" t="n">
-        <v>0.07205997787521778</v>
+        <v>0.07206006914907204</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1010517069038146</v>
+        <v>-0.1010517613644223</v>
       </c>
     </row>
     <row r="14">
@@ -11361,13 +11361,13 @@
         <v>42856</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.03906267784582651</v>
+        <v>-0.03906257756271736</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05800180017388734</v>
+        <v>0.05800188037443688</v>
       </c>
       <c r="D14" t="n">
-        <v>0.06322440354590531</v>
+        <v>0.06322413173742225</v>
       </c>
     </row>
     <row r="15">
@@ -11375,13 +11375,13 @@
         <v>42887</v>
       </c>
       <c r="B15" t="n">
-        <v>0.02931317243506082</v>
+        <v>0.02931296065661426</v>
       </c>
       <c r="C15" t="n">
-        <v>0.009687212969008652</v>
+        <v>0.009687050467393155</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.04247472490164461</v>
+        <v>-0.04247448306877766</v>
       </c>
     </row>
     <row r="16">
@@ -11389,13 +11389,13 @@
         <v>42917</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1704348243980538</v>
+        <v>0.1704349430657408</v>
       </c>
       <c r="C16" t="n">
         <v>0.08728968871479048</v>
       </c>
       <c r="D16" t="n">
-        <v>0.09742893702024635</v>
+        <v>0.09742857879700884</v>
       </c>
     </row>
     <row r="17">
@@ -11409,7 +11409,7 @@
         <v>-0.004455369848767265</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09518401791101549</v>
+        <v>-0.0951837992810568</v>
       </c>
     </row>
     <row r="18">
@@ -11417,13 +11417,13 @@
         <v>42979</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.02050797615593347</v>
+        <v>-0.02050806321238841</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01646547336873794</v>
+        <v>0.01646532611102991</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.01644893113681722</v>
+        <v>-0.01644892972220446</v>
       </c>
     </row>
     <row r="19">
@@ -11431,13 +11431,13 @@
         <v>43009</v>
       </c>
       <c r="B19" t="n">
-        <v>0.2048275974853588</v>
+        <v>0.2048278823278564</v>
       </c>
       <c r="C19" t="n">
-        <v>0.001550713278851701</v>
+        <v>0.001550785939675947</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0243916855723405</v>
+        <v>0.02439133368536095</v>
       </c>
     </row>
     <row r="20">
@@ -11445,13 +11445,13 @@
         <v>43040</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.02051337472769943</v>
+        <v>-0.02051351923959888</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02499300626875534</v>
+        <v>0.02499308040035975</v>
       </c>
       <c r="D20" t="n">
-        <v>0.07363258777215931</v>
+        <v>0.07363277734042017</v>
       </c>
     </row>
     <row r="21">
@@ -11459,13 +11459,13 @@
         <v>43070</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.0005425632347132447</v>
+        <v>-0.0005424126063859891</v>
       </c>
       <c r="C21" t="n">
         <v>0.01008789155248446</v>
       </c>
       <c r="D21" t="n">
-        <v>0.06756487629755181</v>
+        <v>0.06756496117172839</v>
       </c>
     </row>
     <row r="22">
@@ -11473,13 +11473,13 @@
         <v>43101</v>
       </c>
       <c r="B22" t="n">
-        <v>0.04370020114523099</v>
+        <v>0.0437001192041333</v>
       </c>
       <c r="C22" t="n">
-        <v>0.07119198983235031</v>
+        <v>0.07119205968813858</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1038336759494229</v>
+        <v>0.1038335270074915</v>
       </c>
     </row>
     <row r="23">
@@ -11487,13 +11487,13 @@
         <v>43132</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.007021801120325799</v>
+        <v>-0.007021800613352558</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.06057726406637554</v>
+        <v>-0.06057732532907356</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01943047303744838</v>
+        <v>0.01943088045378016</v>
       </c>
     </row>
     <row r="24">
@@ -11501,13 +11501,13 @@
         <v>43160</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.07527095551719676</v>
+        <v>-0.07527116817556612</v>
       </c>
       <c r="C24" t="n">
-        <v>0.001008231483951016</v>
+        <v>0.001008370320564111</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.03479438352847231</v>
+        <v>-0.03479450667737893</v>
       </c>
     </row>
     <row r="25">
@@ -11515,13 +11515,13 @@
         <v>43191</v>
       </c>
       <c r="B25" t="n">
-        <v>0.09131067745508026</v>
+        <v>0.09131077044334845</v>
       </c>
       <c r="C25" t="n">
-        <v>0.03085753580491901</v>
+        <v>0.03085732347994607</v>
       </c>
       <c r="D25" t="n">
-        <v>0.05981609625394912</v>
+        <v>0.05981608805130456</v>
       </c>
     </row>
     <row r="26">
@@ -11529,13 +11529,13 @@
         <v>43221</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.04354809924541314</v>
+        <v>-0.04354810238305384</v>
       </c>
       <c r="C26" t="n">
-        <v>0.100370133421595</v>
+        <v>0.1003702747188024</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02692796567815736</v>
+        <v>0.02692796219391091</v>
       </c>
     </row>
     <row r="27">
@@ -11543,13 +11543,13 @@
         <v>43252</v>
       </c>
       <c r="B27" t="n">
-        <v>0.05546200344772623</v>
+        <v>0.05546193229520369</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.008195072135599224</v>
+        <v>-0.008195071634583218</v>
       </c>
       <c r="D27" t="n">
-        <v>0.06121133452326322</v>
+        <v>0.06121094881525502</v>
       </c>
     </row>
     <row r="28">
@@ -11557,13 +11557,13 @@
         <v>43282</v>
       </c>
       <c r="B28" t="n">
-        <v>0.2277525973184804</v>
+        <v>0.227752629828829</v>
       </c>
       <c r="C28" t="n">
-        <v>0.033697640310828</v>
+        <v>0.03369757659223804</v>
       </c>
       <c r="D28" t="n">
-        <v>0.06989043043726673</v>
+        <v>0.06989080322615493</v>
       </c>
     </row>
     <row r="29">
@@ -11571,13 +11571,13 @@
         <v>43313</v>
       </c>
       <c r="B29" t="n">
-        <v>0.04692240142596171</v>
+        <v>0.04692252314595202</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.05427832827028123</v>
+        <v>-0.05427844753421518</v>
       </c>
       <c r="D29" t="n">
-        <v>0.05567370668349936</v>
+        <v>0.05567358953037593</v>
       </c>
     </row>
     <row r="30">
@@ -11588,10 +11588,10 @@
         <v>0.01312776412558136</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.02675633935328947</v>
+        <v>-0.0267562796730374</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01318442841424083</v>
+        <v>0.01318432329202412</v>
       </c>
     </row>
     <row r="31">
@@ -11599,13 +11599,13 @@
         <v>43374</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.1563655372812077</v>
+        <v>-0.1563655920885397</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.04700767154066388</v>
+        <v>-0.04700773937414449</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.05979037278600052</v>
+        <v>-0.0597903789895079</v>
       </c>
     </row>
     <row r="32">
@@ -11613,13 +11613,13 @@
         <v>43405</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1001649479981783</v>
+        <v>0.1001650194712063</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1133514686654962</v>
+        <v>0.1133515520613138</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0170186389414656</v>
+        <v>-0.01701853046721946</v>
       </c>
     </row>
     <row r="33">
@@ -11627,13 +11627,13 @@
         <v>43435</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.03965581118166639</v>
+        <v>-0.03965569307986005</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.003171204820299756</v>
+        <v>-0.003171266076154367</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.01273532115648235</v>
+        <v>-0.01273498436796072</v>
       </c>
     </row>
     <row r="34">
@@ -11641,13 +11641,13 @@
         <v>43466</v>
       </c>
       <c r="B34" t="n">
-        <v>0.09444838215164508</v>
+        <v>0.09444812457929785</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.01967772115161914</v>
+        <v>-0.01967766230592038</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1374915924939377</v>
+        <v>0.1374913181691446</v>
       </c>
     </row>
     <row r="35">
@@ -11655,13 +11655,13 @@
         <v>43497</v>
       </c>
       <c r="B35" t="n">
-        <v>0.003177930987366517</v>
+        <v>0.003178268442047383</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.001153804913053169</v>
+        <v>-0.001153804985149831</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.01496017786828963</v>
+        <v>-0.01496017637277403</v>
       </c>
     </row>
     <row r="36">
@@ -11669,13 +11669,13 @@
         <v>43525</v>
       </c>
       <c r="B36" t="n">
-        <v>0.107388026792318</v>
+        <v>0.1073878907254151</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1161704454027115</v>
+        <v>0.1161703901118953</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01300576788121832</v>
+        <v>0.01300566507667278</v>
       </c>
     </row>
     <row r="37">
@@ -11683,13 +11683,13 @@
         <v>43556</v>
       </c>
       <c r="B37" t="n">
-        <v>0.02167597900980334</v>
+        <v>0.02167587566951013</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0006253746755428002</v>
+        <v>-0.0006252626512279758</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01008258981792975</v>
+        <v>0.01008248963620018</v>
       </c>
     </row>
     <row r="38">
@@ -11697,13 +11697,13 @@
         <v>43586</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.04498110054431226</v>
+        <v>-0.04498129854803867</v>
       </c>
       <c r="C38" t="n">
         <v>0.04655984040330785</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0181006640910496</v>
+        <v>-0.01810066588630477</v>
       </c>
     </row>
     <row r="39">
@@ -11711,13 +11711,13 @@
         <v>43617</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.05792582864992946</v>
+        <v>-0.05792573699483083</v>
       </c>
       <c r="C39" t="n">
         <v>0.007586562715956591</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.007794240062351521</v>
+        <v>-0.007794038829487149</v>
       </c>
     </row>
     <row r="40">
@@ -11725,13 +11725,13 @@
         <v>43647</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.06930801147133692</v>
+        <v>-0.0693081291368447</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.07288198530362033</v>
+        <v>-0.0728818789360649</v>
       </c>
       <c r="D40" t="n">
-        <v>0.09953740466097383</v>
+        <v>0.09953719092063085</v>
       </c>
     </row>
     <row r="41">
@@ -11739,13 +11739,13 @@
         <v>43678</v>
       </c>
       <c r="B41" t="n">
-        <v>0.07056798399213804</v>
+        <v>0.07056811891260195</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.01052560567579375</v>
+        <v>-0.01052560446819906</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0267748583872347</v>
+        <v>0.02677513862914194</v>
       </c>
     </row>
     <row r="42">
@@ -11753,13 +11753,13 @@
         <v>43709</v>
       </c>
       <c r="B42" t="n">
-        <v>0.07344254589634525</v>
+        <v>0.07344266444726588</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1043172708225355</v>
+        <v>0.1043172587269816</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.01135091783738595</v>
+        <v>-0.011351366656429</v>
       </c>
     </row>
     <row r="43">
@@ -11770,10 +11770,10 @@
         <v>0.09915556009616355</v>
       </c>
       <c r="C43" t="n">
-        <v>0.00236263620305821</v>
+        <v>0.002362425961570436</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.14901022767021</v>
+        <v>-0.1490099036089589</v>
       </c>
     </row>
     <row r="44">
@@ -11784,10 +11784,10 @@
         <v>0.0592755585995135</v>
       </c>
       <c r="C44" t="n">
-        <v>0.03624993963825274</v>
+        <v>0.03624994343540666</v>
       </c>
       <c r="D44" t="n">
-        <v>0.02846491065420786</v>
+        <v>0.02846469324464596</v>
       </c>
     </row>
     <row r="45">
@@ -11795,13 +11795,13 @@
         <v>43800</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.02391769280994405</v>
+        <v>-0.02391778117471599</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.002235492874372746</v>
+        <v>-0.00223549310034743</v>
       </c>
       <c r="D45" t="n">
-        <v>0.04997469709462621</v>
+        <v>0.0499745980896722</v>
       </c>
     </row>
     <row r="46">
@@ -11809,13 +11809,13 @@
         <v>43831</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.06763327402710306</v>
+        <v>-0.06763309908984705</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.03600353698342085</v>
+        <v>-0.03600333800817923</v>
       </c>
       <c r="D46" t="n">
-        <v>0.06127323508627058</v>
+        <v>0.06127324724935623</v>
       </c>
     </row>
     <row r="47">
@@ -11823,13 +11823,13 @@
         <v>43862</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.05879642791671713</v>
+        <v>-0.05879661640180378</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0396719642701564</v>
+        <v>-0.0396721702911893</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.057026876000982</v>
+        <v>-0.05702660610029919</v>
       </c>
     </row>
     <row r="48">
@@ -11837,13 +11837,13 @@
         <v>43891</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.1617431615816605</v>
+        <v>-0.161743023523557</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.2681187612152165</v>
+        <v>-0.2681186811204925</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.1232746707332385</v>
+        <v>-0.1232747576852954</v>
       </c>
     </row>
     <row r="49">
@@ -11851,10 +11851,10 @@
         <v>43922</v>
       </c>
       <c r="B49" t="n">
-        <v>0.3162738468170883</v>
+        <v>0.3162737658214723</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1623156001554493</v>
+        <v>0.1623157496834866</v>
       </c>
       <c r="D49" t="n">
         <v>0.1153548508540314</v>
@@ -11865,10 +11865,10 @@
         <v>43952</v>
       </c>
       <c r="B50" t="n">
-        <v>0.008377263814855818</v>
+        <v>0.008377357312147282</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.05005976602900586</v>
+        <v>-0.05005982391231345</v>
       </c>
       <c r="D50" t="n">
         <v>-0.03424177924873795</v>
@@ -11879,13 +11879,13 @@
         <v>43983</v>
       </c>
       <c r="B51" t="n">
-        <v>0.1636848665973858</v>
+        <v>0.1636847586998986</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1200019907632648</v>
+        <v>0.1200020503505979</v>
       </c>
       <c r="D51" t="n">
-        <v>0.07954832230292519</v>
+        <v>0.0795484273227578</v>
       </c>
     </row>
     <row r="52">
@@ -11893,13 +11893,13 @@
         <v>44013</v>
       </c>
       <c r="B52" t="n">
-        <v>0.2130156576818383</v>
+        <v>0.213015737360237</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0310079206578745</v>
+        <v>-0.03100809828238349</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3125891400442689</v>
+        <v>0.3125889150726808</v>
       </c>
     </row>
     <row r="53">
@@ -11907,13 +11907,13 @@
         <v>44044</v>
       </c>
       <c r="B53" t="n">
-        <v>0.01067532253241876</v>
+        <v>0.01067525614499365</v>
       </c>
       <c r="C53" t="n">
-        <v>0.08041230295238777</v>
+        <v>0.08041249514741322</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.03871635389804962</v>
+        <v>-0.03871620853940427</v>
       </c>
     </row>
     <row r="54">
@@ -11921,13 +11921,13 @@
         <v>44075</v>
       </c>
       <c r="B54" t="n">
-        <v>0.07384546212711274</v>
+        <v>0.07384533214232603</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.03338238910218128</v>
+        <v>-0.03338273173997197</v>
       </c>
       <c r="D54" t="n">
-        <v>0.08577420487199516</v>
+        <v>0.08577427535790516</v>
       </c>
     </row>
     <row r="55">
@@ -11935,13 +11935,13 @@
         <v>44105</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.08049328457516425</v>
+        <v>-0.08049323379551354</v>
       </c>
       <c r="C55" t="n">
-        <v>0.09730178450181715</v>
+        <v>0.09730204672749854</v>
       </c>
       <c r="D55" t="n">
-        <v>0.05192172353144642</v>
+        <v>0.05192164514936781</v>
       </c>
     </row>
     <row r="56">
@@ -11949,13 +11949,13 @@
         <v>44136</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.06069610401646264</v>
+        <v>-0.06069597636913215</v>
       </c>
       <c r="C56" t="n">
-        <v>0.21739679151955</v>
+        <v>0.2173969004107923</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0482904786594951</v>
+        <v>0.04829047539972153</v>
       </c>
     </row>
     <row r="57">
@@ -11963,13 +11963,13 @@
         <v>44166</v>
       </c>
       <c r="B57" t="n">
-        <v>0.0287594663578159</v>
+        <v>0.0287594643425122</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.003157711231364213</v>
+        <v>-0.003157800394886001</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1416363645378773</v>
+        <v>0.1416362910235387</v>
       </c>
     </row>
     <row r="58">
@@ -11977,10 +11977,10 @@
         <v>44197</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.07220561831527372</v>
+        <v>-0.07220568151243623</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.03188755481339445</v>
+        <v>-0.0318874650840808</v>
       </c>
       <c r="D58" t="n">
         <v>-0.013338056299943</v>
@@ -11991,13 +11991,13 @@
         <v>44228</v>
       </c>
       <c r="B59" t="n">
-        <v>0.1323869006619385</v>
+        <v>0.1323868272453617</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1034879609389157</v>
+        <v>0.1034877659775615</v>
       </c>
       <c r="D59" t="n">
-        <v>0.01150092896955845</v>
+        <v>0.01150081463484343</v>
       </c>
     </row>
     <row r="60">
@@ -12005,13 +12005,13 @@
         <v>44256</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.03964917051080541</v>
+        <v>-0.0396490434144422</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.02655761517504096</v>
+        <v>-0.02655753341309275</v>
       </c>
       <c r="D60" t="n">
-        <v>0.09155800263144798</v>
+        <v>0.09155823905012861</v>
       </c>
     </row>
     <row r="61">
@@ -12019,13 +12019,13 @@
         <v>44287</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.004293243505164579</v>
+        <v>-0.004293310725519861</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.05446380783913329</v>
+        <v>-0.05446389412321695</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.01001425000458223</v>
+        <v>-0.0100143525211146</v>
       </c>
     </row>
     <row r="62">
@@ -12033,10 +12033,10 @@
         <v>44317</v>
       </c>
       <c r="B62" t="n">
-        <v>0.08312857910270832</v>
+        <v>0.08312851130142329</v>
       </c>
       <c r="C62" t="n">
-        <v>0.07332004794857072</v>
+        <v>0.07332005463932845</v>
       </c>
       <c r="D62" t="n">
         <v>0.02909143628022748</v>
@@ -12047,13 +12047,13 @@
         <v>44348</v>
       </c>
       <c r="B63" t="n">
-        <v>-0.02298284605771062</v>
+        <v>-0.02298278489874583</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.01184156034932848</v>
+        <v>-0.01184147633566679</v>
       </c>
       <c r="D63" t="n">
-        <v>0.1464455419972512</v>
+        <v>0.1464454403531685</v>
       </c>
     </row>
     <row r="64">
@@ -12061,13 +12061,13 @@
         <v>44378</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.0323381894019904</v>
+        <v>-0.03233812533184333</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.04357863128731954</v>
+        <v>-0.04357854524805116</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0187878928123093</v>
+        <v>0.01878816045864995</v>
       </c>
     </row>
     <row r="65">
@@ -12075,13 +12075,13 @@
         <v>44409</v>
       </c>
       <c r="B65" t="n">
-        <v>0.1094925022985254</v>
+        <v>0.1094924288375885</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1086262874678294</v>
+        <v>0.1086262776958546</v>
       </c>
       <c r="D65" t="n">
-        <v>0.05957786873262116</v>
+        <v>0.05957768431275801</v>
       </c>
     </row>
     <row r="66">
@@ -12089,13 +12089,13 @@
         <v>44440</v>
       </c>
       <c r="B66" t="n">
-        <v>0.115625644326244</v>
+        <v>0.1156254056178236</v>
       </c>
       <c r="C66" t="n">
-        <v>0.008568435013004416</v>
+        <v>0.008568272027543955</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.01831295599133109</v>
+        <v>-0.01831303812325913</v>
       </c>
     </row>
     <row r="67">
@@ -12103,13 +12103,13 @@
         <v>44470</v>
       </c>
       <c r="B67" t="n">
-        <v>0.006748022372087936</v>
+        <v>0.006748237784204747</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.007586410643711683</v>
+        <v>-0.007586330798361351</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.004447330668744476</v>
+        <v>-0.0044471637126835</v>
       </c>
     </row>
     <row r="68">
@@ -12123,7 +12123,7 @@
         <v>-0.05641713495158662</v>
       </c>
       <c r="D68" t="n">
-        <v>0.03602364689464332</v>
+        <v>0.03602355982949401</v>
       </c>
     </row>
     <row r="69">
@@ -12134,10 +12134,10 @@
         <v>-0.01548589968317371</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.009474177560710784</v>
+        <v>-0.0094740916427134</v>
       </c>
       <c r="D69" t="n">
-        <v>0.1022390697778548</v>
+        <v>0.1022391508935789</v>
       </c>
     </row>
     <row r="70">
@@ -12145,13 +12145,13 @@
         <v>44562</v>
       </c>
       <c r="B70" t="n">
-        <v>0.007790765801754418</v>
+        <v>0.007790879611988988</v>
       </c>
       <c r="C70" t="n">
-        <v>0.004258403025136692</v>
+        <v>0.004258489395541742</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.08028067312331422</v>
+        <v>-0.08028074080708236</v>
       </c>
     </row>
     <row r="71">
@@ -12159,13 +12159,13 @@
         <v>44593</v>
       </c>
       <c r="B71" t="n">
-        <v>-0.01133403576054681</v>
+        <v>-0.01133426034140439</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.04001484216082307</v>
+        <v>-0.04001492162046583</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.01186509328523022</v>
+        <v>-0.01186501326976475</v>
       </c>
     </row>
     <row r="72">
@@ -12173,13 +12173,13 @@
         <v>44621</v>
       </c>
       <c r="B72" t="n">
-        <v>0.1166323439425943</v>
+        <v>0.1166324714899951</v>
       </c>
       <c r="C72" t="n">
-        <v>0.03092038683728271</v>
+        <v>0.03092020411091956</v>
       </c>
       <c r="D72" t="n">
-        <v>0.111477015820898</v>
+        <v>0.111477087770157</v>
       </c>
     </row>
     <row r="73">
@@ -12190,10 +12190,10 @@
         <v>0.05901896555568986</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.05831949318436302</v>
+        <v>-0.05831941100044513</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.1779373278171686</v>
+        <v>-0.177937374744681</v>
       </c>
     </row>
     <row r="74">
@@ -12204,10 +12204,10 @@
         <v>-0.05648250331436078</v>
       </c>
       <c r="C74" t="n">
-        <v>0.003141620465593409</v>
+        <v>0.003141713144231284</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.04079610755467156</v>
+        <v>-0.04079628118751444</v>
       </c>
     </row>
     <row r="75">
@@ -12218,10 +12218,10 @@
         <v>-0.01405415476974137</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.01819838761936465</v>
+        <v>-0.01819847832642518</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.01743677560043289</v>
+        <v>-0.01743668481798433</v>
       </c>
     </row>
     <row r="76">
@@ -12243,7 +12243,7 @@
         <v>44774</v>
       </c>
       <c r="B77" t="n">
-        <v>0.05120644033431643</v>
+        <v>0.05120633293240195</v>
       </c>
       <c r="C77" t="n">
         <v>0.03618749550588252</v>
@@ -12257,10 +12257,10 @@
         <v>44805</v>
       </c>
       <c r="B78" t="n">
-        <v>-0.09569623589860432</v>
+        <v>-0.09569614350574818</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.04357045679013083</v>
+        <v>-0.04357037143384646</v>
       </c>
       <c r="D78" t="n">
         <v>-0.05325031508898737</v>
@@ -12271,13 +12271,13 @@
         <v>44835</v>
       </c>
       <c r="B79" t="n">
-        <v>0.07227431513353522</v>
+        <v>0.07227420215142799</v>
       </c>
       <c r="C79" t="n">
-        <v>0.05301305784084009</v>
+        <v>0.05301278537557663</v>
       </c>
       <c r="D79" t="n">
-        <v>0.08787015652342722</v>
+        <v>0.08787005926705849</v>
       </c>
     </row>
     <row r="80">
@@ -12285,13 +12285,13 @@
         <v>44866</v>
       </c>
       <c r="B80" t="n">
-        <v>0.07128558868849533</v>
+        <v>0.07128570156643566</v>
       </c>
       <c r="C80" t="n">
-        <v>0.07466418807298547</v>
+        <v>0.07466428548061299</v>
       </c>
       <c r="D80" t="n">
-        <v>0.07489848772434327</v>
+        <v>0.07489849442032215</v>
       </c>
     </row>
     <row r="81">
@@ -12299,13 +12299,13 @@
         <v>44896</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.06742090228748265</v>
+        <v>-0.06742100064294965</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0122478152644856</v>
+        <v>0.01224781623039117</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.07752539074504605</v>
+        <v>-0.07752531402161922</v>
       </c>
     </row>
     <row r="82">
@@ -12313,13 +12313,13 @@
         <v>44927</v>
       </c>
       <c r="B82" t="n">
-        <v>-0.07590678949528251</v>
+        <v>-0.07590690296697222</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.01513995270751467</v>
+        <v>-0.01513979806850441</v>
       </c>
       <c r="D82" t="n">
-        <v>0.01694072630161036</v>
+        <v>0.01694063614052865</v>
       </c>
     </row>
     <row r="83">
@@ -12327,13 +12327,13 @@
         <v>44958</v>
       </c>
       <c r="B83" t="n">
-        <v>-0.01329754391523208</v>
+        <v>-0.01329720456261541</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.002432063943726526</v>
+        <v>-0.002432221965212533</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.03012220597395865</v>
+        <v>-0.03012220864456749</v>
       </c>
     </row>
     <row r="84">
@@ -12341,13 +12341,13 @@
         <v>44986</v>
       </c>
       <c r="B84" t="n">
-        <v>0.00365994673980552</v>
+        <v>0.003659830649118234</v>
       </c>
       <c r="C84" t="n">
-        <v>0.006220276945063663</v>
+        <v>0.006220356738144917</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.04006581347552762</v>
+        <v>-0.04006581713805146</v>
       </c>
     </row>
     <row r="85">
@@ -12355,13 +12355,13 @@
         <v>45017</v>
       </c>
       <c r="B85" t="n">
-        <v>0.03837308748533363</v>
+        <v>0.03837320273090516</v>
       </c>
       <c r="C85" t="n">
         <v>0.04849177751958011</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.1226933736973395</v>
+        <v>-0.1226932901531115</v>
       </c>
     </row>
     <row r="86">
@@ -12369,7 +12369,7 @@
         <v>45047</v>
       </c>
       <c r="B86" t="n">
-        <v>0.02040911684465785</v>
+        <v>0.02040900359286013</v>
       </c>
       <c r="C86" t="n">
         <v>-0.04547878949323492</v>
@@ -12383,13 +12383,13 @@
         <v>45078</v>
       </c>
       <c r="B87" t="n">
-        <v>0.03253161661561332</v>
+        <v>0.03253172538244864</v>
       </c>
       <c r="C87" t="n">
         <v>0.06832514125652933</v>
       </c>
       <c r="D87" t="n">
-        <v>0.01304717681472867</v>
+        <v>0.01304707366602154</v>
       </c>
     </row>
     <row r="88">
@@ -12397,13 +12397,13 @@
         <v>45108</v>
       </c>
       <c r="B88" t="n">
-        <v>0.08299924766203226</v>
+        <v>0.08299913357895106</v>
       </c>
       <c r="C88" t="n">
         <v>-0.02950520700502202</v>
       </c>
       <c r="D88" t="n">
-        <v>0.02876951257632698</v>
+        <v>0.02876961732589689</v>
       </c>
     </row>
     <row r="89">
@@ -12411,13 +12411,13 @@
         <v>45139</v>
       </c>
       <c r="B89" t="n">
-        <v>-0.05580084100833849</v>
+        <v>-0.05580074374145993</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.04829819157577586</v>
+        <v>-0.04829811562507236</v>
       </c>
       <c r="D89" t="n">
-        <v>0.05882579414322286</v>
+        <v>0.05882589311606279</v>
       </c>
     </row>
     <row r="90">
@@ -12425,10 +12425,10 @@
         <v>45170</v>
       </c>
       <c r="B90" t="n">
-        <v>-0.02231659789370977</v>
+        <v>-0.02231669860996432</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.0287313694882575</v>
+        <v>-0.0287314470004878</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -12439,13 +12439,13 @@
         <v>45200</v>
       </c>
       <c r="B91" t="n">
-        <v>-0.02434980881223348</v>
+        <v>-0.02434970344559451</v>
       </c>
       <c r="C91" t="n">
         <v>-0.03262790907292967</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.04671006048244808</v>
+        <v>-0.04671024306454596</v>
       </c>
     </row>
     <row r="92">
@@ -12453,13 +12453,13 @@
         <v>45231</v>
       </c>
       <c r="B92" t="n">
-        <v>0.03914078552641831</v>
+        <v>0.03914067330304039</v>
       </c>
       <c r="C92" t="n">
         <v>0.05573995895664141</v>
       </c>
       <c r="D92" t="n">
-        <v>0.07715929720190373</v>
+        <v>0.07715940282198264</v>
       </c>
     </row>
     <row r="93">
@@ -12495,13 +12495,13 @@
         <v>45323</v>
       </c>
       <c r="B95" t="n">
-        <v>0.02395533985038512</v>
+        <v>0.02395525325271675</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.04044308056615198</v>
+        <v>-0.04044299481880209</v>
       </c>
       <c r="D95" t="n">
-        <v>0.007826948504550346</v>
+        <v>0.007827028258251767</v>
       </c>
     </row>
     <row r="96">
@@ -12509,13 +12509,13 @@
         <v>45352</v>
       </c>
       <c r="B96" t="n">
-        <v>0.01714793192957242</v>
+        <v>0.01714810252326515</v>
       </c>
       <c r="C96" t="n">
-        <v>0.03170873116284034</v>
+        <v>0.03170863896791176</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.1050538975948073</v>
+        <v>-0.1050540475500689</v>
       </c>
     </row>
     <row r="97">
@@ -12523,13 +12523,13 @@
         <v>45383</v>
       </c>
       <c r="B97" t="n">
-        <v>-0.0126862417160658</v>
+        <v>-0.01268632380719259</v>
       </c>
       <c r="C97" t="n">
         <v>0.04986526611447317</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.0517339727653664</v>
+        <v>-0.05173388891630015</v>
       </c>
     </row>
     <row r="98">
@@ -12540,7 +12540,7 @@
         <v>-0.02494890928578097</v>
       </c>
       <c r="C98" t="n">
-        <v>0.007532507668675636</v>
+        <v>0.007532425167660728</v>
       </c>
       <c r="D98" t="n">
         <v>-0.009608981910239289</v>
@@ -12554,7 +12554,7 @@
         <v>0.09437925303146977</v>
       </c>
       <c r="C99" t="n">
-        <v>0.1144218994437196</v>
+        <v>0.1144220725815248</v>
       </c>
       <c r="D99" t="n">
         <v>0.1358997691855399</v>
@@ -12565,13 +12565,13 @@
         <v>45474</v>
       </c>
       <c r="B100" t="n">
-        <v>-0.03831289748878441</v>
+        <v>-0.03831297640943399</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.04041455056372545</v>
+        <v>-0.0404145475941915</v>
       </c>
       <c r="D100" t="n">
-        <v>0.1924365957345227</v>
+        <v>0.192436512846629</v>
       </c>
     </row>
     <row r="101">
@@ -12579,13 +12579,13 @@
         <v>45505</v>
       </c>
       <c r="B101" t="n">
-        <v>0.002789874583664753</v>
+        <v>0.002789956877411459</v>
       </c>
       <c r="C101" t="n">
-        <v>0.01308996779098082</v>
+        <v>0.01308989021720786</v>
       </c>
       <c r="D101" t="n">
-        <v>0.04038526812305476</v>
+        <v>0.04038540995302697</v>
       </c>
     </row>
     <row r="102">
@@ -12599,7 +12599,7 @@
         <v>0.05812814747457162</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.03503625445768643</v>
+        <v>-0.03503625211680583</v>
       </c>
     </row>
     <row r="103">
@@ -12610,10 +12610,10 @@
         <v>-0.09787847189939403</v>
       </c>
       <c r="C103" t="n">
-        <v>0.002107327860843</v>
+        <v>0.002107256430842863</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.06309976096629355</v>
+        <v>-0.06309982583629936</v>
       </c>
     </row>
     <row r="104">
@@ -12624,7 +12624,7 @@
         <v>-0.02991637461127583</v>
       </c>
       <c r="C104" t="n">
-        <v>0.03476985395198673</v>
+        <v>0.03476992771017007</v>
       </c>
       <c r="D104" t="n">
         <v>0.06928647442245439</v>
@@ -12638,7 +12638,7 @@
         <v>-0.059394856650272</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.01291732405612833</v>
+        <v>-0.01291725517144848</v>
       </c>
       <c r="D105" t="n">
         <v>0.01192236364466992</v>
@@ -12652,10 +12652,10 @@
         <v>0.04084913724202299</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.04179707658923082</v>
+        <v>-0.04179714345849983</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.0001063419483060546</v>
+        <v>-0.0001062736490458072</v>
       </c>
     </row>
     <row r="107">
@@ -12669,7 +12669,7 @@
         <v>0.01980872744921469</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.1021917514407553</v>
+        <v>-0.102191812766912</v>
       </c>
     </row>
     <row r="108">
@@ -12680,7 +12680,7 @@
         <v>0.06249474199562455</v>
       </c>
       <c r="C108" t="n">
-        <v>0.05529900306008573</v>
+        <v>0.05529893164451694</v>
       </c>
       <c r="D108" t="n">
         <v>-0.06935467893870073</v>
@@ -12694,7 +12694,7 @@
         <v>0.1018744068157158</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0529482009593909</v>
+        <v>0.05294827221587783</v>
       </c>
       <c r="D109" t="n">
         <v>-0.04491773330927662</v>
@@ -12708,10 +12708,10 @@
         <v>0.01131676360786527</v>
       </c>
       <c r="C110" t="n">
-        <v>0.01033775009584303</v>
+        <v>0.01033768582553751</v>
       </c>
       <c r="D110" t="n">
-        <v>0.04173046067354669</v>
+        <v>0.04173054626957517</v>
       </c>
     </row>
     <row r="111">
@@ -12722,10 +12722,10 @@
         <v>0.05609118821429271</v>
       </c>
       <c r="C111" t="n">
-        <v>0.02910172579328685</v>
+        <v>0.02910172764452623</v>
       </c>
       <c r="D111" t="n">
-        <v>0.03944302829352053</v>
+        <v>0.03944294288545058</v>
       </c>
     </row>
     <row r="112">
@@ -12736,7 +12736,7 @@
         <v>-0.07357062629644417</v>
       </c>
       <c r="C112" t="n">
-        <v>0.01943654738745182</v>
+        <v>0.01943661040270772</v>
       </c>
       <c r="D112" t="n">
         <v>-0.05793477443741268</v>
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.2114788033080162</v>
+        <v>-0.2114788580279693</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -13215,13 +13215,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.07020861165076352</v>
+        <v>0.07020861100335116</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02153099663820352</v>
+        <v>0.0215309782071518</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02033709669403654</v>
+        <v>0.02033708260679609</v>
       </c>
     </row>
     <row r="3">
@@ -13231,13 +13231,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02153099663820352</v>
+        <v>0.0215309782071518</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04811833741636462</v>
+        <v>0.04811835164481708</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007297247831060697</v>
+        <v>0.007297244881136339</v>
       </c>
     </row>
     <row r="4">
@@ -13247,13 +13247,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02033709669403654</v>
+        <v>0.02033708260679609</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007297247831060697</v>
+        <v>0.007297244881136339</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06425516992866435</v>
+        <v>0.06425512456745011</v>
       </c>
     </row>
   </sheetData>
